--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="701">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1191,6 +1191,12 @@
   </si>
   <si>
     <t xml:space="preserve">QuestExploration_AfterCrystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONEV</t>
   </si>
   <si>
     <t xml:space="preserve">bg_road</t>
@@ -3010,7 +3016,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="12.8">
@@ -3033,7 +3039,7 @@
         <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" ht="12.8">
@@ -3056,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" ht="12.8">
@@ -3079,7 +3085,7 @@
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" ht="12.8">
@@ -3102,7 +3108,7 @@
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" ht="12.8">
@@ -3125,7 +3131,7 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" ht="12.8">
@@ -3148,7 +3154,7 @@
         <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" ht="12.8">
@@ -3171,7 +3177,7 @@
         <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" ht="12.8">
@@ -3194,7 +3200,7 @@
         <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" ht="12.8">
@@ -3217,7 +3223,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" ht="12.8">
@@ -3240,7 +3246,7 @@
         <v>53</v>
       </c>
       <c r="H15" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -5065,7 +5071,7 @@
         <v>92</v>
       </c>
       <c r="K35" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" ht="12.8">
@@ -5087,7 +5093,7 @@
         <v>94</v>
       </c>
       <c r="K37" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" ht="12.8">
@@ -5109,7 +5115,7 @@
         <v>96</v>
       </c>
       <c r="K39" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" ht="12.8">
@@ -5137,7 +5143,7 @@
         <v>99</v>
       </c>
       <c r="K41" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" ht="12.8">
@@ -5244,7 +5250,7 @@
         <v>117</v>
       </c>
       <c r="K54" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" s="5" customFormat="1" ht="12.8">
@@ -5530,7 +5536,7 @@
         <v>120</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -5793,7 +5799,7 @@
         <v>122</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -6056,7 +6062,7 @@
         <v>124</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -6858,7 +6864,7 @@
         <v>131</v>
       </c>
       <c r="K65" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="66" ht="32.8">
@@ -6872,7 +6878,7 @@
         <v>133</v>
       </c>
       <c r="K66" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" ht="12.8">
@@ -6894,7 +6900,7 @@
         <v>137</v>
       </c>
       <c r="K68" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69" ht="35.8">
@@ -6908,7 +6914,7 @@
         <v>139</v>
       </c>
       <c r="K69" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="70" ht="12.8">
@@ -7003,7 +7009,7 @@
         <v>144</v>
       </c>
       <c r="K80" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="82" ht="12.8">
@@ -7327,7 +7333,7 @@
         <v>150</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
@@ -7590,7 +7596,7 @@
         <v>152</v>
       </c>
       <c r="K96" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" ht="12.8">
@@ -7607,7 +7613,7 @@
         <v>154</v>
       </c>
       <c r="K97" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" ht="105.95">
@@ -7624,7 +7630,7 @@
         <v>156</v>
       </c>
       <c r="K98" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="99" ht="53.7">
@@ -7641,7 +7647,7 @@
         <v>158</v>
       </c>
       <c r="K99" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" ht="43.25">
@@ -7658,7 +7664,7 @@
         <v>160</v>
       </c>
       <c r="K100" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="101" ht="43.25">
@@ -7675,7 +7681,7 @@
         <v>162</v>
       </c>
       <c r="K101" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="102" ht="12.8">
@@ -7692,7 +7698,7 @@
         <v>164</v>
       </c>
       <c r="K102" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="103" ht="12.8">
@@ -7709,7 +7715,7 @@
         <v>166</v>
       </c>
       <c r="K103" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="104" ht="53.7">
@@ -7726,7 +7732,7 @@
         <v>168</v>
       </c>
       <c r="K104" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="105" ht="12.8">
@@ -7743,7 +7749,7 @@
         <v>170</v>
       </c>
       <c r="K105" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="106" ht="12.8">
@@ -7768,7 +7774,7 @@
         <v>172</v>
       </c>
       <c r="K107" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="108" ht="12.8">
@@ -8348,7 +8354,7 @@
         <v>177</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
@@ -8611,7 +8617,7 @@
         <v>179</v>
       </c>
       <c r="K119" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="120" ht="12.8">
@@ -8628,7 +8634,7 @@
         <v>181</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -8891,7 +8897,7 @@
         <v>183</v>
       </c>
       <c r="K121" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="122" ht="43.25">
@@ -8908,7 +8914,7 @@
         <v>185</v>
       </c>
       <c r="K122" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="123" ht="22.35">
@@ -8925,7 +8931,7 @@
         <v>187</v>
       </c>
       <c r="K123" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="124" ht="12.8">
@@ -8942,7 +8948,7 @@
         <v>189</v>
       </c>
       <c r="K124" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="125" ht="85.05">
@@ -8959,7 +8965,7 @@
         <v>191</v>
       </c>
       <c r="K125" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="126" ht="74.6">
@@ -8976,7 +8982,7 @@
         <v>193</v>
       </c>
       <c r="K126" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="127" ht="53.7">
@@ -8993,7 +8999,7 @@
         <v>195</v>
       </c>
       <c r="K127" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="128" ht="53.7">
@@ -9010,7 +9016,7 @@
         <v>197</v>
       </c>
       <c r="K128" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="129" ht="12.8">
@@ -9607,7 +9613,7 @@
         <v>177</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
@@ -9870,7 +9876,7 @@
         <v>202</v>
       </c>
       <c r="K140" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="141" ht="12.8">
@@ -9887,7 +9893,7 @@
         <v>204</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
@@ -10150,7 +10156,7 @@
         <v>206</v>
       </c>
       <c r="K142" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="143" ht="12.8">
@@ -10167,7 +10173,7 @@
         <v>208</v>
       </c>
       <c r="K143" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="144" ht="12.8">
@@ -10184,7 +10190,7 @@
         <v>210</v>
       </c>
       <c r="K144" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="145" ht="12.8">
@@ -10492,7 +10498,7 @@
         <v>214</v>
       </c>
       <c r="K150" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="151" ht="64.15">
@@ -10509,7 +10515,7 @@
         <v>216</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -10772,7 +10778,7 @@
         <v>218</v>
       </c>
       <c r="K152" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="153" ht="12.8">
@@ -10789,7 +10795,7 @@
         <v>220</v>
       </c>
       <c r="K153" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="154" ht="64.15">
@@ -10806,7 +10812,7 @@
         <v>222</v>
       </c>
       <c r="K154" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="155" ht="64.15">
@@ -10823,7 +10829,7 @@
         <v>224</v>
       </c>
       <c r="K155" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="156" ht="85.05">
@@ -10840,7 +10846,7 @@
         <v>226</v>
       </c>
       <c r="K156" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="157" ht="12.8">
@@ -10857,7 +10863,7 @@
         <v>228</v>
       </c>
       <c r="K157" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="158" ht="64.15">
@@ -10874,7 +10880,7 @@
         <v>230</v>
       </c>
       <c r="K158" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" ht="12.8">
@@ -10908,7 +10914,7 @@
         <v>232</v>
       </c>
       <c r="K160" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="161" ht="53.7">
@@ -10925,7 +10931,7 @@
         <v>234</v>
       </c>
       <c r="K161" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="162" ht="12.8">
@@ -12273,7 +12279,7 @@
         <v>241</v>
       </c>
       <c r="K174" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="175" ht="12.8">
@@ -12290,7 +12296,7 @@
         <v>244</v>
       </c>
       <c r="K175" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="176" s="5" customFormat="1" ht="12.8">
@@ -12313,7 +12319,7 @@
         <v>246</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
@@ -12582,7 +12588,7 @@
         <v>248</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
@@ -12851,7 +12857,7 @@
         <v>250</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
@@ -13120,7 +13126,7 @@
         <v>252</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
@@ -13389,7 +13395,7 @@
         <v>254</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
@@ -14159,7 +14165,7 @@
         <v>257</v>
       </c>
       <c r="K183" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184" ht="22.35">
@@ -14176,7 +14182,7 @@
         <v>259</v>
       </c>
       <c r="K184" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="185" ht="22.35">
@@ -14193,7 +14199,7 @@
         <v>261</v>
       </c>
       <c r="K185" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="186" ht="12.8">
@@ -14210,7 +14216,7 @@
         <v>263</v>
       </c>
       <c r="K186" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="187" ht="12.8">
@@ -14268,7 +14274,7 @@
         <v>266</v>
       </c>
       <c r="K191" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="192" ht="12.8">
@@ -14319,7 +14325,7 @@
         <v>269</v>
       </c>
       <c r="K201" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="202" ht="64.15">
@@ -14336,7 +14342,7 @@
         <v>271</v>
       </c>
       <c r="K202" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="205" ht="12.8">
@@ -16017,7 +16023,7 @@
         <v>282</v>
       </c>
       <c r="K236" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="237" ht="12.8">
@@ -16039,7 +16045,7 @@
         <v>284</v>
       </c>
       <c r="K238" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="239" ht="12.8">
@@ -16061,7 +16067,7 @@
         <v>286</v>
       </c>
       <c r="K240" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="241" ht="12.8">
@@ -16184,7 +16190,7 @@
         <v>294</v>
       </c>
       <c r="K255" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="256" ht="22.35">
@@ -16201,7 +16207,7 @@
         <v>296</v>
       </c>
       <c r="K256" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="257" ht="95.5">
@@ -16218,7 +16224,7 @@
         <v>298</v>
       </c>
       <c r="K257" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="258" ht="12.8">
@@ -16235,7 +16241,7 @@
         <v>300</v>
       </c>
       <c r="K258" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" ht="12.8">
@@ -16252,7 +16258,7 @@
         <v>302</v>
       </c>
       <c r="K259" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="260" ht="12.8">
@@ -16269,7 +16275,7 @@
         <v>304</v>
       </c>
       <c r="K260" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="261" ht="53.7">
@@ -16286,7 +16292,7 @@
         <v>306</v>
       </c>
       <c r="K261" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="262" ht="53.7">
@@ -16303,7 +16309,7 @@
         <v>308</v>
       </c>
       <c r="K262" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="263" ht="12.8">
@@ -16337,7 +16343,7 @@
         <v>310</v>
       </c>
       <c r="K264" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" ht="85.05">
@@ -16354,7 +16360,7 @@
         <v>312</v>
       </c>
       <c r="K265" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="266" ht="12.8">
@@ -16371,7 +16377,7 @@
         <v>314</v>
       </c>
       <c r="K266" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="267" ht="12.8">
@@ -16420,7 +16426,7 @@
         <v>319</v>
       </c>
       <c r="K271" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="273" ht="12.8">
@@ -16453,6 +16459,14 @@
       </c>
       <c r="E276" s="1" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="277" ht="12.8">
+      <c r="D277" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="282" ht="12.8">
@@ -16733,7 +16747,7 @@
         <v>128</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="289" ht="12.8">
@@ -17013,13 +17027,13 @@
         <v>83</v>
       </c>
       <c r="I291" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
@@ -17276,13 +17290,13 @@
         <v>84</v>
       </c>
       <c r="I293" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
@@ -17556,13 +17570,13 @@
         <v>86</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K295" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="296" ht="12.8">
@@ -17573,13 +17587,13 @@
         <v>87</v>
       </c>
       <c r="I296" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K296" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="297" ht="12.8">
@@ -17590,13 +17604,13 @@
         <v>88</v>
       </c>
       <c r="I297" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K297" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="298" ht="74.6">
@@ -17607,13 +17621,13 @@
         <v>89</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J298" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K298" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="299" ht="95.5">
@@ -17624,13 +17638,13 @@
         <v>90</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J299" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K299" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="300" ht="12.8">
@@ -17641,13 +17655,13 @@
         <v>91</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K300" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="301" ht="53.7">
@@ -17658,13 +17672,13 @@
         <v>92</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J301" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K301" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="302" ht="12.8">
@@ -17675,13 +17689,13 @@
         <v>93</v>
       </c>
       <c r="I302" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K302" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="303" ht="85.05">
@@ -17692,13 +17706,13 @@
         <v>94</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J303" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K303" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="304" ht="12.8">
@@ -17709,13 +17723,13 @@
         <v>95</v>
       </c>
       <c r="I304" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K304" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="305" ht="12.8">
@@ -17726,13 +17740,13 @@
         <v>96</v>
       </c>
       <c r="I305" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K305" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="306" ht="12.8">
@@ -17760,13 +17774,13 @@
         <v>98</v>
       </c>
       <c r="I307" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K307" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="308" ht="12.8">
@@ -17777,13 +17791,13 @@
         <v>99</v>
       </c>
       <c r="I308" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K308" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="309" ht="12.8">
@@ -17811,13 +17825,13 @@
         <v>101</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J310" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K310" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="311" ht="12.8">
@@ -17872,7 +17886,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" ht="12.8">
@@ -17895,11 +17909,11 @@
         <v>106</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J323" s="4"/>
       <c r="K323" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -18153,10 +18167,10 @@
         <v>107</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K324" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="325" ht="12.8">
@@ -18164,10 +18178,10 @@
         <v>108</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
@@ -18421,10 +18435,10 @@
         <v>109</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K326" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="327" ht="22.35">
@@ -18432,10 +18446,10 @@
         <v>110</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K327" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="328" ht="12.8">
@@ -18443,10 +18457,10 @@
         <v>111</v>
       </c>
       <c r="I328" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K328" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="329" ht="12.8">
@@ -18454,10 +18468,10 @@
         <v>112</v>
       </c>
       <c r="I329" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K329" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="330" ht="12.8">
@@ -18481,7 +18495,7 @@
         <v>128</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="335" ht="12.8">
@@ -18489,7 +18503,7 @@
         <v>86</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="337" s="9" customFormat="1" ht="12.8">
@@ -19022,10 +19036,10 @@
         <v>113</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
@@ -19282,10 +19296,10 @@
         <v>114</v>
       </c>
       <c r="I340" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
@@ -19542,10 +19556,10 @@
         <v>115</v>
       </c>
       <c r="I341" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K341" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="342" ht="12.8">
@@ -19556,10 +19570,10 @@
         <v>116</v>
       </c>
       <c r="I342" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K342" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="343" ht="12.8">
@@ -19578,10 +19592,10 @@
         <v>117</v>
       </c>
       <c r="I344" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K344" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="345" ht="12.8">
@@ -19592,10 +19606,10 @@
         <v>118</v>
       </c>
       <c r="I345" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K345" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="346" ht="12.8">
@@ -19606,10 +19620,10 @@
         <v>119</v>
       </c>
       <c r="I346" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K346" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="347" ht="12.8">
@@ -19620,10 +19634,10 @@
         <v>120</v>
       </c>
       <c r="I347" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K347" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="348" ht="12.8">
@@ -19634,10 +19648,10 @@
         <v>121</v>
       </c>
       <c r="I348" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K348" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="349" ht="12.8">
@@ -19645,7 +19659,7 @@
         <v>86</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" ht="12.8">
@@ -19656,10 +19670,10 @@
         <v>122</v>
       </c>
       <c r="I350" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K350" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="351" s="9" customFormat="1" ht="12.8">
@@ -20181,7 +20195,7 @@
         <v>128</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="355" ht="12.8">
@@ -20192,7 +20206,7 @@
         <v>86</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" ht="12.8">
@@ -20470,10 +20484,10 @@
         <v>123</v>
       </c>
       <c r="I358" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K358" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="359" ht="12.8">
@@ -20738,7 +20752,7 @@
         <v>128</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="362" ht="12.8">
@@ -20749,7 +20763,7 @@
         <v>86</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" ht="12.8">
@@ -20774,11 +20788,11 @@
         <v>124</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J364" s="4"/>
       <c r="K364" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
@@ -21035,10 +21049,10 @@
         <v>125</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K365" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="366" ht="12.8">
@@ -21049,10 +21063,10 @@
         <v>126</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K366" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
@@ -21309,10 +21323,10 @@
         <v>127</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K367" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="368" ht="32.8">
@@ -21323,10 +21337,10 @@
         <v>128</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K368" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="369" ht="53.7">
@@ -21337,10 +21351,10 @@
         <v>129</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K369" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="370" ht="32.8">
@@ -21351,10 +21365,10 @@
         <v>130</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K370" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="371" ht="12.8">
@@ -21365,10 +21379,10 @@
         <v>131</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K371" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="372" ht="12.8">
@@ -21379,10 +21393,10 @@
         <v>132</v>
       </c>
       <c r="I372" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K372" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="373" ht="12.8">
@@ -21393,10 +21407,10 @@
         <v>133</v>
       </c>
       <c r="I373" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K373" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="374" ht="12.8">
@@ -21407,10 +21421,10 @@
         <v>134</v>
       </c>
       <c r="I374" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K374" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="375" ht="43.25">
@@ -21421,10 +21435,10 @@
         <v>135</v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K375" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="376" ht="12.8">
@@ -21435,10 +21449,10 @@
         <v>136</v>
       </c>
       <c r="I376" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K376" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="377" ht="12.8">
@@ -21449,10 +21463,10 @@
         <v>137</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K377" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="378" ht="12.8">
@@ -21463,10 +21477,10 @@
         <v>138</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K378" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="379" ht="12.8">
@@ -21482,7 +21496,7 @@
         <v>134</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="381" ht="22.35">
@@ -21496,10 +21510,10 @@
         <v>139</v>
       </c>
       <c r="I381" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K381" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="382" ht="12.8">
@@ -21542,7 +21556,7 @@
         <v>86</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="387" ht="12.8">
@@ -21565,11 +21579,11 @@
         <v>140</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J388" s="4"/>
       <c r="K388" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
@@ -21823,10 +21837,10 @@
         <v>141</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K389" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="390" ht="12.8">
@@ -21834,10 +21848,10 @@
         <v>142</v>
       </c>
       <c r="I390" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K390" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L390" s="1"/>
       <c r="M390" s="1"/>
@@ -22091,10 +22105,10 @@
         <v>143</v>
       </c>
       <c r="I391" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K391" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="392" ht="12.8">
@@ -22102,10 +22116,10 @@
         <v>144</v>
       </c>
       <c r="I392" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K392" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="394" ht="12.8">
@@ -22647,7 +22661,7 @@
         <v>128</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="403" ht="12.8">
@@ -22655,7 +22669,7 @@
         <v>86</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" s="9" customFormat="1" ht="12.8">
@@ -22935,11 +22949,11 @@
         <v>145</v>
       </c>
       <c r="I406" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J406" s="4"/>
       <c r="K406" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L406" s="1"/>
       <c r="M406" s="1"/>
@@ -23196,10 +23210,10 @@
         <v>146</v>
       </c>
       <c r="I407" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K407" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L407" s="1"/>
       <c r="M407" s="1"/>
@@ -23456,10 +23470,10 @@
         <v>147</v>
       </c>
       <c r="I408" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K408" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L408" s="1"/>
       <c r="M408" s="1"/>
@@ -23716,10 +23730,10 @@
         <v>148</v>
       </c>
       <c r="I409" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K409" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="410" ht="74.6">
@@ -23730,10 +23744,10 @@
         <v>149</v>
       </c>
       <c r="I410" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K410" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="411" ht="12.8">
@@ -23744,10 +23758,10 @@
         <v>150</v>
       </c>
       <c r="I411" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K411" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="412" ht="12.8">
@@ -23758,10 +23772,10 @@
         <v>151</v>
       </c>
       <c r="I412" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K412" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="413" ht="12.8">
@@ -23772,10 +23786,10 @@
         <v>152</v>
       </c>
       <c r="I413" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K413" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="414" ht="12.8">
@@ -23786,10 +23800,10 @@
         <v>153</v>
       </c>
       <c r="I414" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K414" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="415" ht="12.8">
@@ -23797,7 +23811,7 @@
         <v>86</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="416" ht="12.8">
@@ -24339,10 +24353,10 @@
         <v>154</v>
       </c>
       <c r="I420" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K420" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="421" ht="12.8">
@@ -24350,10 +24364,10 @@
         <v>155</v>
       </c>
       <c r="I421" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K421" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="422" ht="12.8">
@@ -24369,7 +24383,7 @@
         <v>128</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="424" ht="12.8">
@@ -24393,10 +24407,10 @@
         <v>156</v>
       </c>
       <c r="I427" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K427" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="429" ht="12.8">
@@ -24407,10 +24421,10 @@
         <v>157</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K429" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="430" ht="12.8">
@@ -24421,10 +24435,10 @@
         <v>158</v>
       </c>
       <c r="I430" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K430" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="432" ht="12.8">
@@ -24464,10 +24478,10 @@
         <v>159</v>
       </c>
       <c r="I436" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K436" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="437" ht="12.8">
@@ -24483,7 +24497,7 @@
         <v>128</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="439" ht="12.8">
@@ -24510,10 +24524,10 @@
         <v>160</v>
       </c>
       <c r="I442" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K442" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="443" ht="12.8">
@@ -24524,10 +24538,10 @@
         <v>161</v>
       </c>
       <c r="I443" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K443" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="444" ht="12.8">
@@ -24538,10 +24552,10 @@
         <v>162</v>
       </c>
       <c r="I444" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K444" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="446" ht="12.8">
@@ -24581,10 +24595,10 @@
         <v>163</v>
       </c>
       <c r="I450" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K450" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="451" ht="32.8">
@@ -24592,10 +24606,10 @@
         <v>164</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K451" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="452" ht="12.8">
@@ -24603,10 +24617,10 @@
         <v>165</v>
       </c>
       <c r="I452" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K452" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="453" ht="12.8">
@@ -24622,10 +24636,10 @@
         <v>166</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K454" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="456" ht="12.8">
@@ -24633,10 +24647,10 @@
         <v>167</v>
       </c>
       <c r="I456" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K456" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="457" ht="12.8">
@@ -24644,10 +24658,10 @@
         <v>168</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K457" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="460" ht="12.8">
@@ -24655,7 +24669,7 @@
         <v>86</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="461" ht="12.8">
@@ -24663,10 +24677,10 @@
         <v>169</v>
       </c>
       <c r="I461" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K461" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="462" s="9" customFormat="1" ht="12.8">
@@ -24937,7 +24951,7 @@
         <v>128</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="464" ht="12.8">
@@ -24948,7 +24962,7 @@
         <v>86</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K464" s="1"/>
       <c r="L464" s="1"/>
@@ -25983,10 +25997,10 @@
         <v>170</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K469" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L469" s="1"/>
       <c r="M469" s="1"/>
@@ -26243,10 +26257,10 @@
         <v>171</v>
       </c>
       <c r="I470" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K470" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="471" ht="12.8">
@@ -26257,10 +26271,10 @@
         <v>172</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K471" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="472" ht="12.8">
@@ -26271,10 +26285,10 @@
         <v>173</v>
       </c>
       <c r="I472" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K472" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="473" ht="12.8">
@@ -26285,10 +26299,10 @@
         <v>174</v>
       </c>
       <c r="I473" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K473" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="474" ht="12.8">
@@ -26299,10 +26313,10 @@
         <v>175</v>
       </c>
       <c r="I474" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K474" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="476" ht="12.8">
@@ -26310,7 +26324,7 @@
         <v>102</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" ht="12.8">
@@ -26318,7 +26332,7 @@
         <v>128</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="478" ht="12.8">
@@ -26326,7 +26340,7 @@
         <v>86</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="480" s="9" customFormat="1" ht="12.8">
@@ -26606,11 +26620,11 @@
         <v>176</v>
       </c>
       <c r="I481" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J481" s="4"/>
       <c r="K481" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L481" s="1"/>
       <c r="M481" s="1"/>
@@ -26867,10 +26881,10 @@
         <v>177</v>
       </c>
       <c r="I482" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K482" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L482" s="1"/>
       <c r="M482" s="1"/>
@@ -27971,7 +27985,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" ht="12.8">
@@ -27979,7 +27993,7 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" ht="12.8">
@@ -27987,12 +28001,12 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" ht="12.8">
@@ -28034,7 +28048,7 @@
         <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -28551,10 +28565,10 @@
     </row>
     <row r="21" ht="12.8">
       <c r="I21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" ht="12.8">
@@ -28810,15 +28824,15 @@
         <v>128</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" ht="12.8">
       <c r="I25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" ht="12.8">
@@ -28871,7 +28885,7 @@
         <v>86</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -29388,10 +29402,10 @@
     </row>
     <row r="39" ht="12.8">
       <c r="I39" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" ht="12.8">
@@ -29681,7 +29695,7 @@
         <v>86</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -30445,13 +30459,13 @@
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K54" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="55" ht="12.8">
@@ -30713,13 +30727,13 @@
         <v>2</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K56" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="57" ht="64.15">
@@ -30727,13 +30741,13 @@
         <v>3</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K57" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="58" ht="12.8">
@@ -30749,13 +30763,13 @@
         <v>4</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K59" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="60" ht="32.8">
@@ -30763,13 +30777,13 @@
         <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K60" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="61" ht="22.35">
@@ -30777,13 +30791,13 @@
         <v>6</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K61" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="62" ht="12.8">
@@ -30799,13 +30813,13 @@
         <v>7</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K63" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="64" ht="53.7">
@@ -30813,13 +30827,13 @@
         <v>8</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K64" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="65" ht="22.35">
@@ -30827,13 +30841,13 @@
         <v>9</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K65" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="66" ht="43.25">
@@ -30841,13 +30855,13 @@
         <v>10</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K66" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="68" ht="12.8">
@@ -30894,7 +30908,7 @@
         <v>86</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -31658,13 +31672,13 @@
         <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K82" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="83" ht="12.8">
@@ -31926,13 +31940,13 @@
         <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K84" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86" ht="12.8">
@@ -31985,7 +31999,7 @@
         <v>86</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -32247,10 +32261,10 @@
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K99" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="100" ht="43.25">
@@ -32258,10 +32272,10 @@
         <v>12</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K100" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="101" ht="22.35">
@@ -32269,10 +32283,10 @@
         <v>13</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K101" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="102" ht="12.8">
@@ -32288,10 +32302,10 @@
         <v>14</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K103" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="104" ht="32.8">
@@ -32299,10 +32313,10 @@
         <v>15</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K104" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="105" s="9" customFormat="1" ht="22.35">
@@ -32317,11 +32331,11 @@
         <v>16</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
@@ -32574,10 +32588,10 @@
         <v>17</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -32838,10 +32852,10 @@
         <v>18</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -33102,10 +33116,10 @@
         <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K110" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="111" ht="32.8">
@@ -33113,10 +33127,10 @@
         <v>20</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K111" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="112" ht="32.8">
@@ -33124,10 +33138,10 @@
         <v>21</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K112" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="113" ht="22.35">
@@ -33135,10 +33149,10 @@
         <v>22</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K113" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="114" ht="32.8">
@@ -33146,10 +33160,10 @@
         <v>23</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K114" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="115" ht="32.8">
@@ -33157,10 +33171,10 @@
         <v>24</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K115" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L115" s="1"/>
     </row>
@@ -33169,10 +33183,10 @@
         <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K116" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="117" ht="12.8">
@@ -33188,10 +33202,10 @@
         <v>26</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K118" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="119" ht="32.8">
@@ -33199,10 +33213,10 @@
         <v>27</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K119" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="120" ht="32.8">
@@ -33210,10 +33224,10 @@
         <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K120" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="121" ht="32.8">
@@ -33221,10 +33235,10 @@
         <v>29</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K121" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="122" ht="32.8">
@@ -33232,10 +33246,10 @@
         <v>30</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K122" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="123" ht="12.8">
@@ -33267,7 +33281,7 @@
         <v>86</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -33526,7 +33540,7 @@
     </row>
     <row r="128" ht="12.8">
       <c r="D128" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" ht="12.8">
@@ -34322,7 +34336,7 @@
         <v>86</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
@@ -34581,7 +34595,7 @@
     </row>
     <row r="143" ht="12.8">
       <c r="D143" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" ht="12.8">

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="index" sheetId="1" r:id="rId3"/>
-    <sheet name="mono" sheetId="2" r:id="rId4"/>
-    <sheet name="fiama" sheetId="3" r:id="rId5"/>
+    <sheet name="index" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="mono" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="fiama" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="491">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -497,7 +497,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Unaware of what was yet to come
@@ -507,7 +507,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">we gazed at flames of the bonfire
@@ -517,7 +517,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">waiting patiently for the dawn to break.</t>
@@ -1809,805 +1809,6 @@
   </si>
   <si>
     <t xml:space="preserve">endroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">宫廷会议</t>
-  </si>
-  <si>
-    <t xml:space="preserve">迷之少女</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利拉的本事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">莱姆·伊德之梦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳木堡之主</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(test)柳木堡之主2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(test)分别</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(test)背叛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(test)尼米尔之丘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结局</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工作人员表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对现在而言早已被遗忘的过去…
-这颗星球的大地上埋没着许多文明的残骸
-在莱姆·伊德文明的伤痕未愈便迎来的第十一纪
-有一段关于西埃尔·泰尔文明的故事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">沙漠古帝国的战火蔓延到各地
-给世界带来了长期的混乱。
-在西大陆，失去了萨伊拉飞艇的帝国
-开始慢慢撤退
-长达十年的战争迎来了终结。
-人类庆祝着他们获得的第一次胜利与和平
-恢复了过去的生活。
-但是，他们没有忘记艾莱亚在这场大战中的背叛，
-因为他们选择了观望。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">而后，近十五年的岁月过去了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">时间流逝…
-和前往米西利亚的商队搭伙旅行的你
-听到了一些让人不安的传闻
-这让你预感又将有一股暗中涌动的力量再次逼近西之地。
-旅行即将结束的某一天晚上
-你被神秘的光芒所吸引
-踏进了古老的森林。
-你不断向着森林的深处前进，遇到了颜色越来越浓的蓝色瘴气
-随之你感到意识愈渐模糊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">醒过来了吗？
-还是先躺着比较好。你之前失去了意识。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能在无力回天之前被发现算你幸运。人类踏进艾莱亚的森林可不算明智。特别是在这树木喧嚣的大风之夜。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…为了把倒在森林里的你搬到这里，我们也只好选择停下急迫的旅程在这里停留一晚了。这倒不是在和你抱怨什么，毕竟我那位很难伺候的同伴对这次意外的休息机会还感到挺满意的。
-你是旅行者吗？为什么要去米西利亚？
-…算了，我还是不多问了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在你该好好睡觉。毕竟人只有在真正需要休息的时候才能得到平静。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是的…这就是我们故事的开始。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阿什和往常一样嘴上不饶人
-但他其实比我更加享受
-你无意中带给我们的休息时间。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">米西利亚的命运，
-世界的真相，我们的抉择
-伊尔瓦将因此留下难以磨灭的伤痕…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">然而此时的我们对将要发生的事还一无所知
-我们望着篝火的火焰
-静静地等待着天亮。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，我们神秘的客人终于醒来了。
-我把粥放在了篝火旁。虽然已经完全凉了。
-…填饱肚子之后就来找我们吧。我有话跟你说。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 米西利亚宫廷 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喂，这个会议要持续到什么时候？我们到底要讨论什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贝里希，你又有诗兴了？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…自从15年前的战争以来，米西利亚始终在困境中徘徊。我们的土地不仅遭到战争摧残，还被神秘的瘟疫所侵袭。食物和资金都在日益枯竭。国内纠纷不断，贵族间的不和愈演愈烈，连未来有望的乔南公爵的继承人也突然失去了音讯。
-加之人类普遍在战后对艾莱亚萌生了反感。这让提倡两族融合的米西利亚在提里斯各国之中的立场变得十分尴尬。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">更严重的是，帝国为了向米西利亚复仇，已经又在建造新的飞艇了。
-对于今后该如何是好这个问题，根本无法通过讨论得出答案。现在我们光是处理自己领地的问题就已经忙得不可开交了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你还是那么认真啊，梅尔文。
-总之，我们就像身处一条奶酪一样的船上，四处是洞。现在所做的讨论，无异于是在悠闲地商量该先堵住哪个洞。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那边的小鬼们，从刚才开始就在嘀嘀咕咕什么呢？
-还有你，贝里希，你把乐器带到宫廷会议上是怎么回事！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我就是觉得，或许可以在这唱一首歌。说不定能让你们刻板的脑袋变得灵活些。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贝里希，你说什么…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">别那么上火，卡多恩。其实正如贝里希所说，像这样的会议什么都决定不了。
-我有点儿小事，先走了。起来，艾露米纳雷。要走了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…啊，是，埃夫隆德大人！对不起。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…那小姑娘怎么回事？站着睡着了吗？
-就算她是少主的随从，在这里睡着也实属不敬。少主他也真是，竟不拿米西利亚的头等大事当回事。……哎，这个国家究竟怎么了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 米西利亚宫廷花园 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你在磨蹭什么，艾露米纳雷。照你的步调走天就要黑了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">且慢，埃夫隆德。我有话要和你说。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这不是父亲大人吗。您这是从那无聊的会议中溜出来赏花了吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">别耍贫嘴埃夫隆德，这就是那位姑娘吗。
-姑娘，你叫什么名字？在宫廷生活可有什么不便？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我叫艾露米纳雷，陛下。宫廷的生活与孤儿院的生活没有太大的差别。我只是跟着埃夫隆德大人……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…有劳你了。不过你偶尔也会想独自清静一下吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈哈！您可真会开玩笑啊，父亲大人。
-您又不是不知道有过村子因为有人吓唬梦现之子而毁灭的事情。别看她这样，她其实胆小得要命。我根本不敢让她有一刻她离开我的视线。唉，如果她能有已故的芙莉亚乌涅大人一半美丽，这起码也算个享受啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所以说，梦现之子的力量…算是研究成功了吗。
-…真是让人难以相信啊。尽管我知道这是种不可饶恕的罪孽，却还是把一切都交给了你们，不，是交给了你。
-只要掌握了这股人类从未有过的力量作为工具，米西利亚的人民就有办法得救了吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工具？父亲您可不要误会了。
-我做这研究既不是为了人类，也不是为了米西利亚。一切都是为了艾露米纳雷和她的同胞们，为了让她们在即将到来的苦难时代中能生存下去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">父亲确实是把「诅咒」强加给了我们，然后哥哥就因此卑怯地逃跑了。但我不这么认为，我会改变一切，包括把您所认为的诅咒变成祝福。
-父亲大人您自己多保重吧，我还有事就先告辞了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇，梅尔文大人！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇，太棒了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">女士们，稍安勿躁啊，你们都挡在这里，这路还怎么让别人走。
-啊，那位女士，请不要推搡。请把路让一让！
-…啊，贝里希，你来的可正是时候。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">梅尔文，你身边总是这么热闹啊。真巧，今天我正带来了新曲，也能请女士们欣赏一下了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊呀呀ー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…那么多女士，一眨眼就不见了。喂，梅尔文，我的歌有那么糟糕吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是啊…呃，不是。总之多谢你了。
-至于你的歌…我觉得演奏的部分还是不错的。我妹妹也和我说过，你们刚生的孩子在听到你的莱雅琴演奏后就会忘记哭泣安然入梦。要按她的评价来说，只要你不张嘴，人们都会以为是有艾莱亚在进行一场绝美的演奏。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…喂喂，你这莫不是在损我？算了，就当作是在夸我好了。
-那这么说来我最爱妻子还是很有品味的，能够听得出我这得到赛特拉斯公爵真传的琴技水平不凡。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你的莱雅琴是赛特拉斯大人教的？我怎么没听说过？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">倒也没什么特别值得一说的。
-你也知道，我以前是泽纳恩那边的人，因为做了些蠢事，在10年前逃亡到了米西利亚这边来。那时的我只懂舞刀弄剑的，加上人生地不熟，日子也不好过。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后来有一天，我在酒馆机缘巧合的遇到了一位弹着莱雅琴的男子。当然，我那时候并不知道他就是赛特拉斯大人。
-只是看大伙都觉得他那样玩弄乐器很优雅，就嘲讽说「乐器是给女人和孩子玩的东西」。后来你猜怎么着，他既不生气也不反驳，而是在看过我一眼后，没把我当回事的自顾自的演奏起了一曲泽纳恩的牧歌。
-然后我就…哎，算了，不跟你说了。后来的事就任你想象吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…对我们米西利亚人来说，赛特拉斯大人是一位让人感到亲近信任的慈祥父亲，也是一位让人不敢抬头直视的严厉老师。毕竟他已经守护了这个国家100多年。我看就算是你，也赢不过赛特拉斯大人吧。
-说起来，后来从人们口中得知你不练习剑术，而是跑到郊外的山丘上一个人练莱雅琴的时候，大家还以为你是爱上了哪个女人呢。不知不觉时间又过去那么久，现在看惯了你背着莱雅琴的样子，反而觉得这样才像你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你只顾着玩音乐，害我都找不到练剑的对手了。真怕你的武艺都生疏了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我自己也没想到，可能比刀剑，演奏才更符合我的性格。
-不过我明白你的担心。现在的米西利亚阴云密布，也许确实是时候该把乐器放回柜子里去了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我喜欢米西利亚这个地方。
-虽然最开始在这里生活的那段日子里，人们看到我这么个大个子在扛着乐器四处走动都会笑话我，但后来米西利亚终究是接受了无家可归又性格偏激的我。不仅如此，我还在这里找到了毕生的挚友和美丽的妻子，有了个吵闹的秃头老丈人，每天的日子都变得热闹得很啊。
-让那又小又穷的泽纳恩吃屎去吧！我，我要为我好不容易找寻到的故乡献出我的心脏。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…虽然算是借着酒劲说出来的话吧。但你能有这样的觉悟，是谁都会高看你一眼的。
-好了，你该回家了。小心别醉醺醺地在你家小宝宝面前唱歌，我妹妹会杀了你的！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵，既然石化植物的根都侵蚀到了这种地方。看来前面确实是会有以太结晶。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对这还满意么，加拉斯卿？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不枉我特意来一趟。不过与沙漠地下广阔的魔石群相比，这儿只算少的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我听说建造萨伊拉飞艇会需要大量的魔石。你会来到这里，是不是因为只靠那丰富的沙漠地下资源也不够安心呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">勘察魔石的确是目的之一。但是来提里斯边境这个因缘之地的理由不仅于此。
-那场令人难忘的恐怖光之风暴…只要照着地图看，就能知道最初看到到光的地方和这个「风之墓地」所在的位置一样。这不是有些太巧了吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…米西利亚的奇迹。你是说摧毁了萨伊拉无敌飞船的风暴与尼米尔的魔石有关…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵……这确实是个值得和加拉斯卿深入探讨的设想。
-不过我们这里似乎来了一位不速之客。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，看起来不过是个冒险者而已。
-不是什么问题。让我们帝国的魔像来收拾吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，完成向导任务的我也是时候离开了。加拉斯卿，请不要忘记我们约好的事情。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷…喂，艾露米纳雷，你又睡着了吗？该走了，你这个拖拖拉拉的家伙！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…对、对不起，埃夫隆德大人！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了，我确实也很好奇一个冒险者来到「风之墓地」的深层是想干什么，但不巧的是我要先去前面。
-别客气，来和我的魔像们一起跳舞吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">从能记事时起，我就能听到森林的「声音」。
-我总是依偎在古老森林的大树旁，听着树木的歌声。因为森林的歌声让我回想起逝去的母亲。
-引导我来到这里的也是森林的声音。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…尼米尔的地底居然有这样的地方呢。
-但是…我明白。这个「森林」的生命已经迎来终结，只是慢慢地在等待枯萎。
-不管曾有过什么，阿什期待的东西已经不在这里了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在对现在而言早已被遗忘的过去
-古代文明莱姆·伊德发现了“它”。
-“它”被称为「永远闪耀之物」
-也有着寄宿死者思念之光、注满星辰之泪、玛那…
-又或是“以太”这样的名字。
-那是能将事物应有模样进行记忆、再生、融合
-的灵魂之泉。
-没过多久它就渗透了人类的世界
-也改变了莱姆·伊德的文明。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是，醉心于以太的莱姆·伊德
-和星球一起走上了灭亡的道路。
-因以太引起的纷争连绵不断
-让大地深受伤害，让天空被阴云覆盖。
-最终，以太的枯竭
-让生态环境变成了人类无法居住的状态。
-永远的冬天到来了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">只有「不死的大树」在冬天幸存下来。
-大树孕育了森林，森林不久孕育了生命。
-那片森林被称为温戴尔。
-那森林中树木产生的蓝光树粉
-在风中飞舞，直通云霄。
-那是星球净化和再生的开始。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…西埃尔·泰尔的时代就这样从星球再生的约定中开始了。但是，温戴尔的风已经停了数百年。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">巨大的…飞蛾？
-…我是在做梦吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然是人类却能听到我的声音吗，森林的女儿啊，我的名字是欧涅芙。是不死大树的伴侣，始源的存在，在伊尔瓦生灵们的母亲。
-在你面前的水晶，或者被称为魔石的结晶，是上古时代树木与以太融合石化而成的。那魔石隐藏着巨大的力量。
-…然而在经过漫长岁月之后释放这种力量的方法却遗失了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是，距今20年前，一个艾莱亚人释放了尼米尔魔石的力量，唤来了狂风。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…尼米尔的狂风。魔石回应了赛特大人的祈祷。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那风是伊尔瓦长年期待的以太风的先兆。「无风的季节」结束，星球的净化现在又要开始了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">星球的净化…等等，你想说什么？
-我们为了寻求击退帝国侵略的力量来到了这里。但是，这片森林的魔石已经枯竭。我们无法阻止萨伊拉的舰队了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其他地方还有魔石存在。如果你想要力量，就去东南山脉的遗迹利萨纳斯吧。
-还有一件事。只有「风声聆听者」才能释放魔石并呼唤失去的风。去寻找「风声聆听者」吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我不能完全相信你的话。风声聆听者是指赛特大人吗？你为什么要帮助我们？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森林的女儿，脆弱又短命的人类啊，你无法理解我的职责。我必须离开了。
-有一件事你要记得。即使用魔石打败帝国，如果风就此消失了的话，等待西埃尔·泰尔的是终极的失败。
-聆听森林之声的女儿啊，愿你得到风的加护。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">等一下！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森之淑女欧涅芙…她到底是…
-不，现在必须尽快回到据点，向阿什报告。
-好了，我们走吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 米西利亚的街道上 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没想到会在这里待这么久。那个旅人居然会如此热心地进行开拓。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你看上去没有精神啊，菲亚玛。从尼米尔回来之后就一直都是这这副样子。
-…没事吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，对不起，让你担心了。在那之后我每天晚上都会梦见莱姆·伊德。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">莱姆·伊德的梦？什么内容？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">尼米尔腐朽的魔石让我看到古代的记忆，看到了曾经存在于伊尔瓦名为莱姆·伊德的文明一步步走向终结的轨迹。
-他们有着比我们更先进的文明。但是，他们被以太的力量所吸引，走上了灭亡的道路。围绕以太的人类之间的争斗不断，大地枯萎，弱者被凌虐…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是有什么奇怪的吗？据我所知，人类在任何时代都是这样的。
-我们永远被两种感情所支配。恐惧和欲望。只要有两人以上的地方就一定会有争端。历史教我们用过去的悲剧来约束欲望，但我从未见过成功的先例。
-我们不会改变。莱姆·伊德的人民也是人类。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你还是那么爱讽刺啊…对，人类是不会改变的。谈到这点让我心情忧郁。无论我们做什么事，无论把什么留在世界上，人的丑陋和残酷都不会改变。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想成为赛特大人的助力。米西利亚也许还能得救……但是，人类总有一天会再次开始干涉艾莱亚的。
-我有一种不好的预感，也许会有更大的不幸在等着赛特大人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">菲亚…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我也不明白。
-虽然想说点漂亮话出来，但我早就放弃自己，放弃一切了。可能只要不对世界抱有期待，也就不会感到失望了吧。不管发生什么，我只是要保护赛特拉斯大人而已。
-不过，也不是没办法让世界变成你所期望的样子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">办法？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">只要让人类都灭亡，只剩下艾莱亚不就好了。这样一来世界就会和争斗、迫害都无缘，变得和平。不，或许说最初时我们不出生就好了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开玩笑的，菲亚。你别那么吓人好不好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我没有生气。只是有些东西让我心烦。因为你的「办法」听起来太完美了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼，旅途遥远我们一定都累了。
-来，走吧。我们需要一张舒适松软的床。而且，如果在天黑之前到达柳木堡的厨房的话，可能还会有热乎乎的派吃呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">显示测试</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（以太流中共享了艾露米纳雷记忆的菲亚玛
-以第一人称讲述艾露米纳雷回忆的场面）
-（菲亚玛自我的边界变得模糊）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我躺在古老森林的一棵大树下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这…不是我的记忆吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这一定是我在以太流中看到的那个女孩的记忆。
-艾露米纳雷的重要记忆。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我躺在古老森林的一棵大树下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（被埃夫隆德拯救的艾露米纳雷的描写）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">埃夫隆德的部下一个个倒下。
-周围已经只有敌人了（与米西利亚的现状重叠）。
-艾露米纳雷也晕乎乎地打败了几只魔兽，但又倒下了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退下吧，艾露米纳雷。没有必要为了叛徒而战！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈…哈…对不起，埃夫隆德大人…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">像蝎狮一样的东西想要袭击两人，死亡就在眼前。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看来到此为止了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">埃夫隆德紧紧抱住艾露米纳雷。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">埃夫隆德大人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵，你还是那么懒惰。这种时候还想睡觉吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不，埃夫隆德大人。我不困。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我还想再看看这个世界。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…！(醒了过来）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(艾露米纳雷的身体被青色的光包围）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷的力量解放了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…埃夫隆德大人！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是…怎么回事？
-有人和艾露米纳雷产生共鸣，把她的力量唤了回来。虽然那个人不是我。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这种感觉…是菲亚玛，那个女孩吗！
-…对了，尼米尔的山丘…那个时候我也感觉到了。除了我以外谁的存在。菲亚玛有唤醒者的能力吗？但是，她到底是怎么得到那个资格的呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-艾露米纳雷歼灭了蝎狮和周围敌人。
-不久后两人周围就没有能动的东西了，艾露米纳雷跪了下来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷虽然已经停止了战斗，但无法阻止自己失控的力量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊…啊…埃夫隆德大人…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么了，艾露米纳雷。已经没有敌人了。控制住「力量」。不然的话你就会……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无法控制。是除了我们以外的人…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不能切断和那个女孩的共鸣吗！
-菲亚玛，快停止艾露米纳雷的力量！给我住手！听不见吗，可恶！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对不起，埃夫隆德先生…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷对埃夫隆德微笑。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">掉在地上的艾露米纳雷的向前跪下，握着埃夫隆德的手。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（从这里开始是菲亚玛的独白）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当赛特拉斯的士兵发现他时
-周围没有其他能动的东西。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">他双手握住一个被扯断了的少女的手臂，蹲在地上。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在这场战斗中失去大部分主战斗力的泽纳恩开始撤退。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贝里希失踪了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 孤儿院地下 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">表现·测试效果。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼唤风吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风不是属于我的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">埃夫隆德诱导着梦现之子们进行迎击，但却遭到了激烈的炮火。埃夫隆德此时作为唤醒者还不成熟，无法激发艾露米纳雷的力量。埃夫隆德将其归咎于艾露米纳雷而叫骂。一边与从萨伊拉的飞艇上飞来的魔导兵交战，一边看着孩子在炮火中被炸飞，目睹恶心场面的艾露米纳雷呕吐了起来。随着艾露米纳雷力量的失控，周围陷入混乱。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我知道。但是那个时候芙琳呼唤了风。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（询问菲亚玛当时有没有记忆）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那时候我…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我因为古老森林大树的影响睡着了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（菲亚玛的回忆描写）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在炮火中不断倒下的梦现之子们。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(恶心）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷！你在干什么，你这个废物！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（帝国的袭击什么的都无所谓了）
-（即使米西利亚灭亡也没关系）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">垃圾们，动起来！
-释放你们的力量。释放一切。
-死了也没关系，毕竟你们「已经」被抛弃了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还有死去的梦现之子们。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我听到了孩子们的呼喊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（在以太流中听到艾露米纳雷的叫声）
-（艾露米纳雷和其他梦现之子们的各种感情、恐怖、憎恨、绝望等涌现了过来）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（菲亚玛被以太的洪流吞噬了）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（沉浸在以太洪流中即将迷失自我时、听到了少女的声音）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（少女问哭泣的菲亚玛想做什么。）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（被梦现之子们的感情支配的菲亚玛希望复仇和破坏）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（菲亚玛的强烈的意志成为导火索，与少女产生共鸣）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（起身）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空气……在颤动…
-…什么，这蓝色的鳞粉是什么？发生了什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">噫</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾露米纳雷快退后！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">尼米尔上空有一条光柱。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蓝色闪耀的风化为风暴袭击了萨伊拉的飞艇。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼唤风的是…我…不，是梦中的少女。我唤醒了「什么」？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风声聆听者</t>
-  </si>
-  <si>
-    <t xml:space="preserve">稍微聊聊我自己的故事吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我诞生在米西利亚的一个小村里。
-母亲在我记事前就去世了
-酒鬼父亲每天都对我暴力相向。
-村子里的孩子们排挤我
-同父异母的兄弟也把我当外人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在那个村子里的时候，我恐怕从未露出过笑容。
-即使后来长大学会了如何保护自己
-我和世界之间筑起的高墙也没有消失。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">十年战争结束的时候，我才刚满8岁后不久
-那时，村庄遭到了瘟疫的侵袭。
-我的父亲病死后
-哥哥们就离开家乡去了米西利亚的都城。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">剩下孤身一人被留下的我，只能一边饿着肚子
-一边幸福的看着
-父亲那丑陋的身体日渐腐烂。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…和赛特大人的邂逅
-就是在那时的一个冬夜。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">山丘之上有座柳木堡，
-城堡的主人就是艾莱亚的领主，赛特拉斯公爵。
-在村中肮脏的酒馆里见到他时，
-他正在轻快地演奏羚羊角的莱雅琴。
-若有孩子们在
-他就会唱起古老的艾莱亚故事和童话。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公爵是个爱笑的人，柳木堡的居民都爱戴他。
-所以
-当他靠近无家可归的我时
-我没有任何恐惧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">他牵着我的手
-向着柳木堡中温暖的厨房去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们无言地走在通往城堡的夜路上。
-他握着我的手
-从未松开。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(在柳木堡。Coming Soon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-就这样我们漫长的战斗结束了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">沉睡在芙琳大人腹中的梦现之子
-「风声聆听者」呼唤而来的以太风
-呼啸地掠过米西利亚全境
-将萨伊拉的舰队和帝国军全部击垮。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无数的牺牲
-给伊尔瓦留下了深深的伤痕。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在那之后，失去意识的赛特大人被搬到了柳木堡的废屋中
-我们只能眼睁睁的看着
-米西利亚境内灯火的生机在一天天的减少熄灭。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很快醒来的赛特大人
-变得沉默寡言
-一天里大部分时间都躺在床上度过。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">然后，突然某天
-他从我们面前消失了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">连封信都没有留下
-甚至也没有和他的另一半芙琳大人道别。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">米西利亚的故事，赛特拉斯的故事
-我和柳木堡之主的故事
-就这样迎来了终结。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那之后经过了一年的时间。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我在护送怀孕的芙琳大人前往温戴尔的旅途中
-写下了这个故事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">和米西利亚有关的记忆
-就像是昨天的事情一样
-搅乱了我的心绪。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但即便如此
-我们的脚步却不可思议的轻快。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们围坐在篝火边
-芙琳大人摸着她日渐隆起的肚子
-露出了温柔的微笑。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过
-阿什完全没有注意到这件事。
-这倒也像他。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我也不打算告诉他。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">就算到了现在
-我每天也在想着赛特大人的事情。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳木堡之主
-现在到底在哪里
-又在做些什么呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">他那让两族共存的理想
-是不是已经随着米西利亚的衰败
-一起磨灭了呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">或许
-他的故事
-还没有结束。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">或许
-我们的故事
-还会不断地编织下去。</t>
   </si>
 </sst>
 </file>
@@ -2629,38 +1830,38 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -2685,7 +1886,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -2694,74 +1895,74 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2775,13 +1976,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -2957,20 +2158,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="4" width="8.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26" style="2" customWidth="1"/>
-    <col min="6" max="6" width="62.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2996,7 +2197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3015,11 +2216,8 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" ht="12.8">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3038,11 +2236,8 @@
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="7" ht="12.8">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
@@ -3061,11 +2256,8 @@
       <c r="G7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="8" ht="12.8">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
@@ -3084,11 +2276,8 @@
       <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
@@ -3107,11 +2296,8 @@
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H9" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="10" ht="12.8">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -3130,11 +2316,8 @@
       <c r="G10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H10" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
@@ -3153,11 +2336,8 @@
       <c r="G11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H11" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" ht="12.8">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
         <v>38</v>
       </c>
@@ -3176,11 +2356,8 @@
       <c r="G12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
@@ -3199,11 +2376,8 @@
       <c r="G13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H13" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" ht="12.8">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
@@ -3222,11 +2396,8 @@
       <c r="G14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H14" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="15" ht="12.8">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
@@ -3245,15 +2416,12 @@
       <c r="G15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H15" t="s">
-        <v>502</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -3261,24 +2429,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW492"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="4" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="4" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3313,13 +2481,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>177</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>59</v>
       </c>
@@ -3327,7 +2495,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>61</v>
       </c>
@@ -3335,7 +2503,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>63</v>
       </c>
@@ -3343,7 +2511,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>61</v>
       </c>
@@ -3351,7 +2519,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
         <v>61</v>
       </c>
@@ -3359,7 +2527,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
         <v>61</v>
       </c>
@@ -3367,7 +2535,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
@@ -3375,7 +2543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,7 +2551,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>61</v>
       </c>
@@ -3391,7 +2559,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
@@ -3399,7 +2567,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>61</v>
       </c>
@@ -3407,7 +2575,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>61</v>
       </c>
@@ -3415,7 +2583,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>61</v>
       </c>
@@ -3423,7 +2591,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>61</v>
       </c>
@@ -3431,7 +2599,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>61</v>
       </c>
@@ -3439,7 +2607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>61</v>
       </c>
@@ -3447,7 +2615,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>61</v>
       </c>
@@ -3455,7 +2623,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
         <v>61</v>
       </c>
@@ -3463,7 +2631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>61</v>
       </c>
@@ -3471,7 +2639,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="s">
         <v>61</v>
       </c>
@@ -3479,12 +2647,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" s="5" customFormat="1" ht="12.8">
+    <row r="26" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3743,12 +2911,12 @@
       <c r="IV26" s="1"/>
       <c r="IW26" s="1"/>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="1" ht="12.8">
+    <row r="28" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4011,7 +3179,7 @@
       <c r="IV28" s="1"/>
       <c r="IW28" s="1"/>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
         <v>84</v>
       </c>
@@ -4019,7 +3187,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" s="5" customFormat="1" ht="12.8">
+    <row r="30" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4282,7 +3450,7 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" s="5" customFormat="1" ht="12.8">
+    <row r="31" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4545,7 +3713,7 @@
       <c r="IV31" s="1"/>
       <c r="IW31" s="1"/>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
         <v>85</v>
       </c>
@@ -4800,7 +3968,7 @@
       <c r="IV32" s="1"/>
       <c r="IW32" s="1"/>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
         <v>89</v>
       </c>
@@ -5052,7 +4220,7 @@
       <c r="IV33" s="1"/>
       <c r="IW33" s="1"/>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
         <v>90</v>
       </c>
@@ -5060,8 +4228,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" ht="43.25">
-      <c r="H35" s="1">
+    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -5070,11 +4238,8 @@
       <c r="J35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K35" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="36" ht="12.8">
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
         <v>90</v>
       </c>
@@ -5082,8 +4247,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" ht="126.85">
-      <c r="H37" s="1">
+    <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="6" t="s">
@@ -5092,11 +4257,8 @@
       <c r="J37" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K37" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="1" t="s">
         <v>90</v>
       </c>
@@ -5104,8 +4266,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
-      <c r="H39" s="1">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
         <v>102</v>
       </c>
       <c r="I39" s="6" t="s">
@@ -5114,11 +4276,8 @@
       <c r="J39" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="K39" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="40" ht="12.8">
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
@@ -5129,11 +4288,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" ht="126.85">
+    <row r="41" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
@@ -5142,11 +4301,8 @@
       <c r="J41" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K41" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="1" t="s">
         <v>90</v>
       </c>
@@ -5154,17 +4310,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="1" t="s">
         <v>84</v>
       </c>
@@ -5172,7 +4328,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="1" t="s">
         <v>102</v>
       </c>
@@ -5180,7 +4336,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
@@ -5188,7 +4344,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="1" t="s">
         <v>105</v>
       </c>
@@ -5196,7 +4352,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
@@ -5204,7 +4360,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="1" t="s">
         <v>109</v>
       </c>
@@ -5212,7 +4368,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="1" t="s">
         <v>85</v>
       </c>
@@ -5220,7 +4376,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="1" t="s">
         <v>63</v>
       </c>
@@ -5228,7 +4384,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" ht="12.8">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D53" s="1" t="s">
         <v>113</v>
       </c>
@@ -5236,11 +4392,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" ht="32.8">
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I54" s="6" t="s">
@@ -5249,11 +4405,8 @@
       <c r="J54" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K54" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="55" s="5" customFormat="1" ht="12.8">
+    </row>
+    <row r="55" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5516,7 +4669,7 @@
       <c r="IV55" s="1"/>
       <c r="IW55" s="1"/>
     </row>
-    <row r="56" s="5" customFormat="1" ht="12.8">
+    <row r="56" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -5526,7 +4679,7 @@
         <v>115</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="1">
+      <c r="H56" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -5535,9 +4688,7 @@
       <c r="J56" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>508</v>
-      </c>
+      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
@@ -5785,11 +4936,11 @@
       <c r="IV56" s="1"/>
       <c r="IW56" s="1"/>
     </row>
-    <row r="57" ht="74.6">
+    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F57" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -5798,9 +4949,7 @@
       <c r="J57" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>509</v>
-      </c>
+      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
@@ -6048,11 +5197,11 @@
       <c r="IV57" s="1"/>
       <c r="IW57" s="1"/>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -6061,9 +5210,7 @@
       <c r="J58" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>510</v>
-      </c>
+      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
@@ -6311,7 +5458,7 @@
       <c r="IV58" s="1"/>
       <c r="IW58" s="1"/>
     </row>
-    <row r="59" s="5" customFormat="1" ht="12.8">
+    <row r="59" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -6574,7 +5721,7 @@
       <c r="IV59" s="1"/>
       <c r="IW59" s="1"/>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D60" s="1" t="s">
         <v>102</v>
       </c>
@@ -6582,7 +5729,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="61" ht="12.8">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D61" s="1" t="s">
         <v>63</v>
       </c>
@@ -6837,7 +5984,7 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" ht="12.8">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="1" t="s">
         <v>128</v>
       </c>
@@ -6845,7 +5992,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D63" s="1" t="s">
         <v>107</v>
       </c>
@@ -6853,8 +6000,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" ht="12.8">
-      <c r="H65" s="1">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H65" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I65" s="4" t="s">
@@ -6863,12 +6010,9 @@
       <c r="J65" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="K65" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="66" ht="32.8">
-      <c r="H66" s="1">
+    </row>
+    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -6877,11 +6021,8 @@
       <c r="J66" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="K66" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="67" ht="12.8">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D67" s="1" t="s">
         <v>134</v>
       </c>
@@ -6889,8 +6030,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="35.05">
-      <c r="H68" s="1">
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I68" s="7" t="s">
@@ -6899,12 +6040,9 @@
       <c r="J68" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="K68" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="69" ht="35.8">
-      <c r="H69" s="1">
+    </row>
+    <row r="69" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I69" s="8" t="s">
@@ -6913,11 +6051,8 @@
       <c r="J69" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="K69" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="70" ht="12.8">
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D70" s="1" t="s">
         <v>102</v>
       </c>
@@ -6926,12 +6061,12 @@
       </c>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="72" ht="12.8">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="1" t="s">
         <v>63</v>
       </c>
@@ -6939,7 +6074,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="1" t="s">
         <v>105</v>
       </c>
@@ -6947,7 +6082,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" ht="12.8">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="1" t="s">
         <v>103</v>
       </c>
@@ -6955,7 +6090,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="75" ht="12.8">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D75" s="1" t="s">
         <v>107</v>
       </c>
@@ -6963,7 +6098,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" ht="12.8">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D76" s="1" t="s">
         <v>85</v>
       </c>
@@ -6971,7 +6106,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" ht="12.8">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D77" s="1" t="s">
         <v>86</v>
       </c>
@@ -6979,7 +6114,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D78" s="1" t="s">
         <v>85</v>
       </c>
@@ -6987,7 +6122,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="1" t="s">
         <v>113</v>
       </c>
@@ -6995,11 +6130,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" ht="53.7">
+    <row r="80" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F80" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I80" s="6" t="s">
@@ -7008,31 +6143,28 @@
       <c r="J80" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K80" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="82" ht="12.8">
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D82" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="83" ht="12.8">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D83" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="90" ht="12.8">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D91" s="1" t="s">
         <v>102</v>
       </c>
@@ -7040,7 +6172,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D92" s="1" t="s">
         <v>128</v>
       </c>
@@ -7048,7 +6180,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="93" s="9" customFormat="1" ht="12.8">
+    <row r="93" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7311,7 +6443,7 @@
       <c r="IV93" s="1"/>
       <c r="IW93" s="1"/>
     </row>
-    <row r="94" ht="12.8">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D94" s="1" t="s">
         <v>107</v>
       </c>
@@ -7319,11 +6451,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" ht="12.8">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F95" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H95" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I95" s="4" t="s">
@@ -7332,9 +6464,7 @@
       <c r="J95" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>516</v>
-      </c>
+      <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -7582,11 +6712,11 @@
       <c r="IV95" s="1"/>
       <c r="IW95" s="1"/>
     </row>
-    <row r="96" ht="12.8">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F96" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I96" s="4" t="s">
@@ -7595,15 +6725,12 @@
       <c r="J96" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K96" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="97" ht="12.8">
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F97" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I97" s="4" t="s">
@@ -7612,15 +6739,12 @@
       <c r="J97" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="K97" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="98" ht="105.95">
+    </row>
+    <row r="98" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F98" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I98" s="6" t="s">
@@ -7629,15 +6753,12 @@
       <c r="J98" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="K98" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="99" ht="53.7">
+    </row>
+    <row r="99" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F99" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H99" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I99" s="6" t="s">
@@ -7646,15 +6767,12 @@
       <c r="J99" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="K99" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="100" ht="43.25">
+    </row>
+    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F100" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H100" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I100" s="6" t="s">
@@ -7663,15 +6781,12 @@
       <c r="J100" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K100" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="101" ht="43.25">
+    </row>
+    <row r="101" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F101" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H101" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I101" s="6" t="s">
@@ -7680,15 +6795,12 @@
       <c r="J101" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="K101" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="102" ht="12.8">
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F102" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H102" s="1">
+      <c r="H102" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I102" s="4" t="s">
@@ -7697,15 +6809,12 @@
       <c r="J102" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="K102" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="103" ht="12.8">
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F103" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H103" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I103" s="4" t="s">
@@ -7714,15 +6823,12 @@
       <c r="J103" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="K103" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="104" ht="53.7">
+    </row>
+    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F104" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H104" s="1">
+      <c r="H104" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I104" s="6" t="s">
@@ -7731,15 +6837,12 @@
       <c r="J104" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="K104" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="105" ht="12.8">
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F105" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H105" s="1">
+      <c r="H105" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I105" s="4" t="s">
@@ -7748,11 +6851,8 @@
       <c r="J105" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="K105" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="106" ht="12.8">
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="1" t="s">
         <v>134</v>
       </c>
@@ -7760,11 +6860,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="107" ht="85.05">
+    <row r="107" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F107" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H107" s="1">
+      <c r="H107" s="1" t="n">
         <v>104</v>
       </c>
       <c r="I107" s="6" t="s">
@@ -7773,11 +6873,8 @@
       <c r="J107" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K107" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="108" ht="12.8">
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="1" t="s">
         <v>84</v>
       </c>
@@ -7785,22 +6882,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="109" ht="12.8">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" ht="12.8">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="113" ht="12.8">
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="114" s="5" customFormat="1" ht="12.8">
+    <row r="114" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -8063,7 +7160,7 @@
       <c r="IV114" s="1"/>
       <c r="IW114" s="1"/>
     </row>
-    <row r="115" ht="12.8">
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="1" t="s">
         <v>128</v>
       </c>
@@ -8071,7 +7168,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" ht="12.8">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="1" t="s">
         <v>86</v>
       </c>
@@ -8326,7 +7423,7 @@
       <c r="IV116" s="1"/>
       <c r="IW116" s="1"/>
     </row>
-    <row r="117" ht="12.8">
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="1" t="s">
         <v>107</v>
       </c>
@@ -8334,7 +7431,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="118" s="9" customFormat="1" ht="12.8">
+    <row r="118" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -8344,7 +7441,7 @@
         <v>65</v>
       </c>
       <c r="G118" s="1"/>
-      <c r="H118" s="1">
+      <c r="H118" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I118" s="4" t="s">
@@ -8353,9 +7450,7 @@
       <c r="J118" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K118" s="1" t="s">
-        <v>528</v>
-      </c>
+      <c r="K118" s="1"/>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -8603,11 +7698,11 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" ht="12.8">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F119" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H119" s="1">
+      <c r="H119" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I119" s="4" t="s">
@@ -8616,15 +7711,12 @@
       <c r="J119" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="K119" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="120" ht="12.8">
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F120" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H120" s="1" t="n">
         <v>105</v>
       </c>
       <c r="I120" s="4" t="s">
@@ -8633,9 +7725,7 @@
       <c r="J120" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="K120" s="1" t="s">
-        <v>530</v>
-      </c>
+      <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
@@ -8883,11 +7973,11 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" ht="12.8">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F121" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I121" s="4" t="s">
@@ -8896,15 +7986,12 @@
       <c r="J121" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="K121" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="122" ht="43.25">
+    </row>
+    <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F122" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H122" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I122" s="6" t="s">
@@ -8913,15 +8000,12 @@
       <c r="J122" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="K122" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="123" ht="22.35">
+    </row>
+    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F123" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I123" s="4" t="s">
@@ -8930,15 +8014,12 @@
       <c r="J123" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="K123" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="124" ht="12.8">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F124" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I124" s="4" t="s">
@@ -8947,15 +8028,12 @@
       <c r="J124" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="K124" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="125" ht="85.05">
+    </row>
+    <row r="125" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F125" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="6" t="s">
@@ -8964,15 +8042,12 @@
       <c r="J125" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="K125" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="126" ht="74.6">
+    </row>
+    <row r="126" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F126" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H126" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I126" s="6" t="s">
@@ -8981,15 +8056,12 @@
       <c r="J126" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="K126" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="127" ht="53.7">
+    </row>
+    <row r="127" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F127" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H127" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I127" s="6" t="s">
@@ -8998,15 +8070,12 @@
       <c r="J127" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="K127" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="128" ht="53.7">
+    </row>
+    <row r="128" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F128" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H128" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I128" s="6" t="s">
@@ -9015,15 +8084,12 @@
       <c r="J128" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="K128" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="129" ht="12.8">
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F129" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H129" s="1" t="n">
         <v>34</v>
       </c>
       <c r="I129" s="4" t="s">
@@ -9032,11 +8098,8 @@
       <c r="J129" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K129" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="130" ht="12.8">
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="1" t="s">
         <v>84</v>
       </c>
@@ -9044,22 +8107,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="132" ht="12.8">
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="134" ht="12.8">
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="135" s="5" customFormat="1" ht="12.8">
+    <row r="135" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -9322,7 +8385,7 @@
       <c r="IV135" s="1"/>
       <c r="IW135" s="1"/>
     </row>
-    <row r="136" ht="12.8">
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D136" s="1" t="s">
         <v>128</v>
       </c>
@@ -9330,7 +8393,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="137" ht="12.8">
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D137" s="1" t="s">
         <v>86</v>
       </c>
@@ -9585,7 +8648,7 @@
       <c r="IV137" s="1"/>
       <c r="IW137" s="1"/>
     </row>
-    <row r="138" ht="12.8">
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D138" s="1" t="s">
         <v>107</v>
       </c>
@@ -9593,7 +8656,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" s="9" customFormat="1" ht="12.8">
+    <row r="139" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -9603,7 +8666,7 @@
         <v>65</v>
       </c>
       <c r="G139" s="1"/>
-      <c r="H139" s="1">
+      <c r="H139" s="1" t="n">
         <v>35</v>
       </c>
       <c r="I139" s="4" t="s">
@@ -9612,9 +8675,7 @@
       <c r="J139" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K139" s="1" t="s">
-        <v>516</v>
-      </c>
+      <c r="K139" s="1"/>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
@@ -9862,11 +8923,11 @@
       <c r="IV139" s="1"/>
       <c r="IW139" s="1"/>
     </row>
-    <row r="140" ht="12.8">
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F140" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H140" s="1">
+      <c r="H140" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I140" s="4" t="s">
@@ -9875,15 +8936,12 @@
       <c r="J140" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="K140" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="141" ht="12.8">
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F141" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H141" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I141" s="4" t="s">
@@ -9892,9 +8950,7 @@
       <c r="J141" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="K141" s="1" t="s">
-        <v>540</v>
-      </c>
+      <c r="K141" s="1"/>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
@@ -10142,11 +9198,11 @@
       <c r="IV141" s="1"/>
       <c r="IW141" s="1"/>
     </row>
-    <row r="142" ht="74.6">
+    <row r="142" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F142" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H142" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I142" s="6" t="s">
@@ -10155,15 +9211,12 @@
       <c r="J142" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="K142" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="143" ht="12.8">
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F143" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H143" s="1">
+      <c r="H143" s="1" t="n">
         <v>39</v>
       </c>
       <c r="I143" s="4" t="s">
@@ -10172,15 +9225,12 @@
       <c r="J143" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="K143" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="144" ht="12.8">
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F144" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H144" s="1">
+      <c r="H144" s="1" t="n">
         <v>40</v>
       </c>
       <c r="I144" s="4" t="s">
@@ -10189,11 +9239,8 @@
       <c r="J144" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="K144" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="145" ht="12.8">
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D145" s="1" t="s">
         <v>102</v>
       </c>
@@ -10201,7 +9248,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="146" ht="12.8">
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D146" s="1" t="s">
         <v>128</v>
       </c>
@@ -10209,7 +9256,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="147" ht="12.8">
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D147" s="1" t="s">
         <v>86</v>
       </c>
@@ -10217,7 +9264,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="148" ht="12.8">
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D148" s="1" t="s">
         <v>107</v>
       </c>
@@ -10225,7 +9272,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="149" s="9" customFormat="1" ht="12.8">
+    <row r="149" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -10484,11 +9531,11 @@
       <c r="IV149" s="1"/>
       <c r="IW149" s="1"/>
     </row>
-    <row r="150" ht="12.8">
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F150" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H150" s="1" t="n">
         <v>41</v>
       </c>
       <c r="I150" s="4" t="s">
@@ -10497,15 +9544,12 @@
       <c r="J150" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="K150" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="151" ht="64.15">
+    </row>
+    <row r="151" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F151" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H151" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I151" s="6" t="s">
@@ -10514,9 +9558,7 @@
       <c r="J151" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K151" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
@@ -10764,11 +9806,11 @@
       <c r="IV151" s="1"/>
       <c r="IW151" s="1"/>
     </row>
-    <row r="152" ht="43.25">
+    <row r="152" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F152" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H152" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I152" s="6" t="s">
@@ -10777,15 +9819,12 @@
       <c r="J152" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="K152" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="153" ht="12.8">
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F153" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H153" s="1">
+      <c r="H153" s="1" t="n">
         <v>44</v>
       </c>
       <c r="I153" s="4" t="s">
@@ -10794,15 +9833,12 @@
       <c r="J153" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="K153" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="154" ht="64.15">
+    </row>
+    <row r="154" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F154" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H154" s="1">
+      <c r="H154" s="1" t="n">
         <v>45</v>
       </c>
       <c r="I154" s="6" t="s">
@@ -10811,15 +9847,12 @@
       <c r="J154" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="K154" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="155" ht="64.15">
+    </row>
+    <row r="155" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F155" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H155" s="1">
+      <c r="H155" s="1" t="n">
         <v>46</v>
       </c>
       <c r="I155" s="6" t="s">
@@ -10828,15 +9861,12 @@
       <c r="J155" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="K155" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="156" ht="85.05">
+    </row>
+    <row r="156" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F156" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H156" s="1">
+      <c r="H156" s="1" t="n">
         <v>47</v>
       </c>
       <c r="I156" s="6" t="s">
@@ -10845,15 +9875,12 @@
       <c r="J156" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="K156" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="157" ht="12.8">
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F157" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H157" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I157" s="4" t="s">
@@ -10862,15 +9889,12 @@
       <c r="J157" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="K157" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="158" ht="64.15">
+    </row>
+    <row r="158" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F158" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H158" s="1">
+      <c r="H158" s="1" t="n">
         <v>49</v>
       </c>
       <c r="I158" s="6" t="s">
@@ -10879,15 +9903,12 @@
       <c r="J158" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="K158" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="159" ht="12.8">
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F159" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H159" s="1">
+      <c r="H159" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I159" s="4" t="s">
@@ -10896,15 +9917,12 @@
       <c r="J159" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K159" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="160" ht="95.5">
+    </row>
+    <row r="160" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F160" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H160" s="1">
+      <c r="H160" s="1" t="n">
         <v>51</v>
       </c>
       <c r="I160" s="6" t="s">
@@ -10913,15 +9931,12 @@
       <c r="J160" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="K160" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="161" ht="53.7">
+    </row>
+    <row r="161" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F161" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H161" s="1">
+      <c r="H161" s="1" t="n">
         <v>52</v>
       </c>
       <c r="I161" s="6" t="s">
@@ -10930,11 +9945,8 @@
       <c r="J161" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="K161" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="162" ht="12.8">
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D162" s="1" t="s">
         <v>84</v>
       </c>
@@ -10942,17 +9954,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="163" ht="12.8">
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D163" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="164" ht="12.8">
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="167" s="5" customFormat="1" ht="12.8">
+    <row r="167" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
         <v>235</v>
       </c>
@@ -11213,7 +10225,7 @@
       <c r="IV167" s="1"/>
       <c r="IW167" s="1"/>
     </row>
-    <row r="168" s="5" customFormat="1" ht="12.8">
+    <row r="168" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -11476,7 +10488,7 @@
       <c r="IV168" s="1"/>
       <c r="IW168" s="1"/>
     </row>
-    <row r="169" s="5" customFormat="1" ht="12.8">
+    <row r="169" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -11739,7 +10751,7 @@
       <c r="IV169" s="1"/>
       <c r="IW169" s="1"/>
     </row>
-    <row r="170" ht="12.8">
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D170" s="1" t="s">
         <v>113</v>
       </c>
@@ -11994,7 +11006,7 @@
       <c r="IV170" s="1"/>
       <c r="IW170" s="1"/>
     </row>
-    <row r="171" ht="12.8">
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D171" s="1" t="s">
         <v>86</v>
       </c>
@@ -12249,7 +11261,7 @@
       <c r="IV171" s="1"/>
       <c r="IW171" s="1"/>
     </row>
-    <row r="172" ht="12.8">
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D172" s="1" t="s">
         <v>237</v>
       </c>
@@ -12257,7 +11269,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="173" ht="12.8">
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D173" s="1" t="s">
         <v>85</v>
       </c>
@@ -12265,11 +11277,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="174" ht="12.8">
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F174" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H174" s="1">
+      <c r="H174" s="1" t="n">
         <v>53</v>
       </c>
       <c r="I174" s="4" t="s">
@@ -12278,15 +11290,12 @@
       <c r="J174" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="K174" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="175" ht="12.8">
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F175" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H175" s="1">
+      <c r="H175" s="1" t="n">
         <v>54</v>
       </c>
       <c r="I175" s="4" t="s">
@@ -12295,11 +11304,8 @@
       <c r="J175" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="K175" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="176" s="5" customFormat="1" ht="12.8">
+    </row>
+    <row r="176" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -12309,7 +11315,7 @@
         <v>69</v>
       </c>
       <c r="G176" s="1"/>
-      <c r="H176" s="1">
+      <c r="H176" s="1" t="n">
         <v>55</v>
       </c>
       <c r="I176" s="4" t="s">
@@ -12318,9 +11324,7 @@
       <c r="J176" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="K176" s="1" t="s">
-        <v>557</v>
-      </c>
+      <c r="K176" s="1"/>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
@@ -12568,7 +11572,7 @@
       <c r="IV176" s="1"/>
       <c r="IW176" s="1"/>
     </row>
-    <row r="177" s="5" customFormat="1" ht="12.8">
+    <row r="177" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -12578,7 +11582,7 @@
         <v>242</v>
       </c>
       <c r="G177" s="1"/>
-      <c r="H177" s="1">
+      <c r="H177" s="1" t="n">
         <v>56</v>
       </c>
       <c r="I177" s="4" t="s">
@@ -12587,9 +11591,7 @@
       <c r="J177" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="K177" s="1" t="s">
-        <v>558</v>
-      </c>
+      <c r="K177" s="1"/>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
@@ -12837,7 +11839,7 @@
       <c r="IV177" s="1"/>
       <c r="IW177" s="1"/>
     </row>
-    <row r="178" s="5" customFormat="1" ht="64.15">
+    <row r="178" s="5" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -12847,7 +11849,7 @@
         <v>69</v>
       </c>
       <c r="G178" s="1"/>
-      <c r="H178" s="1">
+      <c r="H178" s="1" t="n">
         <v>57</v>
       </c>
       <c r="I178" s="6" t="s">
@@ -12856,9 +11858,7 @@
       <c r="J178" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="K178" s="1" t="s">
-        <v>559</v>
-      </c>
+      <c r="K178" s="1"/>
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
@@ -13106,7 +12106,7 @@
       <c r="IV178" s="1"/>
       <c r="IW178" s="1"/>
     </row>
-    <row r="179" s="5" customFormat="1" ht="12.8">
+    <row r="179" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -13116,7 +12116,7 @@
         <v>242</v>
       </c>
       <c r="G179" s="1"/>
-      <c r="H179" s="1">
+      <c r="H179" s="1" t="n">
         <v>58</v>
       </c>
       <c r="I179" s="4" t="s">
@@ -13125,9 +12125,7 @@
       <c r="J179" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K179" s="1" t="s">
-        <v>560</v>
-      </c>
+      <c r="K179" s="1"/>
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
@@ -13375,7 +12373,7 @@
       <c r="IV179" s="1"/>
       <c r="IW179" s="1"/>
     </row>
-    <row r="180" s="5" customFormat="1" ht="43.25">
+    <row r="180" s="5" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -13385,7 +12383,7 @@
         <v>242</v>
       </c>
       <c r="G180" s="1"/>
-      <c r="H180" s="1">
+      <c r="H180" s="1" t="n">
         <v>59</v>
       </c>
       <c r="I180" s="6" t="s">
@@ -13394,9 +12392,7 @@
       <c r="J180" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="K180" s="1" t="s">
-        <v>561</v>
-      </c>
+      <c r="K180" s="1"/>
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
@@ -13644,7 +12640,7 @@
       <c r="IV180" s="1"/>
       <c r="IW180" s="1"/>
     </row>
-    <row r="181" ht="12.8">
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D181" s="1" t="s">
         <v>255</v>
       </c>
@@ -13896,7 +12892,7 @@
       <c r="IV181" s="1"/>
       <c r="IW181" s="1"/>
     </row>
-    <row r="182" ht="12.8">
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D182" s="1" t="s">
         <v>85</v>
       </c>
@@ -14151,11 +13147,11 @@
       <c r="IV182" s="1"/>
       <c r="IW182" s="1"/>
     </row>
-    <row r="183" ht="32.8">
+    <row r="183" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F183" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H183" s="1">
+      <c r="H183" s="1" t="n">
         <v>60</v>
       </c>
       <c r="I183" s="6" t="s">
@@ -14164,15 +13160,12 @@
       <c r="J183" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="K183" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="184" ht="22.35">
+    </row>
+    <row r="184" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F184" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H184" s="1">
+      <c r="H184" s="1" t="n">
         <v>61</v>
       </c>
       <c r="I184" s="6" t="s">
@@ -14181,15 +13174,12 @@
       <c r="J184" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="K184" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="185" ht="22.35">
+    </row>
+    <row r="185" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F185" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H185" s="1">
+      <c r="H185" s="1" t="n">
         <v>103</v>
       </c>
       <c r="I185" s="6" t="s">
@@ -14198,15 +13188,12 @@
       <c r="J185" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="K185" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="186" ht="12.8">
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F186" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H186" s="1" t="n">
         <v>62</v>
       </c>
       <c r="I186" s="4" t="s">
@@ -14215,15 +13202,12 @@
       <c r="J186" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="K186" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="187" ht="12.8">
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F187" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H187" s="1">
+      <c r="H187" s="1" t="n">
         <v>63</v>
       </c>
       <c r="I187" s="4" t="s">
@@ -14232,11 +13216,8 @@
       <c r="J187" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K187" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="188" ht="12.8">
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D188" s="1" t="s">
         <v>102</v>
       </c>
@@ -14244,7 +13225,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="189" ht="12.8">
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D189" s="1" t="s">
         <v>264</v>
       </c>
@@ -14252,7 +13233,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="190" ht="12.8">
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D190" s="1" t="s">
         <v>107</v>
       </c>
@@ -14260,11 +13241,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="191" ht="43.25">
+    <row r="191" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F191" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H191" s="1">
+      <c r="H191" s="1" t="n">
         <v>64</v>
       </c>
       <c r="I191" s="6" t="s">
@@ -14273,11 +13254,8 @@
       <c r="J191" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="K191" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="192" ht="12.8">
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D192" s="1" t="s">
         <v>84</v>
       </c>
@@ -14285,17 +13263,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="196" ht="12.8">
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B196" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="198" ht="12.8">
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="199" ht="12.8">
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D199" s="1" t="s">
         <v>63</v>
       </c>
@@ -14303,7 +13281,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="200" ht="12.8">
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D200" s="1" t="s">
         <v>113</v>
       </c>
@@ -14311,11 +13289,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="201" ht="64.15">
+    <row r="201" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F201" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H201" s="1">
+      <c r="H201" s="1" t="n">
         <v>65</v>
       </c>
       <c r="I201" s="6" t="s">
@@ -14324,15 +13302,12 @@
       <c r="J201" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="K201" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="202" ht="64.15">
+    </row>
+    <row r="202" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F202" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H202" s="1">
+      <c r="H202" s="1" t="n">
         <v>66</v>
       </c>
       <c r="I202" s="6" t="s">
@@ -14341,11 +13316,8 @@
       <c r="J202" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="K202" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="205" ht="12.8">
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D205" s="1" t="s">
         <v>63</v>
       </c>
@@ -14353,7 +13325,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" ht="12.8">
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D206" s="1" t="s">
         <v>82</v>
       </c>
@@ -14361,7 +13333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="207" ht="12.8">
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D207" s="1" t="s">
         <v>272</v>
       </c>
@@ -14369,7 +13341,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="208" s="5" customFormat="1" ht="12.8">
+    <row r="208" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -14632,7 +13604,7 @@
       <c r="IV208" s="1"/>
       <c r="IW208" s="1"/>
     </row>
-    <row r="209" ht="12.8">
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D209" s="1" t="s">
         <v>85</v>
       </c>
@@ -14640,7 +13612,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="210" ht="12.8">
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
@@ -14889,7 +13861,7 @@
       <c r="IV210" s="1"/>
       <c r="IW210" s="1"/>
     </row>
-    <row r="211" s="5" customFormat="1" ht="12.8">
+    <row r="211" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -15152,7 +14124,7 @@
       <c r="IV211" s="1"/>
       <c r="IW211" s="1"/>
     </row>
-    <row r="212" s="5" customFormat="1" ht="12.8">
+    <row r="212" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -15415,7 +14387,7 @@
       <c r="IV212" s="1"/>
       <c r="IW212" s="1"/>
     </row>
-    <row r="213" ht="12.8">
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D213" s="1" t="s">
         <v>85</v>
       </c>
@@ -15670,7 +14642,7 @@
       <c r="IV213" s="1"/>
       <c r="IW213" s="1"/>
     </row>
-    <row r="214" ht="12.8">
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
@@ -15919,7 +14891,7 @@
       <c r="IV214" s="1"/>
       <c r="IW214" s="1"/>
     </row>
-    <row r="215" ht="12.8">
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D215" s="1" t="s">
         <v>274</v>
       </c>
@@ -15927,7 +14899,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="216" ht="12.8">
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D216" s="1" t="s">
         <v>113</v>
       </c>
@@ -15935,7 +14907,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="217" ht="12.8">
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D217" s="1" t="s">
         <v>85</v>
       </c>
@@ -15943,7 +14915,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="219" ht="12.8">
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D219" s="1" t="s">
         <v>274</v>
       </c>
@@ -15951,7 +14923,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="220" ht="12.8">
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D220" s="1" t="s">
         <v>113</v>
       </c>
@@ -15959,7 +14931,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="221" ht="12.8">
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D221" s="1" t="s">
         <v>102</v>
       </c>
@@ -15967,7 +14939,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="222" ht="12.8">
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D222" s="1" t="s">
         <v>107</v>
       </c>
@@ -15975,12 +14947,12 @@
         <v>277</v>
       </c>
     </row>
-    <row r="224" ht="12.8">
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D224" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="232" ht="12.8">
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D232" s="1" t="s">
         <v>85</v>
       </c>
@@ -15988,7 +14960,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="233" ht="12.8">
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D233" s="1" t="s">
         <v>86</v>
       </c>
@@ -15996,7 +14968,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="234" ht="12.8">
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D234" s="1" t="s">
         <v>85</v>
       </c>
@@ -16004,7 +14976,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="235" ht="12.8">
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D235" s="1" t="s">
         <v>280</v>
       </c>
@@ -16012,8 +14984,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="236" ht="147.75">
-      <c r="H236" s="1">
+    <row r="236" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H236" s="1" t="n">
         <v>67</v>
       </c>
       <c r="I236" s="6" t="s">
@@ -16022,11 +14994,8 @@
       <c r="J236" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="K236" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="237" ht="12.8">
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D237" s="1" t="s">
         <v>90</v>
       </c>
@@ -16034,8 +15003,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="238" ht="105.95">
-      <c r="H238" s="1">
+    <row r="238" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H238" s="1" t="n">
         <v>68</v>
       </c>
       <c r="I238" s="6" t="s">
@@ -16044,11 +15013,8 @@
       <c r="J238" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="K238" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="239" ht="12.8">
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D239" s="1" t="s">
         <v>90</v>
       </c>
@@ -16056,8 +15022,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="240" ht="105.95">
-      <c r="H240" s="1">
+    <row r="240" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H240" s="1" t="n">
         <v>69</v>
       </c>
       <c r="I240" s="6" t="s">
@@ -16066,11 +15032,8 @@
       <c r="J240" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="K240" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="241" ht="12.8">
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D241" s="1" t="s">
         <v>90</v>
       </c>
@@ -16078,17 +15041,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="242" ht="12.8">
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D242" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="243" ht="12.8">
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D243" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="244" ht="12.8">
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D244" s="1" t="s">
         <v>84</v>
       </c>
@@ -16096,7 +15059,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="245" ht="12.8">
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D245" s="1" t="s">
         <v>85</v>
       </c>
@@ -16104,7 +15067,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="246" ht="12.8">
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D246" s="1" t="s">
         <v>274</v>
       </c>
@@ -16112,7 +15075,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="247" ht="12.8">
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D247" s="1" t="s">
         <v>113</v>
       </c>
@@ -16120,7 +15083,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="248" ht="12.8">
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D248" s="1" t="s">
         <v>288</v>
       </c>
@@ -16128,7 +15091,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="249" ht="12.8">
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D249" s="1" t="s">
         <v>272</v>
       </c>
@@ -16136,7 +15099,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="250" ht="12.8">
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D250" s="1" t="s">
         <v>85</v>
       </c>
@@ -16144,7 +15107,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="251" ht="12.8">
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D251" s="1" t="s">
         <v>86</v>
       </c>
@@ -16152,7 +15115,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="252" ht="12.8">
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D252" s="1" t="s">
         <v>85</v>
       </c>
@@ -16160,7 +15123,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="253" ht="12.8">
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D253" s="1" t="s">
         <v>63</v>
       </c>
@@ -16168,7 +15131,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="254" ht="12.8">
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D254" s="1" t="s">
         <v>113</v>
       </c>
@@ -16176,11 +15139,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="255" ht="12.8">
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F255" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H255" s="1">
+      <c r="H255" s="1" t="n">
         <v>70</v>
       </c>
       <c r="I255" s="4" t="s">
@@ -16189,15 +15152,12 @@
       <c r="J255" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="K255" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="256" ht="22.35">
+    </row>
+    <row r="256" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F256" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H256" s="1">
+      <c r="H256" s="1" t="n">
         <v>71</v>
       </c>
       <c r="I256" s="6" t="s">
@@ -16206,15 +15166,12 @@
       <c r="J256" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="K256" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="257" ht="95.5">
+    </row>
+    <row r="257" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F257" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H257" s="1">
+      <c r="H257" s="1" t="n">
         <v>72</v>
       </c>
       <c r="I257" s="6" t="s">
@@ -16223,15 +15180,12 @@
       <c r="J257" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="K257" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="258" ht="12.8">
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F258" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H258" s="1">
+      <c r="H258" s="1" t="n">
         <v>73</v>
       </c>
       <c r="I258" s="4" t="s">
@@ -16240,15 +15194,12 @@
       <c r="J258" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="K258" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="259" ht="12.8">
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F259" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H259" s="1">
+      <c r="H259" s="1" t="n">
         <v>74</v>
       </c>
       <c r="I259" s="4" t="s">
@@ -16257,15 +15208,12 @@
       <c r="J259" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="K259" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="260" ht="12.8">
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F260" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H260" s="1">
+      <c r="H260" s="1" t="n">
         <v>75</v>
       </c>
       <c r="I260" s="4" t="s">
@@ -16274,15 +15222,12 @@
       <c r="J260" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="K260" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="261" ht="53.7">
+    </row>
+    <row r="261" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F261" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H261" s="1">
+      <c r="H261" s="1" t="n">
         <v>76</v>
       </c>
       <c r="I261" s="6" t="s">
@@ -16291,15 +15236,12 @@
       <c r="J261" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="K261" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="262" ht="53.7">
+    </row>
+    <row r="262" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F262" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H262" s="1">
+      <c r="H262" s="1" t="n">
         <v>77</v>
       </c>
       <c r="I262" s="6" t="s">
@@ -16308,15 +15250,12 @@
       <c r="J262" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="K262" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="263" ht="12.8">
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F263" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H263" s="1">
+      <c r="H263" s="1" t="n">
         <v>78</v>
       </c>
       <c r="I263" s="4" t="s">
@@ -16325,15 +15264,12 @@
       <c r="J263" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K263" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="264" ht="12.8">
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F264" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H264" s="1">
+      <c r="H264" s="1" t="n">
         <v>79</v>
       </c>
       <c r="I264" s="4" t="s">
@@ -16342,15 +15278,12 @@
       <c r="J264" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K264" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="265" ht="85.05">
+    </row>
+    <row r="265" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F265" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H265" s="1">
+      <c r="H265" s="1" t="n">
         <v>80</v>
       </c>
       <c r="I265" s="6" t="s">
@@ -16359,15 +15292,12 @@
       <c r="J265" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="K265" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="266" ht="12.8">
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F266" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H266" s="1">
+      <c r="H266" s="1" t="n">
         <v>81</v>
       </c>
       <c r="I266" s="4" t="s">
@@ -16376,11 +15306,8 @@
       <c r="J266" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="K266" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="267" ht="12.8">
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D267" s="1" t="s">
         <v>315</v>
       </c>
@@ -16388,7 +15315,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="268" ht="12.8">
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D268" s="1" t="s">
         <v>85</v>
       </c>
@@ -16396,7 +15323,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="269" ht="12.8">
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D269" s="1" t="s">
         <v>255</v>
       </c>
@@ -16404,7 +15331,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="270" ht="12.8">
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D270" s="1" t="s">
         <v>85</v>
       </c>
@@ -16412,11 +15339,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="271" ht="53.7">
+    <row r="271" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F271" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H271" s="1">
+      <c r="H271" s="1" t="n">
         <v>82</v>
       </c>
       <c r="I271" s="6" t="s">
@@ -16425,11 +15352,8 @@
       <c r="J271" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="K271" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="273" ht="12.8">
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D273" s="1" t="s">
         <v>102</v>
       </c>
@@ -16437,7 +15361,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="274" ht="12.8">
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D274" s="1" t="s">
         <v>103</v>
       </c>
@@ -16445,7 +15369,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="275" ht="12.8">
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D275" s="1" t="s">
         <v>107</v>
       </c>
@@ -16453,7 +15377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="276" ht="12.8">
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D276" s="1" t="s">
         <v>85</v>
       </c>
@@ -16461,7 +15385,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="277" ht="12.8">
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D277" s="1" t="s">
         <v>321</v>
       </c>
@@ -16469,17 +15393,17 @@
         <v>322</v>
       </c>
     </row>
-    <row r="282" ht="12.8">
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B282" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="286" ht="12.8">
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="287" s="5" customFormat="1" ht="12.8">
+    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -16742,7 +15666,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" ht="12.8">
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D288" s="1" t="s">
         <v>128</v>
       </c>
@@ -16750,7 +15674,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="289" ht="12.8">
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D289" s="1" t="s">
         <v>86</v>
       </c>
@@ -17005,7 +15929,7 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" ht="12.8">
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D290" s="1" t="s">
         <v>107</v>
       </c>
@@ -17013,7 +15937,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="291" s="9" customFormat="1" ht="12.8">
+    <row r="291" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -17023,7 +15947,7 @@
         <v>65</v>
       </c>
       <c r="G291" s="1"/>
-      <c r="H291" s="1">
+      <c r="H291" s="1" t="n">
         <v>83</v>
       </c>
       <c r="I291" s="4" t="s">
@@ -17032,9 +15956,7 @@
       <c r="J291" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="K291" s="1" t="s">
-        <v>584</v>
-      </c>
+      <c r="K291" s="1"/>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
@@ -17282,11 +16204,11 @@
       <c r="IV291" s="1"/>
       <c r="IW291" s="1"/>
     </row>
-    <row r="293" ht="12.8">
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F293" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H293" s="1">
+      <c r="H293" s="1" t="n">
         <v>84</v>
       </c>
       <c r="I293" s="4" t="s">
@@ -17295,9 +16217,7 @@
       <c r="J293" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="K293" s="1" t="s">
-        <v>585</v>
-      </c>
+      <c r="K293" s="1"/>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
@@ -17545,11 +16465,11 @@
       <c r="IV293" s="1"/>
       <c r="IW293" s="1"/>
     </row>
-    <row r="294" ht="12.8">
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F294" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H294" s="1">
+      <c r="H294" s="1" t="n">
         <v>85</v>
       </c>
       <c r="I294" s="4" t="s">
@@ -17558,15 +16478,12 @@
       <c r="J294" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K294" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="295" ht="43.25">
+    </row>
+    <row r="295" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F295" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H295" s="1">
+      <c r="H295" s="1" t="n">
         <v>86</v>
       </c>
       <c r="I295" s="6" t="s">
@@ -17575,15 +16492,12 @@
       <c r="J295" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="K295" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="296" ht="12.8">
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F296" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H296" s="1">
+      <c r="H296" s="1" t="n">
         <v>87</v>
       </c>
       <c r="I296" s="4" t="s">
@@ -17592,15 +16506,12 @@
       <c r="J296" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="K296" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="297" ht="12.8">
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F297" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H297" s="1">
+      <c r="H297" s="1" t="n">
         <v>88</v>
       </c>
       <c r="I297" s="4" t="s">
@@ -17609,15 +16520,12 @@
       <c r="J297" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="K297" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="298" ht="74.6">
+    </row>
+    <row r="298" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F298" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H298" s="1">
+      <c r="H298" s="1" t="n">
         <v>89</v>
       </c>
       <c r="I298" s="6" t="s">
@@ -17626,15 +16534,12 @@
       <c r="J298" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="K298" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="299" ht="95.5">
+    </row>
+    <row r="299" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F299" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H299" s="1">
+      <c r="H299" s="1" t="n">
         <v>90</v>
       </c>
       <c r="I299" s="6" t="s">
@@ -17643,15 +16548,12 @@
       <c r="J299" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="K299" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="300" ht="12.8">
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F300" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H300" s="1">
+      <c r="H300" s="1" t="n">
         <v>91</v>
       </c>
       <c r="I300" s="4" t="s">
@@ -17660,15 +16562,12 @@
       <c r="J300" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="K300" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="301" ht="53.7">
+    </row>
+    <row r="301" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F301" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H301" s="1">
+      <c r="H301" s="1" t="n">
         <v>92</v>
       </c>
       <c r="I301" s="6" t="s">
@@ -17677,15 +16576,12 @@
       <c r="J301" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="K301" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="302" ht="12.8">
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F302" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H302" s="1">
+      <c r="H302" s="1" t="n">
         <v>93</v>
       </c>
       <c r="I302" s="4" t="s">
@@ -17694,15 +16590,12 @@
       <c r="J302" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="K302" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="303" ht="85.05">
+    </row>
+    <row r="303" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F303" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H303" s="1">
+      <c r="H303" s="1" t="n">
         <v>94</v>
       </c>
       <c r="I303" s="6" t="s">
@@ -17711,15 +16604,12 @@
       <c r="J303" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="K303" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="304" ht="12.8">
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F304" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H304" s="1">
+      <c r="H304" s="1" t="n">
         <v>95</v>
       </c>
       <c r="I304" s="4" t="s">
@@ -17728,15 +16618,12 @@
       <c r="J304" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="K304" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="305" ht="12.8">
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F305" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H305" s="1">
+      <c r="H305" s="1" t="n">
         <v>96</v>
       </c>
       <c r="I305" s="4" t="s">
@@ -17745,15 +16632,12 @@
       <c r="J305" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="K305" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="306" ht="12.8">
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F306" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H306" s="1">
+      <c r="H306" s="1" t="n">
         <v>97</v>
       </c>
       <c r="I306" s="4" t="s">
@@ -17762,15 +16646,12 @@
       <c r="J306" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K306" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="307" ht="12.8">
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F307" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H307" s="1">
+      <c r="H307" s="1" t="n">
         <v>98</v>
       </c>
       <c r="I307" s="4" t="s">
@@ -17779,15 +16660,12 @@
       <c r="J307" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="K307" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="308" ht="12.8">
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F308" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H308" s="1">
+      <c r="H308" s="1" t="n">
         <v>99</v>
       </c>
       <c r="I308" s="4" t="s">
@@ -17796,15 +16674,12 @@
       <c r="J308" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="K308" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="309" ht="12.8">
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F309" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H309" s="1">
+      <c r="H309" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I309" s="4" t="s">
@@ -17813,15 +16688,12 @@
       <c r="J309" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K309" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="310" ht="53.7">
+    </row>
+    <row r="310" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F310" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H310" s="1">
+      <c r="H310" s="1" t="n">
         <v>101</v>
       </c>
       <c r="I310" s="6" t="s">
@@ -17830,11 +16702,8 @@
       <c r="J310" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="K310" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="311" ht="12.8">
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D311" s="1" t="s">
         <v>84</v>
       </c>
@@ -17842,22 +16711,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="312" ht="12.8">
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D312" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="313" ht="12.8">
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B313" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="317" ht="12.8">
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="318" ht="12.8">
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D318" s="1" t="s">
         <v>63</v>
       </c>
@@ -17865,7 +16734,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="319" ht="12.8">
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D319" s="1" t="s">
         <v>102</v>
       </c>
@@ -17873,7 +16742,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="320" ht="12.8">
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D320" s="1" t="s">
         <v>128</v>
       </c>
@@ -17881,7 +16750,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="321" ht="12.8">
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D321" s="1" t="s">
         <v>86</v>
       </c>
@@ -17889,7 +16758,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="322" ht="12.8">
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D322" s="1" t="s">
         <v>107</v>
       </c>
@@ -17897,7 +16766,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="323" s="9" customFormat="1" ht="12.8">
+    <row r="323" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -17905,16 +16774,14 @@
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
-      <c r="H323" s="1">
+      <c r="H323" s="1" t="n">
         <v>106</v>
       </c>
       <c r="I323" s="6" t="s">
         <v>357</v>
       </c>
       <c r="J323" s="4"/>
-      <c r="K323" s="1" t="s">
-        <v>600</v>
-      </c>
+      <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
@@ -18162,27 +17029,22 @@
       <c r="IV323" s="1"/>
       <c r="IW323" s="1"/>
     </row>
-    <row r="324" ht="32.8">
-      <c r="H324" s="1">
+    <row r="324" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H324" s="1" t="n">
         <v>107</v>
       </c>
       <c r="I324" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="K324" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="325" ht="12.8">
-      <c r="H325" s="1">
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="1" t="n">
         <v>108</v>
       </c>
       <c r="I325" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="K325" s="1" t="s">
-        <v>602</v>
-      </c>
+      <c r="K325" s="1"/>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
@@ -18430,51 +17292,39 @@
       <c r="IV325" s="1"/>
       <c r="IW325" s="1"/>
     </row>
-    <row r="326" ht="12.8">
-      <c r="H326" s="1">
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="1" t="n">
         <v>109</v>
       </c>
       <c r="I326" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="K326" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="327" ht="22.35">
-      <c r="H327" s="1">
+    </row>
+    <row r="327" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H327" s="1" t="n">
         <v>110</v>
       </c>
       <c r="I327" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="K327" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="328" ht="12.8">
-      <c r="H328" s="1">
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H328" s="1" t="n">
         <v>111</v>
       </c>
       <c r="I328" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="K328" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="329" ht="12.8">
-      <c r="H329" s="1">
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H329" s="1" t="n">
         <v>112</v>
       </c>
       <c r="I329" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="K329" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="330" ht="12.8">
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D330" s="1" t="s">
         <v>84</v>
       </c>
@@ -18482,7 +17332,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="333" ht="12.8">
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D333" s="1" t="s">
         <v>102</v>
       </c>
@@ -18490,7 +17340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="334" ht="12.8">
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D334" s="1" t="s">
         <v>128</v>
       </c>
@@ -18498,7 +17348,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="335" ht="12.8">
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D335" s="1" t="s">
         <v>86</v>
       </c>
@@ -18506,7 +17356,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="337" s="9" customFormat="1" ht="12.8">
+    <row r="337" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -18769,7 +17619,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="338" s="9" customFormat="1" ht="12.8">
+    <row r="338" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -19028,19 +17878,17 @@
       <c r="IV338" s="1"/>
       <c r="IW338" s="1"/>
     </row>
-    <row r="339" ht="32.8">
+    <row r="339" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F339" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H339" s="1">
+      <c r="H339" s="1" t="n">
         <v>113</v>
       </c>
       <c r="I339" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="K339" s="1" t="s">
-        <v>607</v>
-      </c>
+      <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
@@ -19288,19 +18136,17 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" ht="12.8">
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F340" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H340" s="1">
+      <c r="H340" s="1" t="n">
         <v>114</v>
       </c>
       <c r="I340" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="K340" s="1" t="s">
-        <v>608</v>
-      </c>
+      <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
@@ -19548,35 +18394,29 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="341" ht="12.8">
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F341" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H341" s="1">
+      <c r="H341" s="1" t="n">
         <v>115</v>
       </c>
       <c r="I341" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="K341" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="342" ht="12.8">
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F342" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H342" s="1">
+      <c r="H342" s="1" t="n">
         <v>116</v>
       </c>
       <c r="I342" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="K342" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="343" ht="12.8">
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D343" s="1" t="s">
         <v>84</v>
       </c>
@@ -19584,77 +18424,62 @@
         <v>83</v>
       </c>
     </row>
-    <row r="344" ht="12.8">
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F344" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H344" s="1">
+      <c r="H344" s="1" t="n">
         <v>117</v>
       </c>
       <c r="I344" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="K344" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="345" ht="12.8">
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F345" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H345" s="1">
+      <c r="H345" s="1" t="n">
         <v>118</v>
       </c>
       <c r="I345" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="K345" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="346" ht="12.8">
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F346" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H346" s="1">
+      <c r="H346" s="1" t="n">
         <v>119</v>
       </c>
       <c r="I346" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K346" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="347" ht="12.8">
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F347" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H347" s="1">
+      <c r="H347" s="1" t="n">
         <v>120</v>
       </c>
       <c r="I347" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="K347" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="348" ht="12.8">
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F348" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H348" s="1">
+      <c r="H348" s="1" t="n">
         <v>121</v>
       </c>
       <c r="I348" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="K348" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="349" ht="12.8">
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D349" s="1" t="s">
         <v>86</v>
       </c>
@@ -19662,21 +18487,18 @@
         <v>375</v>
       </c>
     </row>
-    <row r="350" ht="12.8">
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F350" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H350" s="1">
+      <c r="H350" s="1" t="n">
         <v>122</v>
       </c>
       <c r="I350" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="K350" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="351" s="9" customFormat="1" ht="12.8">
+    </row>
+    <row r="351" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -19935,7 +18757,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="353" ht="12.8">
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D353" s="1" t="s">
         <v>102</v>
       </c>
@@ -20190,7 +19012,7 @@
       <c r="IV353" s="1"/>
       <c r="IW353" s="1"/>
     </row>
-    <row r="354" ht="12.8">
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D354" s="1" t="s">
         <v>128</v>
       </c>
@@ -20198,7 +19020,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="355" ht="12.8">
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
         <v>97</v>
       </c>
@@ -20209,7 +19031,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="356" ht="12.8">
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D356" s="1" t="s">
         <v>107</v>
       </c>
@@ -20217,7 +19039,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="357" s="5" customFormat="1" ht="12.8">
+    <row r="357" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -20476,21 +19298,18 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" ht="12.8">
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F358" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H358" s="1">
+      <c r="H358" s="1" t="n">
         <v>123</v>
       </c>
       <c r="I358" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K358" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="359" ht="12.8">
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K359" s="1"/>
       <c r="L359" s="1"/>
       <c r="M359" s="1"/>
@@ -20739,7 +19558,7 @@
       <c r="IV359" s="1"/>
       <c r="IW359" s="1"/>
     </row>
-    <row r="360" ht="12.8">
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D360" s="1" t="s">
         <v>102</v>
       </c>
@@ -20747,7 +19566,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="361" ht="12.8">
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D361" s="1" t="s">
         <v>128</v>
       </c>
@@ -20755,7 +19574,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="362" ht="12.8">
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
         <v>97</v>
       </c>
@@ -20766,7 +19585,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="363" ht="12.8">
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D363" s="1" t="s">
         <v>107</v>
       </c>
@@ -20774,7 +19593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="364" s="5" customFormat="1" ht="12.8">
+    <row r="364" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -20784,16 +19603,14 @@
         <v>72</v>
       </c>
       <c r="G364" s="1"/>
-      <c r="H364" s="1">
+      <c r="H364" s="1" t="n">
         <v>124</v>
       </c>
       <c r="I364" s="4" t="s">
         <v>379</v>
       </c>
       <c r="J364" s="4"/>
-      <c r="K364" s="1" t="s">
-        <v>618</v>
-      </c>
+      <c r="K364" s="1"/>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
@@ -21041,33 +19858,28 @@
       <c r="IV364" s="1"/>
       <c r="IW364" s="1"/>
     </row>
-    <row r="365" ht="12.8">
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F365" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H365" s="1">
+      <c r="H365" s="1" t="n">
         <v>125</v>
       </c>
       <c r="I365" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="K365" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="366" ht="12.8">
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F366" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H366" s="1">
+      <c r="H366" s="1" t="n">
         <v>126</v>
       </c>
       <c r="I366" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="K366" s="1" t="s">
-        <v>620</v>
-      </c>
+      <c r="K366" s="1"/>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -21315,175 +20127,139 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="367" ht="12.8">
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F367" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H367" s="1">
+      <c r="H367" s="1" t="n">
         <v>127</v>
       </c>
       <c r="I367" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="K367" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="368" ht="32.8">
+    </row>
+    <row r="368" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F368" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H368" s="1">
+      <c r="H368" s="1" t="n">
         <v>128</v>
       </c>
       <c r="I368" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="K368" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="369" ht="53.7">
+    </row>
+    <row r="369" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F369" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H369" s="1">
+      <c r="H369" s="1" t="n">
         <v>129</v>
       </c>
       <c r="I369" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="K369" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="370" ht="32.8">
+    </row>
+    <row r="370" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F370" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H370" s="1">
+      <c r="H370" s="1" t="n">
         <v>130</v>
       </c>
       <c r="I370" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="K370" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="371" ht="12.8">
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F371" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H371" s="1">
+      <c r="H371" s="1" t="n">
         <v>131</v>
       </c>
       <c r="I371" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="K371" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="372" ht="12.8">
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F372" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H372" s="1">
+      <c r="H372" s="1" t="n">
         <v>132</v>
       </c>
       <c r="I372" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="K372" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="373" ht="12.8">
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F373" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H373" s="1">
+      <c r="H373" s="1" t="n">
         <v>133</v>
       </c>
       <c r="I373" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="K373" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="374" ht="12.8">
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F374" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H374" s="1">
+      <c r="H374" s="1" t="n">
         <v>134</v>
       </c>
       <c r="I374" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="K374" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="375" ht="43.25">
+    </row>
+    <row r="375" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F375" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H375" s="1">
+      <c r="H375" s="1" t="n">
         <v>135</v>
       </c>
       <c r="I375" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K375" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="376" ht="12.8">
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F376" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H376" s="1">
+      <c r="H376" s="1" t="n">
         <v>136</v>
       </c>
       <c r="I376" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="K376" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="377" ht="12.8">
+    </row>
+    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F377" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H377" s="1">
+      <c r="H377" s="1" t="n">
         <v>137</v>
       </c>
       <c r="I377" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="K377" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="378" ht="12.8">
+    </row>
+    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F378" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H378" s="1">
+      <c r="H378" s="1" t="n">
         <v>138</v>
       </c>
       <c r="I378" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="K378" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="379" ht="12.8">
+    </row>
+    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D379" s="1" t="s">
         <v>84</v>
       </c>
@@ -21491,7 +20267,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="380" ht="12.8">
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D380" s="1" t="s">
         <v>134</v>
       </c>
@@ -21499,24 +20275,21 @@
         <v>394</v>
       </c>
     </row>
-    <row r="381" ht="22.35">
+    <row r="381" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H381" s="1">
+      <c r="H381" s="1" t="n">
         <v>139</v>
       </c>
       <c r="I381" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="K381" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="382" ht="12.8">
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D382" s="1" t="s">
         <v>85</v>
       </c>
@@ -21524,7 +20297,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="383" ht="12.8">
+    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D383" s="1" t="s">
         <v>63</v>
       </c>
@@ -21532,7 +20305,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="384" ht="12.8">
+    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D384" s="1" t="s">
         <v>102</v>
       </c>
@@ -21540,7 +20313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="385" ht="12.8">
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D385" s="1" t="s">
         <v>128</v>
       </c>
@@ -21548,7 +20321,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="386" ht="12.8">
+    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
         <v>97</v>
       </c>
@@ -21559,7 +20332,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="387" ht="12.8">
+    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D387" s="1" t="s">
         <v>107</v>
       </c>
@@ -21567,7 +20340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="388" s="5" customFormat="1" ht="12.8">
+    <row r="388" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -21575,16 +20348,14 @@
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
-      <c r="H388" s="1">
+      <c r="H388" s="1" t="n">
         <v>140</v>
       </c>
       <c r="I388" s="4" t="s">
         <v>396</v>
       </c>
       <c r="J388" s="4"/>
-      <c r="K388" s="1" t="s">
-        <v>634</v>
-      </c>
+      <c r="K388" s="1"/>
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
       <c r="N388" s="1"/>
@@ -21832,27 +20603,22 @@
       <c r="IV388" s="1"/>
       <c r="IW388" s="1"/>
     </row>
-    <row r="389" ht="22.35">
-      <c r="H389" s="1">
+    <row r="389" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H389" s="1" t="n">
         <v>141</v>
       </c>
       <c r="I389" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="K389" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="390" ht="12.8">
-      <c r="H390" s="1">
+    </row>
+    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H390" s="1" t="n">
         <v>142</v>
       </c>
       <c r="I390" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="K390" s="1" t="s">
-        <v>636</v>
-      </c>
+      <c r="K390" s="1"/>
       <c r="L390" s="1"/>
       <c r="M390" s="1"/>
       <c r="N390" s="1"/>
@@ -22100,29 +20866,23 @@
       <c r="IV390" s="1"/>
       <c r="IW390" s="1"/>
     </row>
-    <row r="391" ht="12.8">
-      <c r="H391" s="1">
+    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H391" s="1" t="n">
         <v>143</v>
       </c>
       <c r="I391" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="K391" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="392" ht="12.8">
-      <c r="H392" s="1">
+    </row>
+    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H392" s="1" t="n">
         <v>144</v>
       </c>
       <c r="I392" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="K392" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="394" ht="12.8">
+    </row>
+    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D394" s="1" t="s">
         <v>84</v>
       </c>
@@ -22130,17 +20890,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="395" ht="12.8">
+    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D395" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="396" ht="12.8">
+    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B396" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="399" s="5" customFormat="1" ht="12.8">
+    <row r="399" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
         <v>43</v>
       </c>
@@ -22401,7 +21161,7 @@
       <c r="IV399" s="1"/>
       <c r="IW399" s="1"/>
     </row>
-    <row r="401" ht="12.8">
+    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D401" s="1" t="s">
         <v>102</v>
       </c>
@@ -22656,7 +21416,7 @@
       <c r="IV401" s="1"/>
       <c r="IW401" s="1"/>
     </row>
-    <row r="402" ht="12.8">
+    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D402" s="1" t="s">
         <v>128</v>
       </c>
@@ -22664,7 +21424,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="403" ht="12.8">
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D403" s="1" t="s">
         <v>86</v>
       </c>
@@ -22672,7 +21432,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="405" s="9" customFormat="1" ht="12.8">
+    <row r="405" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -22935,7 +21695,7 @@
       <c r="IV405" s="1"/>
       <c r="IW405" s="1"/>
     </row>
-    <row r="406" s="9" customFormat="1" ht="12.8">
+    <row r="406" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -22945,16 +21705,14 @@
         <v>65</v>
       </c>
       <c r="G406" s="1"/>
-      <c r="H406" s="1">
+      <c r="H406" s="1" t="n">
         <v>145</v>
       </c>
       <c r="I406" s="4" t="s">
         <v>403</v>
       </c>
       <c r="J406" s="4"/>
-      <c r="K406" s="1" t="s">
-        <v>639</v>
-      </c>
+      <c r="K406" s="1"/>
       <c r="L406" s="1"/>
       <c r="M406" s="1"/>
       <c r="N406" s="1"/>
@@ -23202,19 +21960,17 @@
       <c r="IV406" s="1"/>
       <c r="IW406" s="1"/>
     </row>
-    <row r="407" ht="12.8">
+    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F407" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H407" s="1">
+      <c r="H407" s="1" t="n">
         <v>146</v>
       </c>
       <c r="I407" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="K407" s="1" t="s">
-        <v>640</v>
-      </c>
+      <c r="K407" s="1"/>
       <c r="L407" s="1"/>
       <c r="M407" s="1"/>
       <c r="N407" s="1"/>
@@ -23462,19 +22218,17 @@
       <c r="IV407" s="1"/>
       <c r="IW407" s="1"/>
     </row>
-    <row r="408" ht="12.8">
+    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F408" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H408" s="1">
+      <c r="H408" s="1" t="n">
         <v>147</v>
       </c>
       <c r="I408" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="K408" s="1" t="s">
-        <v>641</v>
-      </c>
+      <c r="K408" s="1"/>
       <c r="L408" s="1"/>
       <c r="M408" s="1"/>
       <c r="N408" s="1"/>
@@ -23722,91 +22476,73 @@
       <c r="IV408" s="1"/>
       <c r="IW408" s="1"/>
     </row>
-    <row r="409" ht="12.8">
+    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F409" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H409" s="1">
+      <c r="H409" s="1" t="n">
         <v>148</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="K409" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="410" ht="74.6">
+    </row>
+    <row r="410" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F410" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H410" s="1">
+      <c r="H410" s="1" t="n">
         <v>149</v>
       </c>
       <c r="I410" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="K410" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="411" ht="12.8">
+    </row>
+    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F411" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H411" s="1">
+      <c r="H411" s="1" t="n">
         <v>150</v>
       </c>
       <c r="I411" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="K411" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="412" ht="12.8">
+    </row>
+    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F412" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H412" s="1">
+      <c r="H412" s="1" t="n">
         <v>151</v>
       </c>
       <c r="I412" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K412" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="413" ht="12.8">
+    </row>
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F413" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H413" s="1">
+      <c r="H413" s="1" t="n">
         <v>152</v>
       </c>
       <c r="I413" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="K413" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="414" ht="12.8">
+    </row>
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F414" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H414" s="1">
+      <c r="H414" s="1" t="n">
         <v>153</v>
       </c>
       <c r="I414" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="K414" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="415" ht="12.8">
+    </row>
+    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D415" s="1" t="s">
         <v>86</v>
       </c>
@@ -23814,7 +22550,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="416" ht="12.8">
+    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D416" s="1" t="s">
         <v>63</v>
       </c>
@@ -23822,7 +22558,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="417" s="9" customFormat="1" ht="12.8">
+    <row r="417" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -24085,7 +22821,7 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" ht="12.8">
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D418" s="1" t="s">
         <v>128</v>
       </c>
@@ -24093,7 +22829,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="419" ht="12.8">
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D419" s="1" t="s">
         <v>107</v>
       </c>
@@ -24348,29 +23084,23 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="420" ht="12.8">
-      <c r="H420" s="1">
+    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H420" s="1" t="n">
         <v>154</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="K420" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="421" ht="12.8">
-      <c r="H421" s="1">
+    </row>
+    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H421" s="1" t="n">
         <v>155</v>
       </c>
       <c r="I421" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="K421" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="422" ht="12.8">
+    </row>
+    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D422" s="1" t="s">
         <v>102</v>
       </c>
@@ -24378,7 +23108,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="423" ht="12.8">
+    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D423" s="1" t="s">
         <v>128</v>
       </c>
@@ -24386,7 +23116,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="424" ht="12.8">
+    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D424" s="1" t="s">
         <v>107</v>
       </c>
@@ -24394,54 +23124,45 @@
         <v>88</v>
       </c>
     </row>
-    <row r="425" ht="12.8">
+    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D425" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="427" ht="12.8">
+    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F427" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H427" s="1">
+      <c r="H427" s="1" t="n">
         <v>156</v>
       </c>
       <c r="I427" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="K427" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="429" ht="12.8">
+    </row>
+    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F429" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H429" s="1">
+      <c r="H429" s="1" t="n">
         <v>157</v>
       </c>
       <c r="I429" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="K429" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="430" ht="12.8">
+    </row>
+    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F430" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H430" s="1">
+      <c r="H430" s="1" t="n">
         <v>158</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="K430" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="432" ht="12.8">
+    </row>
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D432" s="1" t="s">
         <v>63</v>
       </c>
@@ -24449,7 +23170,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="433" ht="12.8">
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D433" s="1" t="s">
         <v>102</v>
       </c>
@@ -24457,7 +23178,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="434" ht="12.8">
+    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D434" s="1" t="s">
         <v>128</v>
       </c>
@@ -24465,7 +23186,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="435" ht="12.8">
+    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D435" s="1" t="s">
         <v>107</v>
       </c>
@@ -24473,18 +23194,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="436" ht="22.35">
-      <c r="H436" s="1">
+    <row r="436" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H436" s="1" t="n">
         <v>159</v>
       </c>
       <c r="I436" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="K436" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="437" ht="12.8">
+    </row>
+    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D437" s="1" t="s">
         <v>102</v>
       </c>
@@ -24492,7 +23210,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="438" ht="12.8">
+    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D438" s="1" t="s">
         <v>128</v>
       </c>
@@ -24500,7 +23218,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="439" ht="12.8">
+    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D439" s="1" t="s">
         <v>107</v>
       </c>
@@ -24508,7 +23226,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="440" ht="12.8">
+    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D440" s="1" t="s">
         <v>63</v>
       </c>
@@ -24516,49 +23234,40 @@
         <v>112</v>
       </c>
     </row>
-    <row r="442" ht="32.8">
+    <row r="442" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F442" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H442" s="1">
+      <c r="H442" s="1" t="n">
         <v>160</v>
       </c>
       <c r="I442" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="K442" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="443" ht="12.8">
+    </row>
+    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F443" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H443" s="1">
+      <c r="H443" s="1" t="n">
         <v>161</v>
       </c>
       <c r="I443" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="K443" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="444" ht="12.8">
+    </row>
+    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F444" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H444" s="1">
+      <c r="H444" s="1" t="n">
         <v>162</v>
       </c>
       <c r="I444" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="K444" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="446" ht="12.8">
+    </row>
+    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D446" s="1" t="s">
         <v>63</v>
       </c>
@@ -24566,7 +23275,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="447" ht="12.8">
+    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D447" s="1" t="s">
         <v>102</v>
       </c>
@@ -24574,7 +23283,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="448" ht="12.8">
+    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D448" s="1" t="s">
         <v>128</v>
       </c>
@@ -24582,7 +23291,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="449" ht="12.8">
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D449" s="1" t="s">
         <v>107</v>
       </c>
@@ -24590,40 +23299,31 @@
         <v>88</v>
       </c>
     </row>
-    <row r="450" ht="12.8">
-      <c r="H450" s="1">
+    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H450" s="1" t="n">
         <v>163</v>
       </c>
       <c r="I450" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="K450" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="451" ht="32.8">
-      <c r="H451" s="1">
+    </row>
+    <row r="451" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H451" s="1" t="n">
         <v>164</v>
       </c>
       <c r="I451" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="K451" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="452" ht="12.8">
-      <c r="H452" s="1">
+    </row>
+    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H452" s="1" t="n">
         <v>165</v>
       </c>
       <c r="I452" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="K452" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="453" ht="12.8">
+    </row>
+    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D453" s="1" t="s">
         <v>84</v>
       </c>
@@ -24631,40 +23331,31 @@
         <v>83</v>
       </c>
     </row>
-    <row r="454" ht="12.8">
-      <c r="H454" s="1">
+    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H454" s="1" t="n">
         <v>166</v>
       </c>
       <c r="I454" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K454" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="456" ht="12.8">
-      <c r="H456" s="1">
+    </row>
+    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H456" s="1" t="n">
         <v>167</v>
       </c>
       <c r="I456" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="K456" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="457" ht="12.8">
-      <c r="H457" s="1">
+    </row>
+    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H457" s="1" t="n">
         <v>168</v>
       </c>
       <c r="I457" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K457" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="460" ht="12.8">
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D460" s="1" t="s">
         <v>86</v>
       </c>
@@ -24672,18 +23363,15 @@
         <v>375</v>
       </c>
     </row>
-    <row r="461" ht="12.8">
-      <c r="H461" s="1">
+    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H461" s="1" t="n">
         <v>169</v>
       </c>
       <c r="I461" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K461" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="462" s="9" customFormat="1" ht="12.8">
+    </row>
+    <row r="462" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -24946,7 +23634,7 @@
       <c r="IV462" s="1"/>
       <c r="IW462" s="1"/>
     </row>
-    <row r="463" ht="12.8">
+    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D463" s="1" t="s">
         <v>128</v>
       </c>
@@ -24954,7 +23642,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="464" ht="12.8">
+    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
         <v>97</v>
       </c>
@@ -25212,7 +23900,7 @@
       <c r="IV464" s="1"/>
       <c r="IW464" s="1"/>
     </row>
-    <row r="466" s="5" customFormat="1" ht="12.8">
+    <row r="466" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -25475,7 +24163,7 @@
       <c r="IV466" s="1"/>
       <c r="IW466" s="1"/>
     </row>
-    <row r="467" s="9" customFormat="1" ht="12.8">
+    <row r="467" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -25734,7 +24422,7 @@
       <c r="IV467" s="1"/>
       <c r="IW467" s="1"/>
     </row>
-    <row r="468" ht="12.8">
+    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D468" s="1" t="s">
         <v>63</v>
       </c>
@@ -25989,19 +24677,17 @@
       <c r="IV468" s="1"/>
       <c r="IW468" s="1"/>
     </row>
-    <row r="469" ht="12.8">
+    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F469" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H469" s="1">
+      <c r="H469" s="1" t="n">
         <v>170</v>
       </c>
       <c r="I469" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="K469" s="1" t="s">
-        <v>662</v>
-      </c>
+      <c r="K469" s="1"/>
       <c r="L469" s="1"/>
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
@@ -26249,77 +24935,62 @@
       <c r="IV469" s="1"/>
       <c r="IW469" s="1"/>
     </row>
-    <row r="470" ht="32.8">
+    <row r="470" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F470" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H470" s="1">
+      <c r="H470" s="1" t="n">
         <v>171</v>
       </c>
       <c r="I470" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="K470" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="471" ht="12.8">
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F471" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H471" s="1">
+      <c r="H471" s="1" t="n">
         <v>172</v>
       </c>
       <c r="I471" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="K471" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="472" ht="12.8">
+    </row>
+    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F472" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H472" s="1">
+      <c r="H472" s="1" t="n">
         <v>173</v>
       </c>
       <c r="I472" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="K472" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="473" ht="12.8">
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F473" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H473" s="1">
+      <c r="H473" s="1" t="n">
         <v>174</v>
       </c>
       <c r="I473" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="K473" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="474" ht="12.8">
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F474" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H474" s="1">
+      <c r="H474" s="1" t="n">
         <v>175</v>
       </c>
       <c r="I474" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="K474" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="476" ht="12.8">
+    </row>
+    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D476" s="1" t="s">
         <v>102</v>
       </c>
@@ -26327,7 +24998,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="477" ht="12.8">
+    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D477" s="1" t="s">
         <v>128</v>
       </c>
@@ -26335,7 +25006,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="478" ht="12.8">
+    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D478" s="1" t="s">
         <v>86</v>
       </c>
@@ -26343,7 +25014,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="480" s="9" customFormat="1" ht="12.8">
+    <row r="480" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -26606,7 +25277,7 @@
       <c r="IV480" s="1"/>
       <c r="IW480" s="1"/>
     </row>
-    <row r="481" s="9" customFormat="1" ht="12.8">
+    <row r="481" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -26616,16 +25287,14 @@
         <v>9</v>
       </c>
       <c r="G481" s="1"/>
-      <c r="H481" s="1">
+      <c r="H481" s="1" t="n">
         <v>176</v>
       </c>
       <c r="I481" s="4" t="s">
         <v>436</v>
       </c>
       <c r="J481" s="4"/>
-      <c r="K481" s="1" t="s">
-        <v>668</v>
-      </c>
+      <c r="K481" s="1"/>
       <c r="L481" s="1"/>
       <c r="M481" s="1"/>
       <c r="N481" s="1"/>
@@ -26873,19 +25542,17 @@
       <c r="IV481" s="1"/>
       <c r="IW481" s="1"/>
     </row>
-    <row r="482" ht="12.8">
+    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F482" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H482" s="1">
+      <c r="H482" s="1" t="n">
         <v>177</v>
       </c>
       <c r="I482" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="K482" s="1" t="s">
-        <v>669</v>
-      </c>
+      <c r="K482" s="1"/>
       <c r="L482" s="1"/>
       <c r="M482" s="1"/>
       <c r="N482" s="1"/>
@@ -27133,7 +25800,7 @@
       <c r="IV482" s="1"/>
       <c r="IW482" s="1"/>
     </row>
-    <row r="483" ht="12.8">
+    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K483" s="1"/>
       <c r="L483" s="1"/>
       <c r="M483" s="1"/>
@@ -27382,7 +26049,7 @@
       <c r="IV483" s="1"/>
       <c r="IW483" s="1"/>
     </row>
-    <row r="485" ht="12.8">
+    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D485" s="1" t="s">
         <v>84</v>
       </c>
@@ -27390,17 +26057,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="486" ht="12.8">
+    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D486" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="487" ht="12.8">
+    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B487" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="490" s="5" customFormat="1" ht="12.8">
+    <row r="490" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -27659,7 +26326,7 @@
       <c r="IV490" s="1"/>
       <c r="IW490" s="1"/>
     </row>
-    <row r="492" ht="12.8">
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K492" s="1"/>
       <c r="L492" s="1"/>
       <c r="M492" s="1"/>
@@ -27910,12 +26577,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -27923,23 +26590,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IV160"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="53.26" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -27974,13 +26641,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>61</v>
       </c>
@@ -27988,7 +26655,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>61</v>
       </c>
@@ -27996,7 +26663,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>61</v>
       </c>
@@ -28004,12 +26671,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
         <v>63</v>
       </c>
@@ -28017,17 +26684,17 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>102</v>
       </c>
@@ -28035,7 +26702,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>128</v>
       </c>
@@ -28043,7 +26710,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>86</v>
       </c>
@@ -28297,7 +26964,7 @@
       <c r="IU18" s="1"/>
       <c r="IV18" s="1"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>107</v>
       </c>
@@ -28305,7 +26972,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" s="9" customFormat="1" ht="12.8">
+    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -28563,7 +27230,7 @@
       <c r="IU20" s="1"/>
       <c r="IV20" s="1"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="1" t="s">
         <v>442</v>
       </c>
@@ -28571,7 +27238,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -28819,7 +27486,7 @@
       <c r="IU22" s="1"/>
       <c r="IV22" s="1"/>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>128</v>
       </c>
@@ -28827,7 +27494,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="1" t="s">
         <v>444</v>
       </c>
@@ -28835,7 +27502,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>97</v>
       </c>
@@ -28846,7 +27513,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
         <v>90</v>
       </c>
@@ -28854,17 +27521,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
         <v>102</v>
       </c>
@@ -28872,7 +27539,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
         <v>128</v>
       </c>
@@ -28880,7 +27547,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
         <v>86</v>
       </c>
@@ -29134,7 +27801,7 @@
       <c r="IU36" s="1"/>
       <c r="IV36" s="1"/>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="1" t="s">
         <v>107</v>
       </c>
@@ -29142,7 +27809,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" s="9" customFormat="1" ht="12.8">
+    <row r="38" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -29400,7 +28067,7 @@
       <c r="IU38" s="1"/>
       <c r="IV38" s="1"/>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="1" t="s">
         <v>445</v>
       </c>
@@ -29408,7 +28075,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -29656,7 +28323,7 @@
       <c r="IU40" s="1"/>
       <c r="IV40" s="1"/>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="1" t="s">
         <v>90</v>
       </c>
@@ -29664,17 +28331,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="1" t="s">
         <v>102</v>
       </c>
@@ -29682,7 +28349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="1" t="s">
         <v>128</v>
       </c>
@@ -29690,7 +28357,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="1" t="s">
         <v>86</v>
       </c>
@@ -29944,7 +28611,7 @@
       <c r="IU51" s="1"/>
       <c r="IV51" s="1"/>
     </row>
-    <row r="52" s="9" customFormat="1" ht="12.8">
+    <row r="52" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -30206,7 +28873,7 @@
       <c r="IU52" s="1"/>
       <c r="IV52" s="1"/>
     </row>
-    <row r="53" ht="12.8">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -30454,8 +29121,8 @@
       <c r="IU53" s="1"/>
       <c r="IV53" s="1"/>
     </row>
-    <row r="54" ht="12.8">
-      <c r="H54" s="1">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -30464,11 +29131,8 @@
       <c r="J54" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="K54" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="55" ht="12.8">
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="1" t="s">
         <v>134</v>
       </c>
@@ -30722,8 +29386,8 @@
       <c r="IU55" s="1"/>
       <c r="IV55" s="1"/>
     </row>
-    <row r="56" ht="74.6">
-      <c r="H56" s="1">
+    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I56" s="10" t="s">
@@ -30732,12 +29396,9 @@
       <c r="J56" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="K56" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="57" ht="64.15">
-      <c r="H57" s="1">
+    </row>
+    <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I57" s="10" t="s">
@@ -30746,11 +29407,8 @@
       <c r="J57" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="K57" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="58" ht="12.8">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D58" s="1" t="s">
         <v>134</v>
       </c>
@@ -30758,8 +29416,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" ht="74.6">
-      <c r="H59" s="1">
+    <row r="59" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I59" s="10" t="s">
@@ -30768,12 +29426,9 @@
       <c r="J59" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="K59" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="60" ht="32.8">
-      <c r="H60" s="1">
+    </row>
+    <row r="60" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
@@ -30782,12 +29437,9 @@
       <c r="J60" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="K60" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="61" ht="22.35">
-      <c r="H61" s="1">
+    </row>
+    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I61" s="10" t="s">
@@ -30796,11 +29448,8 @@
       <c r="J61" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="K61" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="62" ht="12.8">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="1" t="s">
         <v>134</v>
       </c>
@@ -30808,8 +29457,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" ht="85.05">
-      <c r="H63" s="1">
+    <row r="63" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H63" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I63" s="10" t="s">
@@ -30818,12 +29467,9 @@
       <c r="J63" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="K63" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="64" ht="53.7">
-      <c r="H64" s="1">
+    </row>
+    <row r="64" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H64" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I64" s="10" t="s">
@@ -30832,12 +29478,9 @@
       <c r="J64" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="K64" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="65" ht="22.35">
-      <c r="H65" s="1">
+    </row>
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H65" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I65" s="10" t="s">
@@ -30846,12 +29489,9 @@
       <c r="J65" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="K65" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="66" ht="43.25">
-      <c r="H66" s="1">
+    </row>
+    <row r="66" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I66" s="10" t="s">
@@ -30860,11 +29500,8 @@
       <c r="J66" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="K66" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="68" ht="12.8">
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="1" t="s">
         <v>84</v>
       </c>
@@ -30872,22 +29509,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D69" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="75" ht="12.8">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" ht="12.8">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D77" s="1" t="s">
         <v>102</v>
       </c>
@@ -30895,7 +29532,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D78" s="1" t="s">
         <v>128</v>
       </c>
@@ -30903,7 +29540,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="1" t="s">
         <v>86</v>
       </c>
@@ -31157,7 +29794,7 @@
       <c r="IU79" s="1"/>
       <c r="IV79" s="1"/>
     </row>
-    <row r="80" s="9" customFormat="1" ht="12.8">
+    <row r="80" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -31419,7 +30056,7 @@
       <c r="IU80" s="1"/>
       <c r="IV80" s="1"/>
     </row>
-    <row r="81" ht="12.8">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -31667,8 +30304,8 @@
       <c r="IU81" s="1"/>
       <c r="IV81" s="1"/>
     </row>
-    <row r="82" ht="12.8">
-      <c r="H82" s="1">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -31677,11 +30314,8 @@
       <c r="J82" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K82" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="83" ht="12.8">
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D83" s="1" t="s">
         <v>134</v>
       </c>
@@ -31935,8 +30569,8 @@
       <c r="IU83" s="1"/>
       <c r="IV83" s="1"/>
     </row>
-    <row r="84" ht="12.8">
-      <c r="H84" s="1">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H84" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -31945,11 +30579,8 @@
       <c r="J84" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K84" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="86" ht="12.8">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>97</v>
       </c>
@@ -31960,7 +30591,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D87" s="1" t="s">
         <v>90</v>
       </c>
@@ -31968,17 +30599,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="89" ht="12.8">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="93" ht="12.8">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="94" ht="12.8">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D94" s="1" t="s">
         <v>102</v>
       </c>
@@ -31986,7 +30617,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" ht="12.8">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D95" s="1" t="s">
         <v>128</v>
       </c>
@@ -31994,7 +30625,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" ht="12.8">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D96" s="1" t="s">
         <v>86</v>
       </c>
@@ -32248,7 +30879,7 @@
       <c r="IU96" s="1"/>
       <c r="IV96" s="1"/>
     </row>
-    <row r="97" ht="12.8">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D97" s="1" t="s">
         <v>107</v>
       </c>
@@ -32256,40 +30887,31 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" ht="22.35">
-      <c r="H99" s="1">
+    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="K99" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="100" ht="43.25">
-      <c r="H100" s="1">
+    </row>
+    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="K100" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="101" ht="22.35">
-      <c r="H101" s="1">
+    </row>
+    <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I101" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="K101" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="102" ht="12.8">
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="1" t="s">
         <v>134</v>
       </c>
@@ -32297,29 +30919,23 @@
         <v>135</v>
       </c>
     </row>
-    <row r="103" ht="43.25">
-      <c r="H103" s="1">
+    <row r="103" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H103" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I103" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="K103" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="104" ht="32.8">
-      <c r="H104" s="1">
+    </row>
+    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H104" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I104" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="K104" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="105" s="9" customFormat="1" ht="22.35">
+    </row>
+    <row r="105" s="9" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -32327,16 +30943,14 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-      <c r="H105" s="1">
+      <c r="H105" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I105" s="10" t="s">
         <v>474</v>
       </c>
       <c r="J105" s="1"/>
-      <c r="K105" s="1" t="s">
-        <v>686</v>
-      </c>
+      <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -32583,16 +31197,14 @@
       <c r="IU105" s="1"/>
       <c r="IV105" s="1"/>
     </row>
-    <row r="106" ht="22.35">
-      <c r="H106" s="1">
+    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H106" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>687</v>
-      </c>
+      <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
@@ -32839,7 +31451,7 @@
       <c r="IU106" s="1"/>
       <c r="IV106" s="1"/>
     </row>
-    <row r="107" ht="12.8">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="1" t="s">
         <v>134</v>
       </c>
@@ -32847,16 +31459,14 @@
         <v>135</v>
       </c>
     </row>
-    <row r="108" ht="32.8">
-      <c r="H108" s="1">
+    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H108" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I108" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>688</v>
-      </c>
+      <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
@@ -33103,7 +31713,7 @@
       <c r="IU108" s="1"/>
       <c r="IV108" s="1"/>
     </row>
-    <row r="109" ht="12.8">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="1" t="s">
         <v>134</v>
       </c>
@@ -33111,85 +31721,64 @@
         <v>135</v>
       </c>
     </row>
-    <row r="110" ht="12.8">
-      <c r="H110" s="1">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H110" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="K110" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="111" ht="32.8">
-      <c r="H111" s="1">
+    </row>
+    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H111" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="K111" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="112" ht="32.8">
-      <c r="H112" s="1">
+    </row>
+    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H112" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I112" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="K112" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="113" ht="22.35">
-      <c r="H113" s="1">
+    </row>
+    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H113" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I113" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="K113" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="114" ht="32.8">
-      <c r="H114" s="1">
+    </row>
+    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H114" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="K114" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="115" ht="32.8">
-      <c r="H115" s="1">
+    </row>
+    <row r="115" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H115" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I115" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="K115" t="s">
-        <v>694</v>
-      </c>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" ht="12.8">
-      <c r="H116" s="1">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H116" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="K116" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="117" ht="12.8">
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="1" t="s">
         <v>134</v>
       </c>
@@ -33197,62 +31786,47 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" ht="22.35">
-      <c r="H118" s="1">
+    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H118" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I118" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="K118" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="119" ht="32.8">
-      <c r="H119" s="1">
+    </row>
+    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H119" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I119" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="K119" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="120" ht="32.8">
-      <c r="H120" s="1">
+    </row>
+    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H120" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="K120" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="121" ht="32.8">
-      <c r="H121" s="1">
+    </row>
+    <row r="121" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H121" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I121" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="K121" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="122" ht="32.8">
-      <c r="H122" s="1">
+    </row>
+    <row r="122" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H122" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="K122" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="123" ht="12.8">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="1" t="s">
         <v>84</v>
       </c>
@@ -33260,7 +31834,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="124" ht="12.8">
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="1" t="s">
         <v>102</v>
       </c>
@@ -33268,7 +31842,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" ht="12.8">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="1" t="s">
         <v>85</v>
       </c>
@@ -33276,7 +31850,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="126" ht="12.8">
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="1" t="s">
         <v>86</v>
       </c>
@@ -33530,7 +32104,7 @@
       <c r="IU126" s="1"/>
       <c r="IV126" s="1"/>
     </row>
-    <row r="127" ht="12.8">
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="1" t="s">
         <v>107</v>
       </c>
@@ -33538,12 +32112,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" ht="12.8">
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="129" ht="12.8">
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="1" t="s">
         <v>84</v>
       </c>
@@ -33551,7 +32125,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" ht="12.8">
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="1" t="s">
         <v>102</v>
       </c>
@@ -33559,12 +32133,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="135" s="9" customFormat="1" ht="12.8">
+    <row r="135" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -33822,7 +32396,7 @@
       <c r="IU135" s="1"/>
       <c r="IV135" s="1"/>
     </row>
-    <row r="136" ht="12.8">
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K136" s="1"/>
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
@@ -34070,7 +32644,7 @@
       <c r="IU136" s="1"/>
       <c r="IV136" s="1"/>
     </row>
-    <row r="138" ht="12.8">
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
@@ -34318,12 +32892,12 @@
       <c r="IU138" s="1"/>
       <c r="IV138" s="1"/>
     </row>
-    <row r="139" ht="12.8">
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="140" ht="12.8">
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D140" s="1" t="s">
         <v>128</v>
       </c>
@@ -34331,7 +32905,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" ht="12.8">
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D141" s="1" t="s">
         <v>86</v>
       </c>
@@ -34585,7 +33159,7 @@
       <c r="IU141" s="1"/>
       <c r="IV141" s="1"/>
     </row>
-    <row r="142" ht="12.8">
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D142" s="1" t="s">
         <v>107</v>
       </c>
@@ -34593,12 +33167,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="143" ht="12.8">
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D143" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="144" ht="12.8">
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D144" s="1" t="s">
         <v>84</v>
       </c>
@@ -34606,12 +33180,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="145" ht="12.8">
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="148" ht="12.8">
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1"/>
@@ -34859,7 +33433,7 @@
       <c r="IU148" s="1"/>
       <c r="IV148" s="1"/>
     </row>
-    <row r="150" s="9" customFormat="1" ht="12.8">
+    <row r="150" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -35117,7 +33691,7 @@
       <c r="IU150" s="1"/>
       <c r="IV150" s="1"/>
     </row>
-    <row r="151" ht="12.8">
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -35365,7 +33939,7 @@
       <c r="IU151" s="1"/>
       <c r="IV151" s="1"/>
     </row>
-    <row r="153" ht="12.8">
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
@@ -35613,7 +34187,7 @@
       <c r="IU153" s="1"/>
       <c r="IV153" s="1"/>
     </row>
-    <row r="157" s="9" customFormat="1" ht="12.8">
+    <row r="157" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -35871,7 +34445,7 @@
       <c r="IU157" s="1"/>
       <c r="IV157" s="1"/>
     </row>
-    <row r="158" ht="12.8">
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
@@ -36119,7 +34693,7 @@
       <c r="IU158" s="1"/>
       <c r="IV158" s="1"/>
     </row>
-    <row r="160" ht="12.8">
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
@@ -36369,12 +34943,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_main.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="index" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="mono" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="fiama" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="index" sheetId="1" r:id="rId3"/>
+    <sheet name="mono" sheetId="2" r:id="rId4"/>
+    <sheet name="fiama" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="701">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -497,7 +497,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Unaware of what was yet to come
@@ -507,7 +507,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">we gazed at flames of the bonfire
@@ -517,7 +517,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">waiting patiently for the dawn to break.</t>
@@ -1809,6 +1809,805 @@
   </si>
   <si>
     <t xml:space="preserve">endroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">宫廷会议</t>
+  </si>
+  <si>
+    <t xml:space="preserve">迷之少女</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利拉的本事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">莱姆·伊德之梦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳木堡之主</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(test)柳木堡之主2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(test)分别</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(test)背叛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(test)尼米尔之丘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工作人员表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对现在而言早已被遗忘的过去…
+这颗星球的大地上埋没着许多文明的残骸
+在莱姆·伊德文明的伤痕未愈便迎来的第十一纪
+有一段关于西埃尔·泰尔文明的故事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沙漠古帝国的战火蔓延到各地
+给世界带来了长期的混乱。
+在西大陆，失去了萨伊拉飞艇的帝国
+开始慢慢撤退
+长达十年的战争迎来了终结。
+人类庆祝着他们获得的第一次胜利与和平
+恢复了过去的生活。
+但是，他们没有忘记艾莱亚在这场大战中的背叛，
+因为他们选择了观望。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">而后，近十五年的岁月过去了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">时间流逝…
+和前往米西利亚的商队搭伙旅行的你
+听到了一些让人不安的传闻
+这让你预感又将有一股暗中涌动的力量再次逼近西之地。
+旅行即将结束的某一天晚上
+你被神秘的光芒所吸引
+踏进了古老的森林。
+你不断向着森林的深处前进，遇到了颜色越来越浓的蓝色瘴气
+随之你感到意识愈渐模糊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">醒过来了吗？
+还是先躺着比较好。你之前失去了意识。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能在无力回天之前被发现算你幸运。人类踏进艾莱亚的森林可不算明智。特别是在这树木喧嚣的大风之夜。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…为了把倒在森林里的你搬到这里，我们也只好选择停下急迫的旅程在这里停留一晚了。这倒不是在和你抱怨什么，毕竟我那位很难伺候的同伴对这次意外的休息机会还感到挺满意的。
+你是旅行者吗？为什么要去米西利亚？
+…算了，我还是不多问了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在你该好好睡觉。毕竟人只有在真正需要休息的时候才能得到平静。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是的…这就是我们故事的开始。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿什和往常一样嘴上不饶人
+但他其实比我更加享受
+你无意中带给我们的休息时间。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">米西利亚的命运，
+世界的真相，我们的抉择
+伊尔瓦将因此留下难以磨灭的伤痕…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">然而此时的我们对将要发生的事还一无所知
+我们望着篝火的火焰
+静静地等待着天亮。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，我们神秘的客人终于醒来了。
+我把粥放在了篝火旁。虽然已经完全凉了。
+…填饱肚子之后就来找我们吧。我有话跟你说。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 米西利亚宫廷 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喂，这个会议要持续到什么时候？我们到底要讨论什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贝里希，你又有诗兴了？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…自从15年前的战争以来，米西利亚始终在困境中徘徊。我们的土地不仅遭到战争摧残，还被神秘的瘟疫所侵袭。食物和资金都在日益枯竭。国内纠纷不断，贵族间的不和愈演愈烈，连未来有望的乔南公爵的继承人也突然失去了音讯。
+加之人类普遍在战后对艾莱亚萌生了反感。这让提倡两族融合的米西利亚在提里斯各国之中的立场变得十分尴尬。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更严重的是，帝国为了向米西利亚复仇，已经又在建造新的飞艇了。
+对于今后该如何是好这个问题，根本无法通过讨论得出答案。现在我们光是处理自己领地的问题就已经忙得不可开交了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你还是那么认真啊，梅尔文。
+总之，我们就像身处一条奶酪一样的船上，四处是洞。现在所做的讨论，无异于是在悠闲地商量该先堵住哪个洞。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那边的小鬼们，从刚才开始就在嘀嘀咕咕什么呢？
+还有你，贝里希，你把乐器带到宫廷会议上是怎么回事！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我就是觉得，或许可以在这唱一首歌。说不定能让你们刻板的脑袋变得灵活些。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贝里希，你说什么…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别那么上火，卡多恩。其实正如贝里希所说，像这样的会议什么都决定不了。
+我有点儿小事，先走了。起来，艾露米纳雷。要走了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…啊，是，埃夫隆德大人！对不起。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…那小姑娘怎么回事？站着睡着了吗？
+就算她是少主的随从，在这里睡着也实属不敬。少主他也真是，竟不拿米西利亚的头等大事当回事。……哎，这个国家究竟怎么了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 米西利亚宫廷花园 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你在磨蹭什么，艾露米纳雷。照你的步调走天就要黑了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">且慢，埃夫隆德。我有话要和你说。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这不是父亲大人吗。您这是从那无聊的会议中溜出来赏花了吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别耍贫嘴埃夫隆德，这就是那位姑娘吗。
+姑娘，你叫什么名字？在宫廷生活可有什么不便？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我叫艾露米纳雷，陛下。宫廷的生活与孤儿院的生活没有太大的差别。我只是跟着埃夫隆德大人……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…有劳你了。不过你偶尔也会想独自清静一下吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈哈！您可真会开玩笑啊，父亲大人。
+您又不是不知道有过村子因为有人吓唬梦现之子而毁灭的事情。别看她这样，她其实胆小得要命。我根本不敢让她有一刻她离开我的视线。唉，如果她能有已故的芙莉亚乌涅大人一半美丽，这起码也算个享受啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所以说，梦现之子的力量…算是研究成功了吗。
+…真是让人难以相信啊。尽管我知道这是种不可饶恕的罪孽，却还是把一切都交给了你们，不，是交给了你。
+只要掌握了这股人类从未有过的力量作为工具，米西利亚的人民就有办法得救了吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工具？父亲您可不要误会了。
+我做这研究既不是为了人类，也不是为了米西利亚。一切都是为了艾露米纳雷和她的同胞们，为了让她们在即将到来的苦难时代中能生存下去。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">父亲确实是把「诅咒」强加给了我们，然后哥哥就因此卑怯地逃跑了。但我不这么认为，我会改变一切，包括把您所认为的诅咒变成祝福。
+父亲大人您自己多保重吧，我还有事就先告辞了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇，梅尔文大人！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇，太棒了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">女士们，稍安勿躁啊，你们都挡在这里，这路还怎么让别人走。
+啊，那位女士，请不要推搡。请把路让一让！
+…啊，贝里希，你来的可正是时候。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">梅尔文，你身边总是这么热闹啊。真巧，今天我正带来了新曲，也能请女士们欣赏一下了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊呀呀ー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…那么多女士，一眨眼就不见了。喂，梅尔文，我的歌有那么糟糕吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是啊…呃，不是。总之多谢你了。
+至于你的歌…我觉得演奏的部分还是不错的。我妹妹也和我说过，你们刚生的孩子在听到你的莱雅琴演奏后就会忘记哭泣安然入梦。要按她的评价来说，只要你不张嘴，人们都会以为是有艾莱亚在进行一场绝美的演奏。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…喂喂，你这莫不是在损我？算了，就当作是在夸我好了。
+那这么说来我最爱妻子还是很有品味的，能够听得出我这得到赛特拉斯公爵真传的琴技水平不凡。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的莱雅琴是赛特拉斯大人教的？我怎么没听说过？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">倒也没什么特别值得一说的。
+你也知道，我以前是泽纳恩那边的人，因为做了些蠢事，在10年前逃亡到了米西利亚这边来。那时的我只懂舞刀弄剑的，加上人生地不熟，日子也不好过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后来有一天，我在酒馆机缘巧合的遇到了一位弹着莱雅琴的男子。当然，我那时候并不知道他就是赛特拉斯大人。
+只是看大伙都觉得他那样玩弄乐器很优雅，就嘲讽说「乐器是给女人和孩子玩的东西」。后来你猜怎么着，他既不生气也不反驳，而是在看过我一眼后，没把我当回事的自顾自的演奏起了一曲泽纳恩的牧歌。
+然后我就…哎，算了，不跟你说了。后来的事就任你想象吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…对我们米西利亚人来说，赛特拉斯大人是一位让人感到亲近信任的慈祥父亲，也是一位让人不敢抬头直视的严厉老师。毕竟他已经守护了这个国家100多年。我看就算是你，也赢不过赛特拉斯大人吧。
+说起来，后来从人们口中得知你不练习剑术，而是跑到郊外的山丘上一个人练莱雅琴的时候，大家还以为你是爱上了哪个女人呢。不知不觉时间又过去那么久，现在看惯了你背着莱雅琴的样子，反而觉得这样才像你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你只顾着玩音乐，害我都找不到练剑的对手了。真怕你的武艺都生疏了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我自己也没想到，可能比刀剑，演奏才更符合我的性格。
+不过我明白你的担心。现在的米西利亚阴云密布，也许确实是时候该把乐器放回柜子里去了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我喜欢米西利亚这个地方。
+虽然最开始在这里生活的那段日子里，人们看到我这么个大个子在扛着乐器四处走动都会笑话我，但后来米西利亚终究是接受了无家可归又性格偏激的我。不仅如此，我还在这里找到了毕生的挚友和美丽的妻子，有了个吵闹的秃头老丈人，每天的日子都变得热闹得很啊。
+让那又小又穷的泽纳恩吃屎去吧！我，我要为我好不容易找寻到的故乡献出我的心脏。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…虽然算是借着酒劲说出来的话吧。但你能有这样的觉悟，是谁都会高看你一眼的。
+好了，你该回家了。小心别醉醺醺地在你家小宝宝面前唱歌，我妹妹会杀了你的！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵，既然石化植物的根都侵蚀到了这种地方。看来前面确实是会有以太结晶。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对这还满意么，加拉斯卿？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不枉我特意来一趟。不过与沙漠地下广阔的魔石群相比，这儿只算少的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我听说建造萨伊拉飞艇会需要大量的魔石。你会来到这里，是不是因为只靠那丰富的沙漠地下资源也不够安心呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">勘察魔石的确是目的之一。但是来提里斯边境这个因缘之地的理由不仅于此。
+那场令人难忘的恐怖光之风暴…只要照着地图看，就能知道最初看到到光的地方和这个「风之墓地」所在的位置一样。这不是有些太巧了吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…米西利亚的奇迹。你是说摧毁了萨伊拉无敌飞船的风暴与尼米尔的魔石有关…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵……这确实是个值得和加拉斯卿深入探讨的设想。
+不过我们这里似乎来了一位不速之客。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，看起来不过是个冒险者而已。
+不是什么问题。让我们帝国的魔像来收拾吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，完成向导任务的我也是时候离开了。加拉斯卿，请不要忘记我们约好的事情。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷…喂，艾露米纳雷，你又睡着了吗？该走了，你这个拖拖拉拉的家伙！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…对、对不起，埃夫隆德大人！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了，我确实也很好奇一个冒险者来到「风之墓地」的深层是想干什么，但不巧的是我要先去前面。
+别客气，来和我的魔像们一起跳舞吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从能记事时起，我就能听到森林的「声音」。
+我总是依偎在古老森林的大树旁，听着树木的歌声。因为森林的歌声让我回想起逝去的母亲。
+引导我来到这里的也是森林的声音。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…尼米尔的地底居然有这样的地方呢。
+但是…我明白。这个「森林」的生命已经迎来终结，只是慢慢地在等待枯萎。
+不管曾有过什么，阿什期待的东西已经不在这里了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在对现在而言早已被遗忘的过去
+古代文明莱姆·伊德发现了“它”。
+“它”被称为「永远闪耀之物」
+也有着寄宿死者思念之光、注满星辰之泪、玛那…
+又或是“以太”这样的名字。
+那是能将事物应有模样进行记忆、再生、融合
+的灵魂之泉。
+没过多久它就渗透了人类的世界
+也改变了莱姆·伊德的文明。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是，醉心于以太的莱姆·伊德
+和星球一起走上了灭亡的道路。
+因以太引起的纷争连绵不断
+让大地深受伤害，让天空被阴云覆盖。
+最终，以太的枯竭
+让生态环境变成了人类无法居住的状态。
+永远的冬天到来了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只有「不死的大树」在冬天幸存下来。
+大树孕育了森林，森林不久孕育了生命。
+那片森林被称为温戴尔。
+那森林中树木产生的蓝光树粉
+在风中飞舞，直通云霄。
+那是星球净化和再生的开始。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…西埃尔·泰尔的时代就这样从星球再生的约定中开始了。但是，温戴尔的风已经停了数百年。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巨大的…飞蛾？
+…我是在做梦吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然是人类却能听到我的声音吗，森林的女儿啊，我的名字是欧涅芙。是不死大树的伴侣，始源的存在，在伊尔瓦生灵们的母亲。
+在你面前的水晶，或者被称为魔石的结晶，是上古时代树木与以太融合石化而成的。那魔石隐藏着巨大的力量。
+…然而在经过漫长岁月之后释放这种力量的方法却遗失了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是，距今20年前，一个艾莱亚人释放了尼米尔魔石的力量，唤来了狂风。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…尼米尔的狂风。魔石回应了赛特大人的祈祷。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那风是伊尔瓦长年期待的以太风的先兆。「无风的季节」结束，星球的净化现在又要开始了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">星球的净化…等等，你想说什么？
+我们为了寻求击退帝国侵略的力量来到了这里。但是，这片森林的魔石已经枯竭。我们无法阻止萨伊拉的舰队了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其他地方还有魔石存在。如果你想要力量，就去东南山脉的遗迹利萨纳斯吧。
+还有一件事。只有「风声聆听者」才能释放魔石并呼唤失去的风。去寻找「风声聆听者」吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我不能完全相信你的话。风声聆听者是指赛特大人吗？你为什么要帮助我们？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森林的女儿，脆弱又短命的人类啊，你无法理解我的职责。我必须离开了。
+有一件事你要记得。即使用魔石打败帝国，如果风就此消失了的话，等待西埃尔·泰尔的是终极的失败。
+聆听森林之声的女儿啊，愿你得到风的加护。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">等一下！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森之淑女欧涅芙…她到底是…
+不，现在必须尽快回到据点，向阿什报告。
+好了，我们走吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 米西利亚的街道上 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没想到会在这里待这么久。那个旅人居然会如此热心地进行开拓。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你看上去没有精神啊，菲亚玛。从尼米尔回来之后就一直都是这这副样子。
+…没事吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，对不起，让你担心了。在那之后我每天晚上都会梦见莱姆·伊德。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">莱姆·伊德的梦？什么内容？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">尼米尔腐朽的魔石让我看到古代的记忆，看到了曾经存在于伊尔瓦名为莱姆·伊德的文明一步步走向终结的轨迹。
+他们有着比我们更先进的文明。但是，他们被以太的力量所吸引，走上了灭亡的道路。围绕以太的人类之间的争斗不断，大地枯萎，弱者被凌虐…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是有什么奇怪的吗？据我所知，人类在任何时代都是这样的。
+我们永远被两种感情所支配。恐惧和欲望。只要有两人以上的地方就一定会有争端。历史教我们用过去的悲剧来约束欲望，但我从未见过成功的先例。
+我们不会改变。莱姆·伊德的人民也是人类。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你还是那么爱讽刺啊…对，人类是不会改变的。谈到这点让我心情忧郁。无论我们做什么事，无论把什么留在世界上，人的丑陋和残酷都不会改变。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想成为赛特大人的助力。米西利亚也许还能得救……但是，人类总有一天会再次开始干涉艾莱亚的。
+我有一种不好的预感，也许会有更大的不幸在等着赛特大人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">菲亚…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我也不明白。
+虽然想说点漂亮话出来，但我早就放弃自己，放弃一切了。可能只要不对世界抱有期待，也就不会感到失望了吧。不管发生什么，我只是要保护赛特拉斯大人而已。
+不过，也不是没办法让世界变成你所期望的样子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">办法？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只要让人类都灭亡，只剩下艾莱亚不就好了。这样一来世界就会和争斗、迫害都无缘，变得和平。不，或许说最初时我们不出生就好了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开玩笑的，菲亚。你别那么吓人好不好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我没有生气。只是有些东西让我心烦。因为你的「办法」听起来太完美了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼，旅途遥远我们一定都累了。
+来，走吧。我们需要一张舒适松软的床。而且，如果在天黑之前到达柳木堡的厨房的话，可能还会有热乎乎的派吃呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">显示测试</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（以太流中共享了艾露米纳雷记忆的菲亚玛
+以第一人称讲述艾露米纳雷回忆的场面）
+（菲亚玛自我的边界变得模糊）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我躺在古老森林的一棵大树下。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这…不是我的记忆吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这一定是我在以太流中看到的那个女孩的记忆。
+艾露米纳雷的重要记忆。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我躺在古老森林的一棵大树下。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（被埃夫隆德拯救的艾露米纳雷的描写）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">埃夫隆德的部下一个个倒下。
+周围已经只有敌人了（与米西利亚的现状重叠）。
+艾露米纳雷也晕乎乎地打败了几只魔兽，但又倒下了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退下吧，艾露米纳雷。没有必要为了叛徒而战！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈…哈…对不起，埃夫隆德大人…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">像蝎狮一样的东西想要袭击两人，死亡就在眼前。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看来到此为止了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">埃夫隆德紧紧抱住艾露米纳雷。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">埃夫隆德大人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵，你还是那么懒惰。这种时候还想睡觉吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不，埃夫隆德大人。我不困。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我还想再看看这个世界。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…！(醒了过来）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(艾露米纳雷的身体被青色的光包围）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷的力量解放了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…埃夫隆德大人！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是…怎么回事？
+有人和艾露米纳雷产生共鸣，把她的力量唤了回来。虽然那个人不是我。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这种感觉…是菲亚玛，那个女孩吗！
+…对了，尼米尔的山丘…那个时候我也感觉到了。除了我以外谁的存在。菲亚玛有唤醒者的能力吗？但是，她到底是怎么得到那个资格的呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+艾露米纳雷歼灭了蝎狮和周围敌人。
+不久后两人周围就没有能动的东西了，艾露米纳雷跪了下来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷虽然已经停止了战斗，但无法阻止自己失控的力量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊…啊…埃夫隆德大人…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么了，艾露米纳雷。已经没有敌人了。控制住「力量」。不然的话你就会……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无法控制。是除了我们以外的人…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不能切断和那个女孩的共鸣吗！
+菲亚玛，快停止艾露米纳雷的力量！给我住手！听不见吗，可恶！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对不起，埃夫隆德先生…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷对埃夫隆德微笑。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">掉在地上的艾露米纳雷的向前跪下，握着埃夫隆德的手。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（从这里开始是菲亚玛的独白）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当赛特拉斯的士兵发现他时
+周围没有其他能动的东西。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他双手握住一个被扯断了的少女的手臂，蹲在地上。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在这场战斗中失去大部分主战斗力的泽纳恩开始撤退。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贝里希失踪了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 孤儿院地下 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表现·测试效果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼唤风吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">风不是属于我的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">埃夫隆德诱导着梦现之子们进行迎击，但却遭到了激烈的炮火。埃夫隆德此时作为唤醒者还不成熟，无法激发艾露米纳雷的力量。埃夫隆德将其归咎于艾露米纳雷而叫骂。一边与从萨伊拉的飞艇上飞来的魔导兵交战，一边看着孩子在炮火中被炸飞，目睹恶心场面的艾露米纳雷呕吐了起来。随着艾露米纳雷力量的失控，周围陷入混乱。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我知道。但是那个时候芙琳呼唤了风。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（询问菲亚玛当时有没有记忆）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那时候我…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我因为古老森林大树的影响睡着了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（菲亚玛的回忆描写）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在炮火中不断倒下的梦现之子们。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(恶心）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷！你在干什么，你这个废物！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（帝国的袭击什么的都无所谓了）
+（即使米西利亚灭亡也没关系）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">垃圾们，动起来！
+释放你们的力量。释放一切。
+死了也没关系，毕竟你们「已经」被抛弃了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还有死去的梦现之子们。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我听到了孩子们的呼喊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（在以太流中听到艾露米纳雷的叫声）
+（艾露米纳雷和其他梦现之子们的各种感情、恐怖、憎恨、绝望等涌现了过来）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（菲亚玛被以太的洪流吞噬了）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（沉浸在以太洪流中即将迷失自我时、听到了少女的声音）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（少女问哭泣的菲亚玛想做什么。）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（被梦现之子们的感情支配的菲亚玛希望复仇和破坏）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（菲亚玛的强烈的意志成为导火索，与少女产生共鸣）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（起身）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空气……在颤动…
+…什么，这蓝色的鳞粉是什么？发生了什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">噫</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾露米纳雷快退后！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">尼米尔上空有一条光柱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蓝色闪耀的风化为风暴袭击了萨伊拉的飞艇。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼唤风的是…我…不，是梦中的少女。我唤醒了「什么」？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">风声聆听者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稍微聊聊我自己的故事吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我诞生在米西利亚的一个小村里。
+母亲在我记事前就去世了
+酒鬼父亲每天都对我暴力相向。
+村子里的孩子们排挤我
+同父异母的兄弟也把我当外人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在那个村子里的时候，我恐怕从未露出过笑容。
+即使后来长大学会了如何保护自己
+我和世界之间筑起的高墙也没有消失。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">十年战争结束的时候，我才刚满8岁后不久
+那时，村庄遭到了瘟疫的侵袭。
+我的父亲病死后
+哥哥们就离开家乡去了米西利亚的都城。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">剩下孤身一人被留下的我，只能一边饿着肚子
+一边幸福的看着
+父亲那丑陋的身体日渐腐烂。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…和赛特大人的邂逅
+就是在那时的一个冬夜。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">山丘之上有座柳木堡，
+城堡的主人就是艾莱亚的领主，赛特拉斯公爵。
+在村中肮脏的酒馆里见到他时，
+他正在轻快地演奏羚羊角的莱雅琴。
+若有孩子们在
+他就会唱起古老的艾莱亚故事和童话。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公爵是个爱笑的人，柳木堡的居民都爱戴他。
+所以
+当他靠近无家可归的我时
+我没有任何恐惧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他牵着我的手
+向着柳木堡中温暖的厨房去。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们无言地走在通往城堡的夜路上。
+他握着我的手
+从未松开。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(在柳木堡。Coming Soon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+就这样我们漫长的战斗结束了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沉睡在芙琳大人腹中的梦现之子
+「风声聆听者」呼唤而来的以太风
+呼啸地掠过米西利亚全境
+将萨伊拉的舰队和帝国军全部击垮。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无数的牺牲
+给伊尔瓦留下了深深的伤痕。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在那之后，失去意识的赛特大人被搬到了柳木堡的废屋中
+我们只能眼睁睁的看着
+米西利亚境内灯火的生机在一天天的减少熄灭。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很快醒来的赛特大人
+变得沉默寡言
+一天里大部分时间都躺在床上度过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">然后，突然某天
+他从我们面前消失了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连封信都没有留下
+甚至也没有和他的另一半芙琳大人道别。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">米西利亚的故事，赛特拉斯的故事
+我和柳木堡之主的故事
+就这样迎来了终结。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那之后经过了一年的时间。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我在护送怀孕的芙琳大人前往温戴尔的旅途中
+写下了这个故事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和米西利亚有关的记忆
+就像是昨天的事情一样
+搅乱了我的心绪。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但即便如此
+我们的脚步却不可思议的轻快。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们围坐在篝火边
+芙琳大人摸着她日渐隆起的肚子
+露出了温柔的微笑。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过
+阿什完全没有注意到这件事。
+这倒也像他。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我也不打算告诉他。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">就算到了现在
+我每天也在想着赛特大人的事情。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳木堡之主
+现在到底在哪里
+又在做些什么呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他那让两族共存的理想
+是不是已经随着米西利亚的衰败
+一起磨灭了呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">或许
+他的故事
+还没有结束。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">或许
+我们的故事
+还会不断地编织下去。</t>
   </si>
 </sst>
 </file>
@@ -1830,38 +2629,38 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -1886,7 +2685,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1895,74 +2694,74 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1976,13 +2775,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -2158,20 +2957,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="62.98"/>
+    <col min="1" max="4" width="8.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26" style="2" customWidth="1"/>
+    <col min="6" max="6" width="62.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2197,7 +2996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2216,8 +3015,11 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" ht="12.8">
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2236,8 +3038,11 @@
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" ht="12.8">
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2256,8 +3061,11 @@
       <c r="G7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
@@ -2276,8 +3084,11 @@
       <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
@@ -2296,8 +3107,11 @@
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="10" ht="12.8">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -2316,8 +3130,11 @@
       <c r="G10" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
@@ -2336,8 +3153,11 @@
       <c r="G11" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="12" ht="12.8">
       <c r="B12" s="1" t="s">
         <v>38</v>
       </c>
@@ -2356,8 +3176,11 @@
       <c r="G12" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
@@ -2376,8 +3199,11 @@
       <c r="G13" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" ht="12.8">
       <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
@@ -2396,8 +3222,11 @@
       <c r="G14" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" ht="12.8">
       <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
@@ -2416,12 +3245,15 @@
       <c r="G15" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="H15" t="s">
+        <v>502</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -2429,24 +3261,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW492"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="62.98"/>
+    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="4" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2481,13 +3313,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>177</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>59</v>
       </c>
@@ -2495,7 +3327,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>61</v>
       </c>
@@ -2503,7 +3335,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>63</v>
       </c>
@@ -2511,7 +3343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>61</v>
       </c>
@@ -2519,7 +3351,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
         <v>61</v>
       </c>
@@ -2527,7 +3359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="1" t="s">
         <v>61</v>
       </c>
@@ -2535,7 +3367,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
@@ -2543,7 +3375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="D12" s="1" t="s">
         <v>61</v>
       </c>
@@ -2551,7 +3383,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>61</v>
       </c>
@@ -2559,7 +3391,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>61</v>
       </c>
@@ -2567,7 +3399,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>61</v>
       </c>
@@ -2575,7 +3407,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>61</v>
       </c>
@@ -2583,7 +3415,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>61</v>
       </c>
@@ -2591,7 +3423,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>61</v>
       </c>
@@ -2599,7 +3431,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>61</v>
       </c>
@@ -2607,7 +3439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>61</v>
       </c>
@@ -2615,7 +3447,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>61</v>
       </c>
@@ -2623,7 +3455,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="D22" s="1" t="s">
         <v>61</v>
       </c>
@@ -2631,7 +3463,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>61</v>
       </c>
@@ -2639,7 +3471,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="D24" s="1" t="s">
         <v>61</v>
       </c>
@@ -2647,12 +3479,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="5" customFormat="1" ht="12.8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2911,12 +3743,12 @@
       <c r="IV26" s="1"/>
       <c r="IW26" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="5" customFormat="1" ht="12.8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -3179,7 +4011,7 @@
       <c r="IV28" s="1"/>
       <c r="IW28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="D29" s="1" t="s">
         <v>84</v>
       </c>
@@ -3187,7 +4019,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="5" customFormat="1" ht="12.8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3450,7 +4282,7 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="5" customFormat="1" ht="12.8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -3713,7 +4545,7 @@
       <c r="IV31" s="1"/>
       <c r="IW31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="D32" s="1" t="s">
         <v>85</v>
       </c>
@@ -3968,7 +4800,7 @@
       <c r="IV32" s="1"/>
       <c r="IW32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="D33" s="1" t="s">
         <v>89</v>
       </c>
@@ -4220,7 +5052,7 @@
       <c r="IV33" s="1"/>
       <c r="IW33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="D34" s="1" t="s">
         <v>90</v>
       </c>
@@ -4228,8 +5060,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H35" s="1" t="n">
+    <row r="35" ht="43.25">
+      <c r="H35" s="1">
         <v>1</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -4238,8 +5070,11 @@
       <c r="J35" s="6" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K35" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="36" ht="12.8">
       <c r="D36" s="1" t="s">
         <v>90</v>
       </c>
@@ -4247,8 +5082,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H37" s="1" t="n">
+    <row r="37" ht="126.85">
+      <c r="H37" s="1">
         <v>2</v>
       </c>
       <c r="I37" s="6" t="s">
@@ -4257,8 +5092,11 @@
       <c r="J37" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K37" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="D38" s="1" t="s">
         <v>90</v>
       </c>
@@ -4266,8 +5104,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="1" t="n">
+    <row r="39" ht="12.8">
+      <c r="H39" s="1">
         <v>102</v>
       </c>
       <c r="I39" s="6" t="s">
@@ -4276,8 +5114,11 @@
       <c r="J39" s="6" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="40" ht="12.8">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
@@ -4288,11 +5129,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="126.85">
       <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="1">
         <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
@@ -4301,8 +5142,11 @@
       <c r="J41" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="D42" s="1" t="s">
         <v>90</v>
       </c>
@@ -4310,17 +5154,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="A43" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="D44" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="D45" s="1" t="s">
         <v>84</v>
       </c>
@@ -4328,7 +5172,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="D46" s="1" t="s">
         <v>102</v>
       </c>
@@ -4336,7 +5180,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
@@ -4344,7 +5188,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="D48" s="1" t="s">
         <v>105</v>
       </c>
@@ -4352,7 +5196,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
@@ -4360,7 +5204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="C50" s="1" t="s">
         <v>109</v>
       </c>
@@ -4368,7 +5212,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="D51" s="1" t="s">
         <v>85</v>
       </c>
@@ -4376,7 +5220,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="D52" s="1" t="s">
         <v>63</v>
       </c>
@@ -4384,7 +5228,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.8">
       <c r="D53" s="1" t="s">
         <v>113</v>
       </c>
@@ -4392,11 +5236,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="32.8">
       <c r="F54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="H54" s="1">
         <v>4</v>
       </c>
       <c r="I54" s="6" t="s">
@@ -4405,8 +5249,11 @@
       <c r="J54" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="55" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="55" s="5" customFormat="1" ht="12.8">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -4669,7 +5516,7 @@
       <c r="IV55" s="1"/>
       <c r="IW55" s="1"/>
     </row>
-    <row r="56" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="5" customFormat="1" ht="12.8">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -4679,7 +5526,7 @@
         <v>115</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="1">
         <v>5</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -4688,7 +5535,9 @@
       <c r="J56" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
@@ -4936,11 +5785,11 @@
       <c r="IV56" s="1"/>
       <c r="IW56" s="1"/>
     </row>
-    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="74.6">
       <c r="F57" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="1">
         <v>6</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -4949,7 +5798,9 @@
       <c r="J57" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>509</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
@@ -5197,11 +6048,11 @@
       <c r="IV57" s="1"/>
       <c r="IW57" s="1"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="F58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="1">
         <v>7</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -5210,7 +6061,9 @@
       <c r="J58" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>510</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
@@ -5458,7 +6311,7 @@
       <c r="IV58" s="1"/>
       <c r="IW58" s="1"/>
     </row>
-    <row r="59" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="5" customFormat="1" ht="12.8">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5721,7 +6574,7 @@
       <c r="IV59" s="1"/>
       <c r="IW59" s="1"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="D60" s="1" t="s">
         <v>102</v>
       </c>
@@ -5729,7 +6582,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.8">
       <c r="D61" s="1" t="s">
         <v>63</v>
       </c>
@@ -5984,7 +6837,7 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.8">
       <c r="D62" s="1" t="s">
         <v>128</v>
       </c>
@@ -5992,7 +6845,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="D63" s="1" t="s">
         <v>107</v>
       </c>
@@ -6000,8 +6853,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H65" s="1" t="n">
+    <row r="65" ht="12.8">
+      <c r="H65" s="1">
         <v>8</v>
       </c>
       <c r="I65" s="4" t="s">
@@ -6010,9 +6863,12 @@
       <c r="J65" s="6" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+      <c r="K65" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="66" ht="32.8">
+      <c r="H66" s="1">
         <v>9</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -6021,8 +6877,11 @@
       <c r="J66" s="6" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="67" ht="12.8">
       <c r="D67" s="1" t="s">
         <v>134</v>
       </c>
@@ -6030,8 +6889,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H68" s="1" t="n">
+    <row r="68" ht="35.05">
+      <c r="H68" s="1">
         <v>10</v>
       </c>
       <c r="I68" s="7" t="s">
@@ -6040,9 +6899,12 @@
       <c r="J68" s="7" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H69" s="1" t="n">
+      <c r="K68" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="69" ht="35.8">
+      <c r="H69" s="1">
         <v>11</v>
       </c>
       <c r="I69" s="8" t="s">
@@ -6051,8 +6913,11 @@
       <c r="J69" s="7" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K69" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="70" ht="12.8">
       <c r="D70" s="1" t="s">
         <v>102</v>
       </c>
@@ -6061,12 +6926,12 @@
       </c>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="D71" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.8">
       <c r="D72" s="1" t="s">
         <v>63</v>
       </c>
@@ -6074,7 +6939,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="D73" s="1" t="s">
         <v>105</v>
       </c>
@@ -6082,7 +6947,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="D74" s="1" t="s">
         <v>103</v>
       </c>
@@ -6090,7 +6955,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.8">
       <c r="D75" s="1" t="s">
         <v>107</v>
       </c>
@@ -6098,7 +6963,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.8">
       <c r="D76" s="1" t="s">
         <v>85</v>
       </c>
@@ -6106,7 +6971,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.8">
       <c r="D77" s="1" t="s">
         <v>86</v>
       </c>
@@ -6114,7 +6979,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="D78" s="1" t="s">
         <v>85</v>
       </c>
@@ -6122,7 +6987,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.8">
       <c r="D79" s="1" t="s">
         <v>113</v>
       </c>
@@ -6130,11 +6995,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="53.7">
       <c r="F80" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H80" s="1" t="n">
+      <c r="H80" s="1">
         <v>12</v>
       </c>
       <c r="I80" s="6" t="s">
@@ -6143,28 +7008,31 @@
       <c r="J80" s="6" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="82" ht="12.8">
       <c r="D82" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="12.8">
       <c r="D83" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="B87" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="12.8">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
       <c r="D91" s="1" t="s">
         <v>102</v>
       </c>
@@ -6172,7 +7040,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
       <c r="D92" s="1" t="s">
         <v>128</v>
       </c>
@@ -6180,7 +7048,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="93" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" s="9" customFormat="1" ht="12.8">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6443,7 +7311,7 @@
       <c r="IV93" s="1"/>
       <c r="IW93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.8">
       <c r="D94" s="1" t="s">
         <v>107</v>
       </c>
@@ -6451,11 +7319,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="12.8">
       <c r="F95" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H95" s="1" t="n">
+      <c r="H95" s="1">
         <v>13</v>
       </c>
       <c r="I95" s="4" t="s">
@@ -6464,7 +7332,9 @@
       <c r="J95" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="K95" s="1"/>
+      <c r="K95" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -6712,11 +7582,11 @@
       <c r="IV95" s="1"/>
       <c r="IW95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="12.8">
       <c r="F96" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="H96" s="1">
         <v>14</v>
       </c>
       <c r="I96" s="4" t="s">
@@ -6725,12 +7595,15 @@
       <c r="J96" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K96" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="97" ht="12.8">
       <c r="F97" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="H97" s="1">
         <v>15</v>
       </c>
       <c r="I97" s="4" t="s">
@@ -6739,12 +7612,15 @@
       <c r="J97" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K97" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="98" ht="105.95">
       <c r="F98" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H98" s="1" t="n">
+      <c r="H98" s="1">
         <v>16</v>
       </c>
       <c r="I98" s="6" t="s">
@@ -6753,12 +7629,15 @@
       <c r="J98" s="6" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K98" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="99" ht="53.7">
       <c r="F99" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="H99" s="1">
         <v>17</v>
       </c>
       <c r="I99" s="6" t="s">
@@ -6767,12 +7646,15 @@
       <c r="J99" s="6" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K99" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="100" ht="43.25">
       <c r="F100" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="H100" s="1">
         <v>18</v>
       </c>
       <c r="I100" s="6" t="s">
@@ -6781,12 +7663,15 @@
       <c r="J100" s="6" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K100" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="101" ht="43.25">
       <c r="F101" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H101" s="1" t="n">
+      <c r="H101" s="1">
         <v>19</v>
       </c>
       <c r="I101" s="6" t="s">
@@ -6795,12 +7680,15 @@
       <c r="J101" s="6" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K101" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="102" ht="12.8">
       <c r="F102" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="H102" s="1">
         <v>20</v>
       </c>
       <c r="I102" s="4" t="s">
@@ -6809,12 +7697,15 @@
       <c r="J102" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K102" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="103" ht="12.8">
       <c r="F103" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="H103" s="1">
         <v>21</v>
       </c>
       <c r="I103" s="4" t="s">
@@ -6823,12 +7714,15 @@
       <c r="J103" s="4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K103" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="104" ht="53.7">
       <c r="F104" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H104" s="1" t="n">
+      <c r="H104" s="1">
         <v>22</v>
       </c>
       <c r="I104" s="6" t="s">
@@ -6837,12 +7731,15 @@
       <c r="J104" s="6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K104" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="105" ht="12.8">
       <c r="F105" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H105" s="1" t="n">
+      <c r="H105" s="1">
         <v>23</v>
       </c>
       <c r="I105" s="4" t="s">
@@ -6851,8 +7748,11 @@
       <c r="J105" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K105" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="106" ht="12.8">
       <c r="D106" s="1" t="s">
         <v>134</v>
       </c>
@@ -6860,11 +7760,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="85.05">
       <c r="F107" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H107" s="1" t="n">
+      <c r="H107" s="1">
         <v>104</v>
       </c>
       <c r="I107" s="6" t="s">
@@ -6873,8 +7773,11 @@
       <c r="J107" s="6" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K107" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="108" ht="12.8">
       <c r="D108" s="1" t="s">
         <v>84</v>
       </c>
@@ -6882,22 +7785,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="12.8">
       <c r="D109" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="12.8">
       <c r="B110" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" ht="12.8">
       <c r="A113" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="114" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="5" customFormat="1" ht="12.8">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7160,7 +8063,7 @@
       <c r="IV114" s="1"/>
       <c r="IW114" s="1"/>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" ht="12.8">
       <c r="D115" s="1" t="s">
         <v>128</v>
       </c>
@@ -7168,7 +8071,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="12.8">
       <c r="D116" s="1" t="s">
         <v>86</v>
       </c>
@@ -7423,7 +8326,7 @@
       <c r="IV116" s="1"/>
       <c r="IW116" s="1"/>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" ht="12.8">
       <c r="D117" s="1" t="s">
         <v>107</v>
       </c>
@@ -7431,7 +8334,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="118" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="9" customFormat="1" ht="12.8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7441,7 +8344,7 @@
         <v>65</v>
       </c>
       <c r="G118" s="1"/>
-      <c r="H118" s="1" t="n">
+      <c r="H118" s="1">
         <v>24</v>
       </c>
       <c r="I118" s="4" t="s">
@@ -7450,7 +8353,9 @@
       <c r="J118" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K118" s="1"/>
+      <c r="K118" s="1" t="s">
+        <v>528</v>
+      </c>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -7698,11 +8603,11 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" ht="12.8">
       <c r="F119" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="H119" s="1">
         <v>25</v>
       </c>
       <c r="I119" s="4" t="s">
@@ -7711,12 +8616,15 @@
       <c r="J119" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K119" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="120" ht="12.8">
       <c r="F120" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H120" s="1" t="n">
+      <c r="H120" s="1">
         <v>105</v>
       </c>
       <c r="I120" s="4" t="s">
@@ -7725,7 +8633,9 @@
       <c r="J120" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="K120" s="1"/>
+      <c r="K120" s="1" t="s">
+        <v>530</v>
+      </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
@@ -7973,11 +8883,11 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="12.8">
       <c r="F121" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H121" s="1" t="n">
+      <c r="H121" s="1">
         <v>26</v>
       </c>
       <c r="I121" s="4" t="s">
@@ -7986,12 +8896,15 @@
       <c r="J121" s="4" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K121" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="122" ht="43.25">
       <c r="F122" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H122" s="1" t="n">
+      <c r="H122" s="1">
         <v>27</v>
       </c>
       <c r="I122" s="6" t="s">
@@ -8000,12 +8913,15 @@
       <c r="J122" s="6" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K122" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="123" ht="22.35">
       <c r="F123" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="1">
         <v>28</v>
       </c>
       <c r="I123" s="4" t="s">
@@ -8014,12 +8930,15 @@
       <c r="J123" s="6" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K123" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="124" ht="12.8">
       <c r="F124" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="1">
         <v>29</v>
       </c>
       <c r="I124" s="4" t="s">
@@ -8028,12 +8947,15 @@
       <c r="J124" s="4" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K124" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="125" ht="85.05">
       <c r="F125" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="H125" s="1">
         <v>30</v>
       </c>
       <c r="I125" s="6" t="s">
@@ -8042,12 +8964,15 @@
       <c r="J125" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="126" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K125" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="126" ht="74.6">
       <c r="F126" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="H126" s="1">
         <v>31</v>
       </c>
       <c r="I126" s="6" t="s">
@@ -8056,12 +8981,15 @@
       <c r="J126" s="6" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K126" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="127" ht="53.7">
       <c r="F127" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H127" s="1" t="n">
+      <c r="H127" s="1">
         <v>32</v>
       </c>
       <c r="I127" s="6" t="s">
@@ -8070,12 +8998,15 @@
       <c r="J127" s="6" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K127" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="128" ht="53.7">
       <c r="F128" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="H128" s="1">
         <v>33</v>
       </c>
       <c r="I128" s="6" t="s">
@@ -8084,12 +9015,15 @@
       <c r="J128" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K128" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="129" ht="12.8">
       <c r="F129" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="H129" s="1">
         <v>34</v>
       </c>
       <c r="I129" s="4" t="s">
@@ -8098,8 +9032,11 @@
       <c r="J129" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K129" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="130" ht="12.8">
       <c r="D130" s="1" t="s">
         <v>84</v>
       </c>
@@ -8107,22 +9044,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
       <c r="D131" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="12.8">
       <c r="B132" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" ht="12.8">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="135" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" s="5" customFormat="1" ht="12.8">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -8385,7 +9322,7 @@
       <c r="IV135" s="1"/>
       <c r="IW135" s="1"/>
     </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" ht="12.8">
       <c r="D136" s="1" t="s">
         <v>128</v>
       </c>
@@ -8393,7 +9330,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" ht="12.8">
       <c r="D137" s="1" t="s">
         <v>86</v>
       </c>
@@ -8648,7 +9585,7 @@
       <c r="IV137" s="1"/>
       <c r="IW137" s="1"/>
     </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="12.8">
       <c r="D138" s="1" t="s">
         <v>107</v>
       </c>
@@ -8656,7 +9593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" s="9" customFormat="1" ht="12.8">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8666,7 +9603,7 @@
         <v>65</v>
       </c>
       <c r="G139" s="1"/>
-      <c r="H139" s="1" t="n">
+      <c r="H139" s="1">
         <v>35</v>
       </c>
       <c r="I139" s="4" t="s">
@@ -8675,7 +9612,9 @@
       <c r="J139" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K139" s="1"/>
+      <c r="K139" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
@@ -8923,11 +9862,11 @@
       <c r="IV139" s="1"/>
       <c r="IW139" s="1"/>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="12.8">
       <c r="F140" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="H140" s="1">
         <v>36</v>
       </c>
       <c r="I140" s="4" t="s">
@@ -8936,12 +9875,15 @@
       <c r="J140" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K140" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="141" ht="12.8">
       <c r="F141" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H141" s="1" t="n">
+      <c r="H141" s="1">
         <v>37</v>
       </c>
       <c r="I141" s="4" t="s">
@@ -8950,7 +9892,9 @@
       <c r="J141" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="K141" s="1"/>
+      <c r="K141" s="1" t="s">
+        <v>540</v>
+      </c>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
@@ -9198,11 +10142,11 @@
       <c r="IV141" s="1"/>
       <c r="IW141" s="1"/>
     </row>
-    <row r="142" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" ht="74.6">
       <c r="F142" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H142" s="1" t="n">
+      <c r="H142" s="1">
         <v>38</v>
       </c>
       <c r="I142" s="6" t="s">
@@ -9211,12 +10155,15 @@
       <c r="J142" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K142" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="143" ht="12.8">
       <c r="F143" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H143" s="1" t="n">
+      <c r="H143" s="1">
         <v>39</v>
       </c>
       <c r="I143" s="4" t="s">
@@ -9225,12 +10172,15 @@
       <c r="J143" s="4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K143" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="144" ht="12.8">
       <c r="F144" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="H144" s="1">
         <v>40</v>
       </c>
       <c r="I144" s="4" t="s">
@@ -9239,8 +10189,11 @@
       <c r="J144" s="4" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K144" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="145" ht="12.8">
       <c r="D145" s="1" t="s">
         <v>102</v>
       </c>
@@ -9248,7 +10201,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" ht="12.8">
       <c r="D146" s="1" t="s">
         <v>128</v>
       </c>
@@ -9256,7 +10209,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" ht="12.8">
       <c r="D147" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,7 +10217,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" ht="12.8">
       <c r="D148" s="1" t="s">
         <v>107</v>
       </c>
@@ -9272,7 +10225,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="149" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" s="9" customFormat="1" ht="12.8">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -9531,11 +10484,11 @@
       <c r="IV149" s="1"/>
       <c r="IW149" s="1"/>
     </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" ht="12.8">
       <c r="F150" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H150" s="1" t="n">
+      <c r="H150" s="1">
         <v>41</v>
       </c>
       <c r="I150" s="4" t="s">
@@ -9544,12 +10497,15 @@
       <c r="J150" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="151" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K150" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="151" ht="64.15">
       <c r="F151" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="H151" s="1">
         <v>42</v>
       </c>
       <c r="I151" s="6" t="s">
@@ -9558,7 +10514,9 @@
       <c r="J151" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K151" s="1"/>
+      <c r="K151" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
@@ -9806,11 +10764,11 @@
       <c r="IV151" s="1"/>
       <c r="IW151" s="1"/>
     </row>
-    <row r="152" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" ht="43.25">
       <c r="F152" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H152" s="1" t="n">
+      <c r="H152" s="1">
         <v>43</v>
       </c>
       <c r="I152" s="6" t="s">
@@ -9819,12 +10777,15 @@
       <c r="J152" s="6" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K152" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="153" ht="12.8">
       <c r="F153" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H153" s="1" t="n">
+      <c r="H153" s="1">
         <v>44</v>
       </c>
       <c r="I153" s="4" t="s">
@@ -9833,12 +10794,15 @@
       <c r="J153" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="154" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K153" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="154" ht="64.15">
       <c r="F154" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H154" s="1" t="n">
+      <c r="H154" s="1">
         <v>45</v>
       </c>
       <c r="I154" s="6" t="s">
@@ -9847,12 +10811,15 @@
       <c r="J154" s="6" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="155" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K154" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="155" ht="64.15">
       <c r="F155" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H155" s="1" t="n">
+      <c r="H155" s="1">
         <v>46</v>
       </c>
       <c r="I155" s="6" t="s">
@@ -9861,12 +10828,15 @@
       <c r="J155" s="6" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="156" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K155" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="156" ht="85.05">
       <c r="F156" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H156" s="1" t="n">
+      <c r="H156" s="1">
         <v>47</v>
       </c>
       <c r="I156" s="6" t="s">
@@ -9875,12 +10845,15 @@
       <c r="J156" s="6" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K156" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="157" ht="12.8">
       <c r="F157" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H157" s="1" t="n">
+      <c r="H157" s="1">
         <v>48</v>
       </c>
       <c r="I157" s="4" t="s">
@@ -9889,12 +10862,15 @@
       <c r="J157" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="158" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K157" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="158" ht="64.15">
       <c r="F158" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H158" s="1" t="n">
+      <c r="H158" s="1">
         <v>49</v>
       </c>
       <c r="I158" s="6" t="s">
@@ -9903,12 +10879,15 @@
       <c r="J158" s="6" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K158" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="159" ht="12.8">
       <c r="F159" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H159" s="1" t="n">
+      <c r="H159" s="1">
         <v>50</v>
       </c>
       <c r="I159" s="4" t="s">
@@ -9917,12 +10896,15 @@
       <c r="J159" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="160" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K159" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="160" ht="95.5">
       <c r="F160" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H160" s="1" t="n">
+      <c r="H160" s="1">
         <v>51</v>
       </c>
       <c r="I160" s="6" t="s">
@@ -9931,12 +10913,15 @@
       <c r="J160" s="6" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="161" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K160" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="161" ht="53.7">
       <c r="F161" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H161" s="1" t="n">
+      <c r="H161" s="1">
         <v>52</v>
       </c>
       <c r="I161" s="6" t="s">
@@ -9945,8 +10930,11 @@
       <c r="J161" s="6" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K161" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="162" ht="12.8">
       <c r="D162" s="1" t="s">
         <v>84</v>
       </c>
@@ -9954,17 +10942,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" ht="12.8">
       <c r="D163" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" ht="12.8">
       <c r="B164" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="167" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" s="5" customFormat="1" ht="12.8">
       <c r="A167" s="1" t="s">
         <v>235</v>
       </c>
@@ -10225,7 +11213,7 @@
       <c r="IV167" s="1"/>
       <c r="IW167" s="1"/>
     </row>
-    <row r="168" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" s="5" customFormat="1" ht="12.8">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -10488,7 +11476,7 @@
       <c r="IV168" s="1"/>
       <c r="IW168" s="1"/>
     </row>
-    <row r="169" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="5" customFormat="1" ht="12.8">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -10751,7 +11739,7 @@
       <c r="IV169" s="1"/>
       <c r="IW169" s="1"/>
     </row>
-    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" ht="12.8">
       <c r="D170" s="1" t="s">
         <v>113</v>
       </c>
@@ -11006,7 +11994,7 @@
       <c r="IV170" s="1"/>
       <c r="IW170" s="1"/>
     </row>
-    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" ht="12.8">
       <c r="D171" s="1" t="s">
         <v>86</v>
       </c>
@@ -11261,7 +12249,7 @@
       <c r="IV171" s="1"/>
       <c r="IW171" s="1"/>
     </row>
-    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" ht="12.8">
       <c r="D172" s="1" t="s">
         <v>237</v>
       </c>
@@ -11269,7 +12257,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" ht="12.8">
       <c r="D173" s="1" t="s">
         <v>85</v>
       </c>
@@ -11277,11 +12265,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" ht="12.8">
       <c r="F174" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H174" s="1" t="n">
+      <c r="H174" s="1">
         <v>53</v>
       </c>
       <c r="I174" s="4" t="s">
@@ -11290,12 +12278,15 @@
       <c r="J174" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K174" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="175" ht="12.8">
       <c r="F175" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H175" s="1" t="n">
+      <c r="H175" s="1">
         <v>54</v>
       </c>
       <c r="I175" s="4" t="s">
@@ -11304,8 +12295,11 @@
       <c r="J175" s="4" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="176" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K175" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="176" s="5" customFormat="1" ht="12.8">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -11315,7 +12309,7 @@
         <v>69</v>
       </c>
       <c r="G176" s="1"/>
-      <c r="H176" s="1" t="n">
+      <c r="H176" s="1">
         <v>55</v>
       </c>
       <c r="I176" s="4" t="s">
@@ -11324,7 +12318,9 @@
       <c r="J176" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="K176" s="1"/>
+      <c r="K176" s="1" t="s">
+        <v>557</v>
+      </c>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
@@ -11572,7 +12568,7 @@
       <c r="IV176" s="1"/>
       <c r="IW176" s="1"/>
     </row>
-    <row r="177" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="5" customFormat="1" ht="12.8">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -11582,7 +12578,7 @@
         <v>242</v>
       </c>
       <c r="G177" s="1"/>
-      <c r="H177" s="1" t="n">
+      <c r="H177" s="1">
         <v>56</v>
       </c>
       <c r="I177" s="4" t="s">
@@ -11591,7 +12587,9 @@
       <c r="J177" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="K177" s="1"/>
+      <c r="K177" s="1" t="s">
+        <v>558</v>
+      </c>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
@@ -11839,7 +12837,7 @@
       <c r="IV177" s="1"/>
       <c r="IW177" s="1"/>
     </row>
-    <row r="178" s="5" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" s="5" customFormat="1" ht="64.15">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -11849,7 +12847,7 @@
         <v>69</v>
       </c>
       <c r="G178" s="1"/>
-      <c r="H178" s="1" t="n">
+      <c r="H178" s="1">
         <v>57</v>
       </c>
       <c r="I178" s="6" t="s">
@@ -11858,7 +12856,9 @@
       <c r="J178" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="K178" s="1"/>
+      <c r="K178" s="1" t="s">
+        <v>559</v>
+      </c>
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
@@ -12106,7 +13106,7 @@
       <c r="IV178" s="1"/>
       <c r="IW178" s="1"/>
     </row>
-    <row r="179" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" s="5" customFormat="1" ht="12.8">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -12116,7 +13116,7 @@
         <v>242</v>
       </c>
       <c r="G179" s="1"/>
-      <c r="H179" s="1" t="n">
+      <c r="H179" s="1">
         <v>58</v>
       </c>
       <c r="I179" s="4" t="s">
@@ -12125,7 +13125,9 @@
       <c r="J179" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="K179" s="1"/>
+      <c r="K179" s="1" t="s">
+        <v>560</v>
+      </c>
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
@@ -12373,7 +13375,7 @@
       <c r="IV179" s="1"/>
       <c r="IW179" s="1"/>
     </row>
-    <row r="180" s="5" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="5" customFormat="1" ht="43.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -12383,7 +13385,7 @@
         <v>242</v>
       </c>
       <c r="G180" s="1"/>
-      <c r="H180" s="1" t="n">
+      <c r="H180" s="1">
         <v>59</v>
       </c>
       <c r="I180" s="6" t="s">
@@ -12392,7 +13394,9 @@
       <c r="J180" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="K180" s="1"/>
+      <c r="K180" s="1" t="s">
+        <v>561</v>
+      </c>
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
@@ -12640,7 +13644,7 @@
       <c r="IV180" s="1"/>
       <c r="IW180" s="1"/>
     </row>
-    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" ht="12.8">
       <c r="D181" s="1" t="s">
         <v>255</v>
       </c>
@@ -12892,7 +13896,7 @@
       <c r="IV181" s="1"/>
       <c r="IW181" s="1"/>
     </row>
-    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" ht="12.8">
       <c r="D182" s="1" t="s">
         <v>85</v>
       </c>
@@ -13147,11 +14151,11 @@
       <c r="IV182" s="1"/>
       <c r="IW182" s="1"/>
     </row>
-    <row r="183" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" ht="32.8">
       <c r="F183" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H183" s="1" t="n">
+      <c r="H183" s="1">
         <v>60</v>
       </c>
       <c r="I183" s="6" t="s">
@@ -13160,12 +14164,15 @@
       <c r="J183" s="6" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="184" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K183" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="184" ht="22.35">
       <c r="F184" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H184" s="1" t="n">
+      <c r="H184" s="1">
         <v>61</v>
       </c>
       <c r="I184" s="6" t="s">
@@ -13174,12 +14181,15 @@
       <c r="J184" s="6" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="185" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K184" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="185" ht="22.35">
       <c r="F185" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H185" s="1" t="n">
+      <c r="H185" s="1">
         <v>103</v>
       </c>
       <c r="I185" s="6" t="s">
@@ -13188,12 +14198,15 @@
       <c r="J185" s="6" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K185" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="186" ht="12.8">
       <c r="F186" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H186" s="1" t="n">
+      <c r="H186" s="1">
         <v>62</v>
       </c>
       <c r="I186" s="4" t="s">
@@ -13202,12 +14215,15 @@
       <c r="J186" s="4" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K186" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="187" ht="12.8">
       <c r="F187" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H187" s="1" t="n">
+      <c r="H187" s="1">
         <v>63</v>
       </c>
       <c r="I187" s="4" t="s">
@@ -13216,8 +14232,11 @@
       <c r="J187" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K187" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="188" ht="12.8">
       <c r="D188" s="1" t="s">
         <v>102</v>
       </c>
@@ -13225,7 +14244,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" ht="12.8">
       <c r="D189" s="1" t="s">
         <v>264</v>
       </c>
@@ -13233,7 +14252,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" ht="12.8">
       <c r="D190" s="1" t="s">
         <v>107</v>
       </c>
@@ -13241,11 +14260,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" ht="43.25">
       <c r="F191" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H191" s="1" t="n">
+      <c r="H191" s="1">
         <v>64</v>
       </c>
       <c r="I191" s="6" t="s">
@@ -13254,8 +14273,11 @@
       <c r="J191" s="6" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K191" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="192" ht="12.8">
       <c r="D192" s="1" t="s">
         <v>84</v>
       </c>
@@ -13263,17 +14285,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" ht="12.8">
       <c r="B196" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" ht="12.8">
       <c r="A198" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" ht="12.8">
       <c r="D199" s="1" t="s">
         <v>63</v>
       </c>
@@ -13281,7 +14303,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" ht="12.8">
       <c r="D200" s="1" t="s">
         <v>113</v>
       </c>
@@ -13289,11 +14311,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" ht="64.15">
       <c r="F201" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H201" s="1" t="n">
+      <c r="H201" s="1">
         <v>65</v>
       </c>
       <c r="I201" s="6" t="s">
@@ -13302,12 +14324,15 @@
       <c r="J201" s="6" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="202" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K201" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="202" ht="64.15">
       <c r="F202" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H202" s="1" t="n">
+      <c r="H202" s="1">
         <v>66</v>
       </c>
       <c r="I202" s="6" t="s">
@@ -13316,8 +14341,11 @@
       <c r="J202" s="6" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K202" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="205" ht="12.8">
       <c r="D205" s="1" t="s">
         <v>63</v>
       </c>
@@ -13325,7 +14353,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" ht="12.8">
       <c r="D206" s="1" t="s">
         <v>82</v>
       </c>
@@ -13333,7 +14361,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" ht="12.8">
       <c r="D207" s="1" t="s">
         <v>272</v>
       </c>
@@ -13341,7 +14369,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="208" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" s="5" customFormat="1" ht="12.8">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -13604,7 +14632,7 @@
       <c r="IV208" s="1"/>
       <c r="IW208" s="1"/>
     </row>
-    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" ht="12.8">
       <c r="D209" s="1" t="s">
         <v>85</v>
       </c>
@@ -13612,7 +14640,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" ht="12.8">
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
@@ -13861,7 +14889,7 @@
       <c r="IV210" s="1"/>
       <c r="IW210" s="1"/>
     </row>
-    <row r="211" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="5" customFormat="1" ht="12.8">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -14124,7 +15152,7 @@
       <c r="IV211" s="1"/>
       <c r="IW211" s="1"/>
     </row>
-    <row r="212" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" s="5" customFormat="1" ht="12.8">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -14387,7 +15415,7 @@
       <c r="IV212" s="1"/>
       <c r="IW212" s="1"/>
     </row>
-    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" ht="12.8">
       <c r="D213" s="1" t="s">
         <v>85</v>
       </c>
@@ -14642,7 +15670,7 @@
       <c r="IV213" s="1"/>
       <c r="IW213" s="1"/>
     </row>
-    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" ht="12.8">
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
@@ -14891,7 +15919,7 @@
       <c r="IV214" s="1"/>
       <c r="IW214" s="1"/>
     </row>
-    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" ht="12.8">
       <c r="D215" s="1" t="s">
         <v>274</v>
       </c>
@@ -14899,7 +15927,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" ht="12.8">
       <c r="D216" s="1" t="s">
         <v>113</v>
       </c>
@@ -14907,7 +15935,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" ht="12.8">
       <c r="D217" s="1" t="s">
         <v>85</v>
       </c>
@@ -14915,7 +15943,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" ht="12.8">
       <c r="D219" s="1" t="s">
         <v>274</v>
       </c>
@@ -14923,7 +15951,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" ht="12.8">
       <c r="D220" s="1" t="s">
         <v>113</v>
       </c>
@@ -14931,7 +15959,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" ht="12.8">
       <c r="D221" s="1" t="s">
         <v>102</v>
       </c>
@@ -14939,7 +15967,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" ht="12.8">
       <c r="D222" s="1" t="s">
         <v>107</v>
       </c>
@@ -14947,12 +15975,12 @@
         <v>277</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" ht="12.8">
       <c r="D224" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" ht="12.8">
       <c r="D232" s="1" t="s">
         <v>85</v>
       </c>
@@ -14960,7 +15988,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" ht="12.8">
       <c r="D233" s="1" t="s">
         <v>86</v>
       </c>
@@ -14968,7 +15996,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" ht="12.8">
       <c r="D234" s="1" t="s">
         <v>85</v>
       </c>
@@ -14976,7 +16004,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" ht="12.8">
       <c r="D235" s="1" t="s">
         <v>280</v>
       </c>
@@ -14984,8 +16012,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H236" s="1" t="n">
+    <row r="236" ht="147.75">
+      <c r="H236" s="1">
         <v>67</v>
       </c>
       <c r="I236" s="6" t="s">
@@ -14994,8 +16022,11 @@
       <c r="J236" s="6" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K236" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="237" ht="12.8">
       <c r="D237" s="1" t="s">
         <v>90</v>
       </c>
@@ -15003,8 +16034,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H238" s="1" t="n">
+    <row r="238" ht="105.95">
+      <c r="H238" s="1">
         <v>68</v>
       </c>
       <c r="I238" s="6" t="s">
@@ -15013,8 +16044,11 @@
       <c r="J238" s="6" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K238" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="239" ht="12.8">
       <c r="D239" s="1" t="s">
         <v>90</v>
       </c>
@@ -15022,8 +16056,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H240" s="1" t="n">
+    <row r="240" ht="105.95">
+      <c r="H240" s="1">
         <v>69</v>
       </c>
       <c r="I240" s="6" t="s">
@@ -15032,8 +16066,11 @@
       <c r="J240" s="6" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K240" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="241" ht="12.8">
       <c r="D241" s="1" t="s">
         <v>90</v>
       </c>
@@ -15041,17 +16078,17 @@
         <v>88</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" ht="12.8">
       <c r="D242" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" ht="12.8">
       <c r="D243" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" ht="12.8">
       <c r="D244" s="1" t="s">
         <v>84</v>
       </c>
@@ -15059,7 +16096,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" ht="12.8">
       <c r="D245" s="1" t="s">
         <v>85</v>
       </c>
@@ -15067,7 +16104,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" ht="12.8">
       <c r="D246" s="1" t="s">
         <v>274</v>
       </c>
@@ -15075,7 +16112,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" ht="12.8">
       <c r="D247" s="1" t="s">
         <v>113</v>
       </c>
@@ -15083,7 +16120,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" ht="12.8">
       <c r="D248" s="1" t="s">
         <v>288</v>
       </c>
@@ -15091,7 +16128,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" ht="12.8">
       <c r="D249" s="1" t="s">
         <v>272</v>
       </c>
@@ -15099,7 +16136,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" ht="12.8">
       <c r="D250" s="1" t="s">
         <v>85</v>
       </c>
@@ -15107,7 +16144,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" ht="12.8">
       <c r="D251" s="1" t="s">
         <v>86</v>
       </c>
@@ -15115,7 +16152,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" ht="12.8">
       <c r="D252" s="1" t="s">
         <v>85</v>
       </c>
@@ -15123,7 +16160,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" ht="12.8">
       <c r="D253" s="1" t="s">
         <v>63</v>
       </c>
@@ -15131,7 +16168,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" ht="12.8">
       <c r="D254" s="1" t="s">
         <v>113</v>
       </c>
@@ -15139,11 +16176,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" ht="12.8">
       <c r="F255" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H255" s="1" t="n">
+      <c r="H255" s="1">
         <v>70</v>
       </c>
       <c r="I255" s="4" t="s">
@@ -15152,12 +16189,15 @@
       <c r="J255" s="4" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="256" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K255" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="256" ht="22.35">
       <c r="F256" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H256" s="1" t="n">
+      <c r="H256" s="1">
         <v>71</v>
       </c>
       <c r="I256" s="6" t="s">
@@ -15166,12 +16206,15 @@
       <c r="J256" s="6" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="257" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K256" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="257" ht="95.5">
       <c r="F257" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H257" s="1" t="n">
+      <c r="H257" s="1">
         <v>72</v>
       </c>
       <c r="I257" s="6" t="s">
@@ -15180,12 +16223,15 @@
       <c r="J257" s="6" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K257" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="258" ht="12.8">
       <c r="F258" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H258" s="1" t="n">
+      <c r="H258" s="1">
         <v>73</v>
       </c>
       <c r="I258" s="4" t="s">
@@ -15194,12 +16240,15 @@
       <c r="J258" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K258" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="259" ht="12.8">
       <c r="F259" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H259" s="1" t="n">
+      <c r="H259" s="1">
         <v>74</v>
       </c>
       <c r="I259" s="4" t="s">
@@ -15208,12 +16257,15 @@
       <c r="J259" s="4" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K259" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="260" ht="12.8">
       <c r="F260" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H260" s="1" t="n">
+      <c r="H260" s="1">
         <v>75</v>
       </c>
       <c r="I260" s="4" t="s">
@@ -15222,12 +16274,15 @@
       <c r="J260" s="4" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="261" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K260" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="261" ht="53.7">
       <c r="F261" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H261" s="1" t="n">
+      <c r="H261" s="1">
         <v>76</v>
       </c>
       <c r="I261" s="6" t="s">
@@ -15236,12 +16291,15 @@
       <c r="J261" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="262" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K261" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="262" ht="53.7">
       <c r="F262" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H262" s="1" t="n">
+      <c r="H262" s="1">
         <v>77</v>
       </c>
       <c r="I262" s="6" t="s">
@@ -15250,12 +16308,15 @@
       <c r="J262" s="6" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K262" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="263" ht="12.8">
       <c r="F263" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H263" s="1" t="n">
+      <c r="H263" s="1">
         <v>78</v>
       </c>
       <c r="I263" s="4" t="s">
@@ -15264,12 +16325,15 @@
       <c r="J263" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K263" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="264" ht="12.8">
       <c r="F264" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H264" s="1" t="n">
+      <c r="H264" s="1">
         <v>79</v>
       </c>
       <c r="I264" s="4" t="s">
@@ -15278,12 +16342,15 @@
       <c r="J264" s="4" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="265" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K264" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="265" ht="85.05">
       <c r="F265" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H265" s="1" t="n">
+      <c r="H265" s="1">
         <v>80</v>
       </c>
       <c r="I265" s="6" t="s">
@@ -15292,12 +16359,15 @@
       <c r="J265" s="6" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K265" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="266" ht="12.8">
       <c r="F266" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H266" s="1" t="n">
+      <c r="H266" s="1">
         <v>81</v>
       </c>
       <c r="I266" s="4" t="s">
@@ -15306,8 +16376,11 @@
       <c r="J266" s="4" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K266" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="267" ht="12.8">
       <c r="D267" s="1" t="s">
         <v>315</v>
       </c>
@@ -15315,7 +16388,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" ht="12.8">
       <c r="D268" s="1" t="s">
         <v>85</v>
       </c>
@@ -15323,7 +16396,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" ht="12.8">
       <c r="D269" s="1" t="s">
         <v>255</v>
       </c>
@@ -15331,7 +16404,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" ht="12.8">
       <c r="D270" s="1" t="s">
         <v>85</v>
       </c>
@@ -15339,11 +16412,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" ht="53.7">
       <c r="F271" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H271" s="1" t="n">
+      <c r="H271" s="1">
         <v>82</v>
       </c>
       <c r="I271" s="6" t="s">
@@ -15352,8 +16425,11 @@
       <c r="J271" s="6" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K271" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="273" ht="12.8">
       <c r="D273" s="1" t="s">
         <v>102</v>
       </c>
@@ -15361,7 +16437,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" ht="12.8">
       <c r="D274" s="1" t="s">
         <v>103</v>
       </c>
@@ -15369,7 +16445,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" ht="12.8">
       <c r="D275" s="1" t="s">
         <v>107</v>
       </c>
@@ -15377,7 +16453,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" ht="12.8">
       <c r="D276" s="1" t="s">
         <v>85</v>
       </c>
@@ -15385,7 +16461,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" ht="12.8">
       <c r="D277" s="1" t="s">
         <v>321</v>
       </c>
@@ -15393,17 +16469,17 @@
         <v>322</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" ht="12.8">
       <c r="B282" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" ht="12.8">
       <c r="A286" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="1" ht="12.8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -15666,7 +16742,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" ht="12.8">
       <c r="D288" s="1" t="s">
         <v>128</v>
       </c>
@@ -15674,7 +16750,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" ht="12.8">
       <c r="D289" s="1" t="s">
         <v>86</v>
       </c>
@@ -15929,7 +17005,7 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" ht="12.8">
       <c r="D290" s="1" t="s">
         <v>107</v>
       </c>
@@ -15937,7 +17013,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="291" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" s="9" customFormat="1" ht="12.8">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -15947,7 +17023,7 @@
         <v>65</v>
       </c>
       <c r="G291" s="1"/>
-      <c r="H291" s="1" t="n">
+      <c r="H291" s="1">
         <v>83</v>
       </c>
       <c r="I291" s="4" t="s">
@@ -15956,7 +17032,9 @@
       <c r="J291" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="K291" s="1"/>
+      <c r="K291" s="1" t="s">
+        <v>584</v>
+      </c>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
@@ -16204,11 +17282,11 @@
       <c r="IV291" s="1"/>
       <c r="IW291" s="1"/>
     </row>
-    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" ht="12.8">
       <c r="F293" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H293" s="1" t="n">
+      <c r="H293" s="1">
         <v>84</v>
       </c>
       <c r="I293" s="4" t="s">
@@ -16217,7 +17295,9 @@
       <c r="J293" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="K293" s="1"/>
+      <c r="K293" s="1" t="s">
+        <v>585</v>
+      </c>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
@@ -16465,11 +17545,11 @@
       <c r="IV293" s="1"/>
       <c r="IW293" s="1"/>
     </row>
-    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" ht="12.8">
       <c r="F294" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H294" s="1" t="n">
+      <c r="H294" s="1">
         <v>85</v>
       </c>
       <c r="I294" s="4" t="s">
@@ -16478,12 +17558,15 @@
       <c r="J294" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="295" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K294" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="295" ht="43.25">
       <c r="F295" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H295" s="1" t="n">
+      <c r="H295" s="1">
         <v>86</v>
       </c>
       <c r="I295" s="6" t="s">
@@ -16492,12 +17575,15 @@
       <c r="J295" s="6" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K295" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="296" ht="12.8">
       <c r="F296" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H296" s="1" t="n">
+      <c r="H296" s="1">
         <v>87</v>
       </c>
       <c r="I296" s="4" t="s">
@@ -16506,12 +17592,15 @@
       <c r="J296" s="4" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K296" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="297" ht="12.8">
       <c r="F297" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H297" s="1" t="n">
+      <c r="H297" s="1">
         <v>88</v>
       </c>
       <c r="I297" s="4" t="s">
@@ -16520,12 +17609,15 @@
       <c r="J297" s="4" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="298" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K297" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="298" ht="74.6">
       <c r="F298" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H298" s="1" t="n">
+      <c r="H298" s="1">
         <v>89</v>
       </c>
       <c r="I298" s="6" t="s">
@@ -16534,12 +17626,15 @@
       <c r="J298" s="6" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="299" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K298" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="299" ht="95.5">
       <c r="F299" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H299" s="1" t="n">
+      <c r="H299" s="1">
         <v>90</v>
       </c>
       <c r="I299" s="6" t="s">
@@ -16548,12 +17643,15 @@
       <c r="J299" s="6" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K299" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="300" ht="12.8">
       <c r="F300" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H300" s="1" t="n">
+      <c r="H300" s="1">
         <v>91</v>
       </c>
       <c r="I300" s="4" t="s">
@@ -16562,12 +17660,15 @@
       <c r="J300" s="4" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="301" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K300" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="301" ht="53.7">
       <c r="F301" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H301" s="1" t="n">
+      <c r="H301" s="1">
         <v>92</v>
       </c>
       <c r="I301" s="6" t="s">
@@ -16576,12 +17677,15 @@
       <c r="J301" s="6" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K301" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="302" ht="12.8">
       <c r="F302" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H302" s="1" t="n">
+      <c r="H302" s="1">
         <v>93</v>
       </c>
       <c r="I302" s="4" t="s">
@@ -16590,12 +17694,15 @@
       <c r="J302" s="4" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="303" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K302" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="303" ht="85.05">
       <c r="F303" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H303" s="1" t="n">
+      <c r="H303" s="1">
         <v>94</v>
       </c>
       <c r="I303" s="6" t="s">
@@ -16604,12 +17711,15 @@
       <c r="J303" s="6" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K303" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="304" ht="12.8">
       <c r="F304" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H304" s="1" t="n">
+      <c r="H304" s="1">
         <v>95</v>
       </c>
       <c r="I304" s="4" t="s">
@@ -16618,12 +17728,15 @@
       <c r="J304" s="4" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K304" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="305" ht="12.8">
       <c r="F305" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H305" s="1" t="n">
+      <c r="H305" s="1">
         <v>96</v>
       </c>
       <c r="I305" s="4" t="s">
@@ -16632,12 +17745,15 @@
       <c r="J305" s="4" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K305" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="306" ht="12.8">
       <c r="F306" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H306" s="1" t="n">
+      <c r="H306" s="1">
         <v>97</v>
       </c>
       <c r="I306" s="4" t="s">
@@ -16646,12 +17762,15 @@
       <c r="J306" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K306" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="307" ht="12.8">
       <c r="F307" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H307" s="1" t="n">
+      <c r="H307" s="1">
         <v>98</v>
       </c>
       <c r="I307" s="4" t="s">
@@ -16660,12 +17779,15 @@
       <c r="J307" s="4" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K307" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="308" ht="12.8">
       <c r="F308" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H308" s="1" t="n">
+      <c r="H308" s="1">
         <v>99</v>
       </c>
       <c r="I308" s="4" t="s">
@@ -16674,12 +17796,15 @@
       <c r="J308" s="4" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K308" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="309" ht="12.8">
       <c r="F309" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H309" s="1" t="n">
+      <c r="H309" s="1">
         <v>100</v>
       </c>
       <c r="I309" s="4" t="s">
@@ -16688,12 +17813,15 @@
       <c r="J309" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="310" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K309" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="310" ht="53.7">
       <c r="F310" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H310" s="1" t="n">
+      <c r="H310" s="1">
         <v>101</v>
       </c>
       <c r="I310" s="6" t="s">
@@ -16702,8 +17830,11 @@
       <c r="J310" s="6" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K310" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="311" ht="12.8">
       <c r="D311" s="1" t="s">
         <v>84</v>
       </c>
@@ -16711,22 +17842,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" ht="12.8">
       <c r="D312" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" ht="12.8">
       <c r="B313" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" ht="12.8">
       <c r="A317" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" ht="12.8">
       <c r="D318" s="1" t="s">
         <v>63</v>
       </c>
@@ -16734,7 +17865,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" ht="12.8">
       <c r="D319" s="1" t="s">
         <v>102</v>
       </c>
@@ -16742,7 +17873,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" ht="12.8">
       <c r="D320" s="1" t="s">
         <v>128</v>
       </c>
@@ -16750,7 +17881,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" ht="12.8">
       <c r="D321" s="1" t="s">
         <v>86</v>
       </c>
@@ -16758,7 +17889,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" ht="12.8">
       <c r="D322" s="1" t="s">
         <v>107</v>
       </c>
@@ -16766,7 +17897,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="323" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" s="9" customFormat="1" ht="12.8">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -16774,14 +17905,16 @@
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
-      <c r="H323" s="1" t="n">
+      <c r="H323" s="1">
         <v>106</v>
       </c>
       <c r="I323" s="6" t="s">
         <v>357</v>
       </c>
       <c r="J323" s="4"/>
-      <c r="K323" s="1"/>
+      <c r="K323" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
@@ -17029,22 +18162,27 @@
       <c r="IV323" s="1"/>
       <c r="IW323" s="1"/>
     </row>
-    <row r="324" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H324" s="1" t="n">
+    <row r="324" ht="32.8">
+      <c r="H324" s="1">
         <v>107</v>
       </c>
       <c r="I324" s="6" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H325" s="1" t="n">
+      <c r="K324" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="325" ht="12.8">
+      <c r="H325" s="1">
         <v>108</v>
       </c>
       <c r="I325" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="K325" s="1"/>
+      <c r="K325" s="1" t="s">
+        <v>602</v>
+      </c>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
@@ -17292,39 +18430,51 @@
       <c r="IV325" s="1"/>
       <c r="IW325" s="1"/>
     </row>
-    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H326" s="1" t="n">
+    <row r="326" ht="12.8">
+      <c r="H326" s="1">
         <v>109</v>
       </c>
       <c r="I326" s="4" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="327" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H327" s="1" t="n">
+      <c r="K326" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="327" ht="22.35">
+      <c r="H327" s="1">
         <v>110</v>
       </c>
       <c r="I327" s="6" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H328" s="1" t="n">
+      <c r="K327" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="328" ht="12.8">
+      <c r="H328" s="1">
         <v>111</v>
       </c>
       <c r="I328" s="4" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H329" s="1" t="n">
+      <c r="K328" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="329" ht="12.8">
+      <c r="H329" s="1">
         <v>112</v>
       </c>
       <c r="I329" s="4" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K329" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="330" ht="12.8">
       <c r="D330" s="1" t="s">
         <v>84</v>
       </c>
@@ -17332,7 +18482,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" ht="12.8">
       <c r="D333" s="1" t="s">
         <v>102</v>
       </c>
@@ -17340,7 +18490,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" ht="12.8">
       <c r="D334" s="1" t="s">
         <v>128</v>
       </c>
@@ -17348,7 +18498,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" ht="12.8">
       <c r="D335" s="1" t="s">
         <v>86</v>
       </c>
@@ -17356,7 +18506,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="337" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="9" customFormat="1" ht="12.8">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -17619,7 +18769,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="338" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" s="9" customFormat="1" ht="12.8">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -17878,17 +19028,19 @@
       <c r="IV338" s="1"/>
       <c r="IW338" s="1"/>
     </row>
-    <row r="339" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" ht="32.8">
       <c r="F339" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H339" s="1" t="n">
+      <c r="H339" s="1">
         <v>113</v>
       </c>
       <c r="I339" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="K339" s="1"/>
+      <c r="K339" s="1" t="s">
+        <v>607</v>
+      </c>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
@@ -18136,17 +19288,19 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" ht="12.8">
       <c r="F340" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H340" s="1" t="n">
+      <c r="H340" s="1">
         <v>114</v>
       </c>
       <c r="I340" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="K340" s="1"/>
+      <c r="K340" s="1" t="s">
+        <v>608</v>
+      </c>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
@@ -18394,29 +19548,35 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" ht="12.8">
       <c r="F341" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H341" s="1" t="n">
+      <c r="H341" s="1">
         <v>115</v>
       </c>
       <c r="I341" s="4" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K341" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="342" ht="12.8">
       <c r="F342" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H342" s="1" t="n">
+      <c r="H342" s="1">
         <v>116</v>
       </c>
       <c r="I342" s="4" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K342" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="343" ht="12.8">
       <c r="D343" s="1" t="s">
         <v>84</v>
       </c>
@@ -18424,62 +19584,77 @@
         <v>83</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" ht="12.8">
       <c r="F344" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H344" s="1" t="n">
+      <c r="H344" s="1">
         <v>117</v>
       </c>
       <c r="I344" s="4" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K344" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="345" ht="12.8">
       <c r="F345" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H345" s="1" t="n">
+      <c r="H345" s="1">
         <v>118</v>
       </c>
       <c r="I345" s="4" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K345" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="346" ht="12.8">
       <c r="F346" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H346" s="1" t="n">
+      <c r="H346" s="1">
         <v>119</v>
       </c>
       <c r="I346" s="4" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K346" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="347" ht="12.8">
       <c r="F347" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H347" s="1" t="n">
+      <c r="H347" s="1">
         <v>120</v>
       </c>
       <c r="I347" s="4" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K347" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="348" ht="12.8">
       <c r="F348" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H348" s="1" t="n">
+      <c r="H348" s="1">
         <v>121</v>
       </c>
       <c r="I348" s="4" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K348" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="349" ht="12.8">
       <c r="D349" s="1" t="s">
         <v>86</v>
       </c>
@@ -18487,18 +19662,21 @@
         <v>375</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" ht="12.8">
       <c r="F350" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H350" s="1" t="n">
+      <c r="H350" s="1">
         <v>122</v>
       </c>
       <c r="I350" s="4" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="351" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K350" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="351" s="9" customFormat="1" ht="12.8">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -18757,7 +19935,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" ht="12.8">
       <c r="D353" s="1" t="s">
         <v>102</v>
       </c>
@@ -19012,7 +20190,7 @@
       <c r="IV353" s="1"/>
       <c r="IW353" s="1"/>
     </row>
-    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" ht="12.8">
       <c r="D354" s="1" t="s">
         <v>128</v>
       </c>
@@ -19020,7 +20198,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" ht="12.8">
       <c r="A355" s="1" t="s">
         <v>97</v>
       </c>
@@ -19031,7 +20209,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" ht="12.8">
       <c r="D356" s="1" t="s">
         <v>107</v>
       </c>
@@ -19039,7 +20217,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="357" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" s="5" customFormat="1" ht="12.8">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -19298,18 +20476,21 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" ht="12.8">
       <c r="F358" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H358" s="1" t="n">
+      <c r="H358" s="1">
         <v>123</v>
       </c>
       <c r="I358" s="4" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K358" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="359" ht="12.8">
       <c r="K359" s="1"/>
       <c r="L359" s="1"/>
       <c r="M359" s="1"/>
@@ -19558,7 +20739,7 @@
       <c r="IV359" s="1"/>
       <c r="IW359" s="1"/>
     </row>
-    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" ht="12.8">
       <c r="D360" s="1" t="s">
         <v>102</v>
       </c>
@@ -19566,7 +20747,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" ht="12.8">
       <c r="D361" s="1" t="s">
         <v>128</v>
       </c>
@@ -19574,7 +20755,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" ht="12.8">
       <c r="A362" s="1" t="s">
         <v>97</v>
       </c>
@@ -19585,7 +20766,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" ht="12.8">
       <c r="D363" s="1" t="s">
         <v>107</v>
       </c>
@@ -19593,7 +20774,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="364" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" s="5" customFormat="1" ht="12.8">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -19603,14 +20784,16 @@
         <v>72</v>
       </c>
       <c r="G364" s="1"/>
-      <c r="H364" s="1" t="n">
+      <c r="H364" s="1">
         <v>124</v>
       </c>
       <c r="I364" s="4" t="s">
         <v>379</v>
       </c>
       <c r="J364" s="4"/>
-      <c r="K364" s="1"/>
+      <c r="K364" s="1" t="s">
+        <v>618</v>
+      </c>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
       <c r="N364" s="1"/>
@@ -19858,28 +21041,33 @@
       <c r="IV364" s="1"/>
       <c r="IW364" s="1"/>
     </row>
-    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" ht="12.8">
       <c r="F365" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H365" s="1" t="n">
+      <c r="H365" s="1">
         <v>125</v>
       </c>
       <c r="I365" s="4" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K365" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="366" ht="12.8">
       <c r="F366" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H366" s="1" t="n">
+      <c r="H366" s="1">
         <v>126</v>
       </c>
       <c r="I366" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="K366" s="1"/>
+      <c r="K366" s="1" t="s">
+        <v>620</v>
+      </c>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
       <c r="N366" s="1"/>
@@ -20127,139 +21315,175 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" ht="12.8">
       <c r="F367" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H367" s="1" t="n">
+      <c r="H367" s="1">
         <v>127</v>
       </c>
       <c r="I367" s="4" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="368" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K367" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="368" ht="32.8">
       <c r="F368" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H368" s="1" t="n">
+      <c r="H368" s="1">
         <v>128</v>
       </c>
       <c r="I368" s="6" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="369" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K368" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="369" ht="53.7">
       <c r="F369" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H369" s="1" t="n">
+      <c r="H369" s="1">
         <v>129</v>
       </c>
       <c r="I369" s="6" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="370" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K369" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="370" ht="32.8">
       <c r="F370" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H370" s="1" t="n">
+      <c r="H370" s="1">
         <v>130</v>
       </c>
       <c r="I370" s="6" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K370" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="371" ht="12.8">
       <c r="F371" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H371" s="1" t="n">
+      <c r="H371" s="1">
         <v>131</v>
       </c>
       <c r="I371" s="4" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K371" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="372" ht="12.8">
       <c r="F372" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H372" s="1" t="n">
+      <c r="H372" s="1">
         <v>132</v>
       </c>
       <c r="I372" s="4" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K372" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="373" ht="12.8">
       <c r="F373" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H373" s="1" t="n">
+      <c r="H373" s="1">
         <v>133</v>
       </c>
       <c r="I373" s="4" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K373" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="374" ht="12.8">
       <c r="F374" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H374" s="1" t="n">
+      <c r="H374" s="1">
         <v>134</v>
       </c>
       <c r="I374" s="4" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="375" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K374" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="375" ht="43.25">
       <c r="F375" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H375" s="1" t="n">
+      <c r="H375" s="1">
         <v>135</v>
       </c>
       <c r="I375" s="6" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K375" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="376" ht="12.8">
       <c r="F376" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H376" s="1" t="n">
+      <c r="H376" s="1">
         <v>136</v>
       </c>
       <c r="I376" s="4" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K376" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="377" ht="12.8">
       <c r="F377" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H377" s="1" t="n">
+      <c r="H377" s="1">
         <v>137</v>
       </c>
       <c r="I377" s="4" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K377" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="378" ht="12.8">
       <c r="F378" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H378" s="1" t="n">
+      <c r="H378" s="1">
         <v>138</v>
       </c>
       <c r="I378" s="4" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K378" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="379" ht="12.8">
       <c r="D379" s="1" t="s">
         <v>84</v>
       </c>
@@ -20267,7 +21491,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" ht="12.8">
       <c r="D380" s="1" t="s">
         <v>134</v>
       </c>
@@ -20275,21 +21499,24 @@
         <v>394</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" ht="22.35">
       <c r="A381" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H381" s="1" t="n">
+      <c r="H381" s="1">
         <v>139</v>
       </c>
       <c r="I381" s="6" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K381" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="382" ht="12.8">
       <c r="D382" s="1" t="s">
         <v>85</v>
       </c>
@@ -20297,7 +21524,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" ht="12.8">
       <c r="D383" s="1" t="s">
         <v>63</v>
       </c>
@@ -20305,7 +21532,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" ht="12.8">
       <c r="D384" s="1" t="s">
         <v>102</v>
       </c>
@@ -20313,7 +21540,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" ht="12.8">
       <c r="D385" s="1" t="s">
         <v>128</v>
       </c>
@@ -20321,7 +21548,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" ht="12.8">
       <c r="A386" s="1" t="s">
         <v>97</v>
       </c>
@@ -20332,7 +21559,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" ht="12.8">
       <c r="D387" s="1" t="s">
         <v>107</v>
       </c>
@@ -20340,7 +21567,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="388" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" s="5" customFormat="1" ht="12.8">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -20348,14 +21575,16 @@
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
-      <c r="H388" s="1" t="n">
+      <c r="H388" s="1">
         <v>140</v>
       </c>
       <c r="I388" s="4" t="s">
         <v>396</v>
       </c>
       <c r="J388" s="4"/>
-      <c r="K388" s="1"/>
+      <c r="K388" s="1" t="s">
+        <v>634</v>
+      </c>
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
       <c r="N388" s="1"/>
@@ -20603,22 +21832,27 @@
       <c r="IV388" s="1"/>
       <c r="IW388" s="1"/>
     </row>
-    <row r="389" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H389" s="1" t="n">
+    <row r="389" ht="22.35">
+      <c r="H389" s="1">
         <v>141</v>
       </c>
       <c r="I389" s="6" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H390" s="1" t="n">
+      <c r="K389" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="390" ht="12.8">
+      <c r="H390" s="1">
         <v>142</v>
       </c>
       <c r="I390" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="K390" s="1"/>
+      <c r="K390" s="1" t="s">
+        <v>636</v>
+      </c>
       <c r="L390" s="1"/>
       <c r="M390" s="1"/>
       <c r="N390" s="1"/>
@@ -20866,23 +22100,29 @@
       <c r="IV390" s="1"/>
       <c r="IW390" s="1"/>
     </row>
-    <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H391" s="1" t="n">
+    <row r="391" ht="12.8">
+      <c r="H391" s="1">
         <v>143</v>
       </c>
       <c r="I391" s="4" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H392" s="1" t="n">
+      <c r="K391" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="392" ht="12.8">
+      <c r="H392" s="1">
         <v>144</v>
       </c>
       <c r="I392" s="4" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K392" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="394" ht="12.8">
       <c r="D394" s="1" t="s">
         <v>84</v>
       </c>
@@ -20890,17 +22130,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" ht="12.8">
       <c r="D395" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" ht="12.8">
       <c r="B396" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="399" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" s="5" customFormat="1" ht="12.8">
       <c r="A399" s="1" t="s">
         <v>43</v>
       </c>
@@ -21161,7 +22401,7 @@
       <c r="IV399" s="1"/>
       <c r="IW399" s="1"/>
     </row>
-    <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" ht="12.8">
       <c r="D401" s="1" t="s">
         <v>102</v>
       </c>
@@ -21416,7 +22656,7 @@
       <c r="IV401" s="1"/>
       <c r="IW401" s="1"/>
     </row>
-    <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" ht="12.8">
       <c r="D402" s="1" t="s">
         <v>128</v>
       </c>
@@ -21424,7 +22664,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" ht="12.8">
       <c r="D403" s="1" t="s">
         <v>86</v>
       </c>
@@ -21432,7 +22672,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="405" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" s="9" customFormat="1" ht="12.8">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -21695,7 +22935,7 @@
       <c r="IV405" s="1"/>
       <c r="IW405" s="1"/>
     </row>
-    <row r="406" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" s="9" customFormat="1" ht="12.8">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -21705,14 +22945,16 @@
         <v>65</v>
       </c>
       <c r="G406" s="1"/>
-      <c r="H406" s="1" t="n">
+      <c r="H406" s="1">
         <v>145</v>
       </c>
       <c r="I406" s="4" t="s">
         <v>403</v>
       </c>
       <c r="J406" s="4"/>
-      <c r="K406" s="1"/>
+      <c r="K406" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="L406" s="1"/>
       <c r="M406" s="1"/>
       <c r="N406" s="1"/>
@@ -21960,17 +23202,19 @@
       <c r="IV406" s="1"/>
       <c r="IW406" s="1"/>
     </row>
-    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" ht="12.8">
       <c r="F407" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H407" s="1" t="n">
+      <c r="H407" s="1">
         <v>146</v>
       </c>
       <c r="I407" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="K407" s="1"/>
+      <c r="K407" s="1" t="s">
+        <v>640</v>
+      </c>
       <c r="L407" s="1"/>
       <c r="M407" s="1"/>
       <c r="N407" s="1"/>
@@ -22218,17 +23462,19 @@
       <c r="IV407" s="1"/>
       <c r="IW407" s="1"/>
     </row>
-    <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" ht="12.8">
       <c r="F408" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H408" s="1" t="n">
+      <c r="H408" s="1">
         <v>147</v>
       </c>
       <c r="I408" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="K408" s="1"/>
+      <c r="K408" s="1" t="s">
+        <v>641</v>
+      </c>
       <c r="L408" s="1"/>
       <c r="M408" s="1"/>
       <c r="N408" s="1"/>
@@ -22476,73 +23722,91 @@
       <c r="IV408" s="1"/>
       <c r="IW408" s="1"/>
     </row>
-    <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" ht="12.8">
       <c r="F409" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H409" s="1" t="n">
+      <c r="H409" s="1">
         <v>148</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="410" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K409" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="410" ht="74.6">
       <c r="F410" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H410" s="1" t="n">
+      <c r="H410" s="1">
         <v>149</v>
       </c>
       <c r="I410" s="6" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K410" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="411" ht="12.8">
       <c r="F411" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H411" s="1" t="n">
+      <c r="H411" s="1">
         <v>150</v>
       </c>
       <c r="I411" s="4" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K411" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="412" ht="12.8">
       <c r="F412" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H412" s="1" t="n">
+      <c r="H412" s="1">
         <v>151</v>
       </c>
       <c r="I412" s="4" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K412" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="413" ht="12.8">
       <c r="F413" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H413" s="1" t="n">
+      <c r="H413" s="1">
         <v>152</v>
       </c>
       <c r="I413" s="4" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K413" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="414" ht="12.8">
       <c r="F414" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H414" s="1" t="n">
+      <c r="H414" s="1">
         <v>153</v>
       </c>
       <c r="I414" s="4" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K414" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="415" ht="12.8">
       <c r="D415" s="1" t="s">
         <v>86</v>
       </c>
@@ -22550,7 +23814,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" ht="12.8">
       <c r="D416" s="1" t="s">
         <v>63</v>
       </c>
@@ -22558,7 +23822,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="417" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" s="9" customFormat="1" ht="12.8">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -22821,7 +24085,7 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" ht="12.8">
       <c r="D418" s="1" t="s">
         <v>128</v>
       </c>
@@ -22829,7 +24093,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" ht="12.8">
       <c r="D419" s="1" t="s">
         <v>107</v>
       </c>
@@ -23084,23 +24348,29 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H420" s="1" t="n">
+    <row r="420" ht="12.8">
+      <c r="H420" s="1">
         <v>154</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H421" s="1" t="n">
+      <c r="K420" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="421" ht="12.8">
+      <c r="H421" s="1">
         <v>155</v>
       </c>
       <c r="I421" s="4" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K421" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="422" ht="12.8">
       <c r="D422" s="1" t="s">
         <v>102</v>
       </c>
@@ -23108,7 +24378,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" ht="12.8">
       <c r="D423" s="1" t="s">
         <v>128</v>
       </c>
@@ -23116,7 +24386,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" ht="12.8">
       <c r="D424" s="1" t="s">
         <v>107</v>
       </c>
@@ -23124,45 +24394,54 @@
         <v>88</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" ht="12.8">
       <c r="D425" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" ht="12.8">
       <c r="F427" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H427" s="1" t="n">
+      <c r="H427" s="1">
         <v>156</v>
       </c>
       <c r="I427" s="4" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K427" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="429" ht="12.8">
       <c r="F429" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H429" s="1" t="n">
+      <c r="H429" s="1">
         <v>157</v>
       </c>
       <c r="I429" s="4" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K429" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="430" ht="12.8">
       <c r="F430" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H430" s="1" t="n">
+      <c r="H430" s="1">
         <v>158</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K430" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="432" ht="12.8">
       <c r="D432" s="1" t="s">
         <v>63</v>
       </c>
@@ -23170,7 +24449,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" ht="12.8">
       <c r="D433" s="1" t="s">
         <v>102</v>
       </c>
@@ -23178,7 +24457,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" ht="12.8">
       <c r="D434" s="1" t="s">
         <v>128</v>
       </c>
@@ -23186,7 +24465,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" ht="12.8">
       <c r="D435" s="1" t="s">
         <v>107</v>
       </c>
@@ -23194,15 +24473,18 @@
         <v>88</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H436" s="1" t="n">
+    <row r="436" ht="22.35">
+      <c r="H436" s="1">
         <v>159</v>
       </c>
       <c r="I436" s="6" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K436" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="437" ht="12.8">
       <c r="D437" s="1" t="s">
         <v>102</v>
       </c>
@@ -23210,7 +24492,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" ht="12.8">
       <c r="D438" s="1" t="s">
         <v>128</v>
       </c>
@@ -23218,7 +24500,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" ht="12.8">
       <c r="D439" s="1" t="s">
         <v>107</v>
       </c>
@@ -23226,7 +24508,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" ht="12.8">
       <c r="D440" s="1" t="s">
         <v>63</v>
       </c>
@@ -23234,40 +24516,49 @@
         <v>112</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" ht="32.8">
       <c r="F442" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H442" s="1" t="n">
+      <c r="H442" s="1">
         <v>160</v>
       </c>
       <c r="I442" s="6" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K442" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="443" ht="12.8">
       <c r="F443" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H443" s="1" t="n">
+      <c r="H443" s="1">
         <v>161</v>
       </c>
       <c r="I443" s="4" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K443" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="444" ht="12.8">
       <c r="F444" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H444" s="1" t="n">
+      <c r="H444" s="1">
         <v>162</v>
       </c>
       <c r="I444" s="4" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K444" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="446" ht="12.8">
       <c r="D446" s="1" t="s">
         <v>63</v>
       </c>
@@ -23275,7 +24566,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" ht="12.8">
       <c r="D447" s="1" t="s">
         <v>102</v>
       </c>
@@ -23283,7 +24574,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" ht="12.8">
       <c r="D448" s="1" t="s">
         <v>128</v>
       </c>
@@ -23291,7 +24582,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" ht="12.8">
       <c r="D449" s="1" t="s">
         <v>107</v>
       </c>
@@ -23299,31 +24590,40 @@
         <v>88</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H450" s="1" t="n">
+    <row r="450" ht="12.8">
+      <c r="H450" s="1">
         <v>163</v>
       </c>
       <c r="I450" s="4" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="451" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H451" s="1" t="n">
+      <c r="K450" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="451" ht="32.8">
+      <c r="H451" s="1">
         <v>164</v>
       </c>
       <c r="I451" s="6" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H452" s="1" t="n">
+      <c r="K451" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="452" ht="12.8">
+      <c r="H452" s="1">
         <v>165</v>
       </c>
       <c r="I452" s="4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K452" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="453" ht="12.8">
       <c r="D453" s="1" t="s">
         <v>84</v>
       </c>
@@ -23331,31 +24631,40 @@
         <v>83</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H454" s="1" t="n">
+    <row r="454" ht="12.8">
+      <c r="H454" s="1">
         <v>166</v>
       </c>
       <c r="I454" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H456" s="1" t="n">
+      <c r="K454" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="456" ht="12.8">
+      <c r="H456" s="1">
         <v>167</v>
       </c>
       <c r="I456" s="4" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H457" s="1" t="n">
+      <c r="K456" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="457" ht="12.8">
+      <c r="H457" s="1">
         <v>168</v>
       </c>
       <c r="I457" s="4" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K457" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="460" ht="12.8">
       <c r="D460" s="1" t="s">
         <v>86</v>
       </c>
@@ -23363,15 +24672,18 @@
         <v>375</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H461" s="1" t="n">
+    <row r="461" ht="12.8">
+      <c r="H461" s="1">
         <v>169</v>
       </c>
       <c r="I461" s="4" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="462" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K461" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="462" s="9" customFormat="1" ht="12.8">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -23634,7 +24946,7 @@
       <c r="IV462" s="1"/>
       <c r="IW462" s="1"/>
     </row>
-    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" ht="12.8">
       <c r="D463" s="1" t="s">
         <v>128</v>
       </c>
@@ -23642,7 +24954,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" ht="12.8">
       <c r="A464" s="1" t="s">
         <v>97</v>
       </c>
@@ -23900,7 +25212,7 @@
       <c r="IV464" s="1"/>
       <c r="IW464" s="1"/>
     </row>
-    <row r="466" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" s="5" customFormat="1" ht="12.8">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -24163,7 +25475,7 @@
       <c r="IV466" s="1"/>
       <c r="IW466" s="1"/>
     </row>
-    <row r="467" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" s="9" customFormat="1" ht="12.8">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -24422,7 +25734,7 @@
       <c r="IV467" s="1"/>
       <c r="IW467" s="1"/>
     </row>
-    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" ht="12.8">
       <c r="D468" s="1" t="s">
         <v>63</v>
       </c>
@@ -24677,17 +25989,19 @@
       <c r="IV468" s="1"/>
       <c r="IW468" s="1"/>
     </row>
-    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" ht="12.8">
       <c r="F469" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H469" s="1" t="n">
+      <c r="H469" s="1">
         <v>170</v>
       </c>
       <c r="I469" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="K469" s="1"/>
+      <c r="K469" s="1" t="s">
+        <v>662</v>
+      </c>
       <c r="L469" s="1"/>
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
@@ -24935,62 +26249,77 @@
       <c r="IV469" s="1"/>
       <c r="IW469" s="1"/>
     </row>
-    <row r="470" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" ht="32.8">
       <c r="F470" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H470" s="1" t="n">
+      <c r="H470" s="1">
         <v>171</v>
       </c>
       <c r="I470" s="6" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K470" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="471" ht="12.8">
       <c r="F471" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H471" s="1" t="n">
+      <c r="H471" s="1">
         <v>172</v>
       </c>
       <c r="I471" s="4" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K471" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="472" ht="12.8">
       <c r="F472" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H472" s="1" t="n">
+      <c r="H472" s="1">
         <v>173</v>
       </c>
       <c r="I472" s="4" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K472" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="473" ht="12.8">
       <c r="F473" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H473" s="1" t="n">
+      <c r="H473" s="1">
         <v>174</v>
       </c>
       <c r="I473" s="4" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K473" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="474" ht="12.8">
       <c r="F474" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H474" s="1" t="n">
+      <c r="H474" s="1">
         <v>175</v>
       </c>
       <c r="I474" s="4" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K474" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="476" ht="12.8">
       <c r="D476" s="1" t="s">
         <v>102</v>
       </c>
@@ -24998,7 +26327,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" ht="12.8">
       <c r="D477" s="1" t="s">
         <v>128</v>
       </c>
@@ -25006,7 +26335,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" ht="12.8">
       <c r="D478" s="1" t="s">
         <v>86</v>
       </c>
@@ -25014,7 +26343,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="480" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" s="9" customFormat="1" ht="12.8">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -25277,7 +26606,7 @@
       <c r="IV480" s="1"/>
       <c r="IW480" s="1"/>
     </row>
-    <row r="481" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" s="9" customFormat="1" ht="12.8">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -25287,14 +26616,16 @@
         <v>9</v>
       </c>
       <c r="G481" s="1"/>
-      <c r="H481" s="1" t="n">
+      <c r="H481" s="1">
         <v>176</v>
       </c>
       <c r="I481" s="4" t="s">
         <v>436</v>
       </c>
       <c r="J481" s="4"/>
-      <c r="K481" s="1"/>
+      <c r="K481" s="1" t="s">
+        <v>668</v>
+      </c>
       <c r="L481" s="1"/>
       <c r="M481" s="1"/>
       <c r="N481" s="1"/>
@@ -25542,17 +26873,19 @@
       <c r="IV481" s="1"/>
       <c r="IW481" s="1"/>
     </row>
-    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" ht="12.8">
       <c r="F482" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H482" s="1" t="n">
+      <c r="H482" s="1">
         <v>177</v>
       </c>
       <c r="I482" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="K482" s="1"/>
+      <c r="K482" s="1" t="s">
+        <v>669</v>
+      </c>
       <c r="L482" s="1"/>
       <c r="M482" s="1"/>
       <c r="N482" s="1"/>
@@ -25800,7 +27133,7 @@
       <c r="IV482" s="1"/>
       <c r="IW482" s="1"/>
     </row>
-    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" ht="12.8">
       <c r="K483" s="1"/>
       <c r="L483" s="1"/>
       <c r="M483" s="1"/>
@@ -26049,7 +27382,7 @@
       <c r="IV483" s="1"/>
       <c r="IW483" s="1"/>
     </row>
-    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" ht="12.8">
       <c r="D485" s="1" t="s">
         <v>84</v>
       </c>
@@ -26057,17 +27390,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" ht="12.8">
       <c r="D486" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" ht="12.8">
       <c r="B487" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="490" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" s="5" customFormat="1" ht="12.8">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -26326,7 +27659,7 @@
       <c r="IV490" s="1"/>
       <c r="IW490" s="1"/>
     </row>
-    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" ht="12.8">
       <c r="K492" s="1"/>
       <c r="L492" s="1"/>
       <c r="M492" s="1"/>
@@ -26577,12 +27910,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -26590,23 +27923,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IV160"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.26"/>
+    <col min="1" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="53.26" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -26641,13 +27974,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>61</v>
       </c>
@@ -26655,7 +27988,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>61</v>
       </c>
@@ -26663,7 +27996,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>61</v>
       </c>
@@ -26671,12 +28004,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="1" t="s">
         <v>63</v>
       </c>
@@ -26684,17 +28017,17 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>102</v>
       </c>
@@ -26702,7 +28035,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>128</v>
       </c>
@@ -26710,7 +28043,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>86</v>
       </c>
@@ -26964,7 +28297,7 @@
       <c r="IU18" s="1"/>
       <c r="IV18" s="1"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>107</v>
       </c>
@@ -26972,7 +28305,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="9" customFormat="1" ht="12.8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -27230,7 +28563,7 @@
       <c r="IU20" s="1"/>
       <c r="IV20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="I21" s="1" t="s">
         <v>442</v>
       </c>
@@ -27238,7 +28571,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -27486,7 +28819,7 @@
       <c r="IU22" s="1"/>
       <c r="IV22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>128</v>
       </c>
@@ -27494,7 +28827,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="I25" s="1" t="s">
         <v>444</v>
       </c>
@@ -27502,7 +28835,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="A26" s="1" t="s">
         <v>97</v>
       </c>
@@ -27513,7 +28846,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="D27" s="1" t="s">
         <v>90</v>
       </c>
@@ -27521,17 +28854,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="D34" s="1" t="s">
         <v>102</v>
       </c>
@@ -27539,7 +28872,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="D35" s="1" t="s">
         <v>128</v>
       </c>
@@ -27547,7 +28880,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="D36" s="1" t="s">
         <v>86</v>
       </c>
@@ -27801,7 +29134,7 @@
       <c r="IU36" s="1"/>
       <c r="IV36" s="1"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="D37" s="1" t="s">
         <v>107</v>
       </c>
@@ -27809,7 +29142,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="9" customFormat="1" ht="12.8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -28067,7 +29400,7 @@
       <c r="IU38" s="1"/>
       <c r="IV38" s="1"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="I39" s="1" t="s">
         <v>445</v>
       </c>
@@ -28075,7 +29408,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -28323,7 +29656,7 @@
       <c r="IU40" s="1"/>
       <c r="IV40" s="1"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="D41" s="1" t="s">
         <v>90</v>
       </c>
@@ -28331,17 +29664,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="B43" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="A47" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="D49" s="1" t="s">
         <v>102</v>
       </c>
@@ -28349,7 +29682,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="D50" s="1" t="s">
         <v>128</v>
       </c>
@@ -28357,7 +29690,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="D51" s="1" t="s">
         <v>86</v>
       </c>
@@ -28611,7 +29944,7 @@
       <c r="IU51" s="1"/>
       <c r="IV51" s="1"/>
     </row>
-    <row r="52" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="9" customFormat="1" ht="12.8">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -28873,7 +30206,7 @@
       <c r="IU52" s="1"/>
       <c r="IV52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.8">
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -29121,8 +30454,8 @@
       <c r="IU53" s="1"/>
       <c r="IV53" s="1"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H54" s="1" t="n">
+    <row r="54" ht="12.8">
+      <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -29131,8 +30464,11 @@
       <c r="J54" s="1" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="55" ht="12.8">
       <c r="D55" s="1" t="s">
         <v>134</v>
       </c>
@@ -29386,8 +30722,8 @@
       <c r="IU55" s="1"/>
       <c r="IV55" s="1"/>
     </row>
-    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H56" s="1" t="n">
+    <row r="56" ht="74.6">
+      <c r="H56" s="1">
         <v>2</v>
       </c>
       <c r="I56" s="10" t="s">
@@ -29396,9 +30732,12 @@
       <c r="J56" s="10" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H57" s="1" t="n">
+      <c r="K56" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="57" ht="64.15">
+      <c r="H57" s="1">
         <v>3</v>
       </c>
       <c r="I57" s="10" t="s">
@@ -29407,8 +30746,11 @@
       <c r="J57" s="10" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="58" ht="12.8">
       <c r="D58" s="1" t="s">
         <v>134</v>
       </c>
@@ -29416,8 +30758,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H59" s="1" t="n">
+    <row r="59" ht="74.6">
+      <c r="H59" s="1">
         <v>4</v>
       </c>
       <c r="I59" s="10" t="s">
@@ -29426,9 +30768,12 @@
       <c r="J59" s="10" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H60" s="1" t="n">
+      <c r="K59" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="60" ht="32.8">
+      <c r="H60" s="1">
         <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
@@ -29437,9 +30782,12 @@
       <c r="J60" s="10" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H61" s="1" t="n">
+      <c r="K60" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="61" ht="22.35">
+      <c r="H61" s="1">
         <v>6</v>
       </c>
       <c r="I61" s="10" t="s">
@@ -29448,8 +30796,11 @@
       <c r="J61" s="10" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="62" ht="12.8">
       <c r="D62" s="1" t="s">
         <v>134</v>
       </c>
@@ -29457,8 +30808,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H63" s="1" t="n">
+    <row r="63" ht="85.05">
+      <c r="H63" s="1">
         <v>7</v>
       </c>
       <c r="I63" s="10" t="s">
@@ -29467,9 +30818,12 @@
       <c r="J63" s="10" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H64" s="1" t="n">
+      <c r="K63" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="64" ht="53.7">
+      <c r="H64" s="1">
         <v>8</v>
       </c>
       <c r="I64" s="10" t="s">
@@ -29478,9 +30832,12 @@
       <c r="J64" s="10" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H65" s="1" t="n">
+      <c r="K64" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="65" ht="22.35">
+      <c r="H65" s="1">
         <v>9</v>
       </c>
       <c r="I65" s="10" t="s">
@@ -29489,9 +30846,12 @@
       <c r="J65" s="10" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+      <c r="K65" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="66" ht="43.25">
+      <c r="H66" s="1">
         <v>10</v>
       </c>
       <c r="I66" s="10" t="s">
@@ -29500,8 +30860,11 @@
       <c r="J66" s="10" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="68" ht="12.8">
       <c r="D68" s="1" t="s">
         <v>84</v>
       </c>
@@ -29509,22 +30872,22 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="D69" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="B70" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.8">
       <c r="A75" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.8">
       <c r="D77" s="1" t="s">
         <v>102</v>
       </c>
@@ -29532,7 +30895,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="D78" s="1" t="s">
         <v>128</v>
       </c>
@@ -29540,7 +30903,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.8">
       <c r="D79" s="1" t="s">
         <v>86</v>
       </c>
@@ -29794,7 +31157,7 @@
       <c r="IU79" s="1"/>
       <c r="IV79" s="1"/>
     </row>
-    <row r="80" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" s="9" customFormat="1" ht="12.8">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -30056,7 +31419,7 @@
       <c r="IU80" s="1"/>
       <c r="IV80" s="1"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.8">
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -30304,8 +31667,8 @@
       <c r="IU81" s="1"/>
       <c r="IV81" s="1"/>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H82" s="1" t="n">
+    <row r="82" ht="12.8">
+      <c r="H82" s="1">
         <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -30314,8 +31677,11 @@
       <c r="J82" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K82" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="83" ht="12.8">
       <c r="D83" s="1" t="s">
         <v>134</v>
       </c>
@@ -30569,8 +31935,8 @@
       <c r="IU83" s="1"/>
       <c r="IV83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H84" s="1" t="n">
+    <row r="84" ht="12.8">
+      <c r="H84" s="1">
         <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -30579,8 +31945,11 @@
       <c r="J84" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K84" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
       <c r="A86" s="1" t="s">
         <v>97</v>
       </c>
@@ -30591,7 +31960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="D87" s="1" t="s">
         <v>90</v>
       </c>
@@ -30599,17 +31968,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" ht="12.8">
       <c r="B89" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="12.8">
       <c r="A93" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.8">
       <c r="D94" s="1" t="s">
         <v>102</v>
       </c>
@@ -30617,7 +31986,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="12.8">
       <c r="D95" s="1" t="s">
         <v>128</v>
       </c>
@@ -30625,7 +31994,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="12.8">
       <c r="D96" s="1" t="s">
         <v>86</v>
       </c>
@@ -30879,7 +32248,7 @@
       <c r="IU96" s="1"/>
       <c r="IV96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="12.8">
       <c r="D97" s="1" t="s">
         <v>107</v>
       </c>
@@ -30887,31 +32256,40 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H99" s="1" t="n">
+    <row r="99" ht="22.35">
+      <c r="H99" s="1">
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H100" s="1" t="n">
+      <c r="K99" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="100" ht="43.25">
+      <c r="H100" s="1">
         <v>12</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H101" s="1" t="n">
+      <c r="K100" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="101" ht="22.35">
+      <c r="H101" s="1">
         <v>13</v>
       </c>
       <c r="I101" s="10" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K101" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="102" ht="12.8">
       <c r="D102" s="1" t="s">
         <v>134</v>
       </c>
@@ -30919,23 +32297,29 @@
         <v>135</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H103" s="1" t="n">
+    <row r="103" ht="43.25">
+      <c r="H103" s="1">
         <v>14</v>
       </c>
       <c r="I103" s="10" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H104" s="1" t="n">
+      <c r="K103" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="104" ht="32.8">
+      <c r="H104" s="1">
         <v>15</v>
       </c>
       <c r="I104" s="10" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="105" s="9" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K104" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="105" s="9" customFormat="1" ht="22.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -30943,14 +32327,16 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-      <c r="H105" s="1" t="n">
+      <c r="H105" s="1">
         <v>16</v>
       </c>
       <c r="I105" s="10" t="s">
         <v>474</v>
       </c>
       <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
+      <c r="K105" s="1" t="s">
+        <v>686</v>
+      </c>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -31197,14 +32583,16 @@
       <c r="IU105" s="1"/>
       <c r="IV105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H106" s="1" t="n">
+    <row r="106" ht="22.35">
+      <c r="H106" s="1">
         <v>17</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="K106" s="1"/>
+      <c r="K106" s="1" t="s">
+        <v>687</v>
+      </c>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
@@ -31451,7 +32839,7 @@
       <c r="IU106" s="1"/>
       <c r="IV106" s="1"/>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="12.8">
       <c r="D107" s="1" t="s">
         <v>134</v>
       </c>
@@ -31459,14 +32847,16 @@
         <v>135</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H108" s="1" t="n">
+    <row r="108" ht="32.8">
+      <c r="H108" s="1">
         <v>18</v>
       </c>
       <c r="I108" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="K108" s="1"/>
+      <c r="K108" s="1" t="s">
+        <v>688</v>
+      </c>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
@@ -31713,7 +33103,7 @@
       <c r="IU108" s="1"/>
       <c r="IV108" s="1"/>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="12.8">
       <c r="D109" s="1" t="s">
         <v>134</v>
       </c>
@@ -31721,64 +33111,85 @@
         <v>135</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H110" s="1" t="n">
+    <row r="110" ht="12.8">
+      <c r="H110" s="1">
         <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H111" s="1" t="n">
+      <c r="K110" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="111" ht="32.8">
+      <c r="H111" s="1">
         <v>20</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H112" s="1" t="n">
+      <c r="K111" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="112" ht="32.8">
+      <c r="H112" s="1">
         <v>21</v>
       </c>
       <c r="I112" s="10" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H113" s="1" t="n">
+      <c r="K112" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="113" ht="22.35">
+      <c r="H113" s="1">
         <v>22</v>
       </c>
       <c r="I113" s="10" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H114" s="1" t="n">
+      <c r="K113" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="114" ht="32.8">
+      <c r="H114" s="1">
         <v>23</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H115" s="1" t="n">
+      <c r="K114" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="115" ht="32.8">
+      <c r="H115" s="1">
         <v>24</v>
       </c>
       <c r="I115" s="10" t="s">
         <v>482</v>
       </c>
+      <c r="K115" t="s">
+        <v>694</v>
+      </c>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H116" s="1" t="n">
+    <row r="116" ht="12.8">
+      <c r="H116" s="1">
         <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K116" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="117" ht="12.8">
       <c r="D117" s="1" t="s">
         <v>134</v>
       </c>
@@ -31786,47 +33197,62 @@
         <v>135</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H118" s="1" t="n">
+    <row r="118" ht="22.35">
+      <c r="H118" s="1">
         <v>26</v>
       </c>
       <c r="I118" s="10" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H119" s="1" t="n">
+      <c r="K118" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="119" ht="32.8">
+      <c r="H119" s="1">
         <v>27</v>
       </c>
       <c r="I119" s="10" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H120" s="1" t="n">
+      <c r="K119" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="120" ht="32.8">
+      <c r="H120" s="1">
         <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H121" s="1" t="n">
+      <c r="K120" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="121" ht="32.8">
+      <c r="H121" s="1">
         <v>29</v>
       </c>
       <c r="I121" s="10" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H122" s="1" t="n">
+      <c r="K121" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="122" ht="32.8">
+      <c r="H122" s="1">
         <v>30</v>
       </c>
       <c r="I122" s="10" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K122" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="123" ht="12.8">
       <c r="D123" s="1" t="s">
         <v>84</v>
       </c>
@@ -31834,7 +33260,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" ht="12.8">
       <c r="D124" s="1" t="s">
         <v>102</v>
       </c>
@@ -31842,7 +33268,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="12.8">
       <c r="D125" s="1" t="s">
         <v>85</v>
       </c>
@@ -31850,7 +33276,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" ht="12.8">
       <c r="D126" s="1" t="s">
         <v>86</v>
       </c>
@@ -32104,7 +33530,7 @@
       <c r="IU126" s="1"/>
       <c r="IV126" s="1"/>
     </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" ht="12.8">
       <c r="D127" s="1" t="s">
         <v>107</v>
       </c>
@@ -32112,12 +33538,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" ht="12.8">
       <c r="D128" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" ht="12.8">
       <c r="D129" s="1" t="s">
         <v>84</v>
       </c>
@@ -32125,7 +33551,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" ht="12.8">
       <c r="D130" s="1" t="s">
         <v>102</v>
       </c>
@@ -32133,12 +33559,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
       <c r="B131" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="135" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" s="9" customFormat="1" ht="12.8">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -32396,7 +33822,7 @@
       <c r="IU135" s="1"/>
       <c r="IV135" s="1"/>
     </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" ht="12.8">
       <c r="K136" s="1"/>
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
@@ -32644,7 +34070,7 @@
       <c r="IU136" s="1"/>
       <c r="IV136" s="1"/>
     </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="12.8">
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
@@ -32892,12 +34318,12 @@
       <c r="IU138" s="1"/>
       <c r="IV138" s="1"/>
     </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" ht="12.8">
       <c r="A139" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="12.8">
       <c r="D140" s="1" t="s">
         <v>128</v>
       </c>
@@ -32905,7 +34331,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" ht="12.8">
       <c r="D141" s="1" t="s">
         <v>86</v>
       </c>
@@ -33159,7 +34585,7 @@
       <c r="IU141" s="1"/>
       <c r="IV141" s="1"/>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" ht="12.8">
       <c r="D142" s="1" t="s">
         <v>107</v>
       </c>
@@ -33167,12 +34593,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" ht="12.8">
       <c r="D143" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" ht="12.8">
       <c r="D144" s="1" t="s">
         <v>84</v>
       </c>
@@ -33180,12 +34606,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" ht="12.8">
       <c r="B145" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" ht="12.8">
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1"/>
@@ -33433,7 +34859,7 @@
       <c r="IU148" s="1"/>
       <c r="IV148" s="1"/>
     </row>
-    <row r="150" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="9" customFormat="1" ht="12.8">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -33691,7 +35117,7 @@
       <c r="IU150" s="1"/>
       <c r="IV150" s="1"/>
     </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" ht="12.8">
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -33939,7 +35365,7 @@
       <c r="IU151" s="1"/>
       <c r="IV151" s="1"/>
     </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" ht="12.8">
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
@@ -34187,7 +35613,7 @@
       <c r="IU153" s="1"/>
       <c r="IV153" s="1"/>
     </row>
-    <row r="157" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="9" customFormat="1" ht="12.8">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -34445,7 +35871,7 @@
       <c r="IU157" s="1"/>
       <c r="IV157" s="1"/>
     </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" ht="12.8">
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
@@ -34693,7 +36119,7 @@
       <c r="IU158" s="1"/>
       <c r="IV158" s="1"/>
     </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" ht="12.8">
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
@@ -34943,12 +36369,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
